--- a/docs/youtube-bias-feedback_backlog.xlsx
+++ b/docs/youtube-bias-feedback_backlog.xlsx
@@ -11,7 +11,7 @@
     <sheet name="미분류·확인 필요" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'백로그'!$A$1:$K$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'백로그'!$A$1:$K$170</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K167"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3071,190 +3071,186 @@
       </c>
     </row>
     <row r="56" outlineLevel="2">
-      <c r="A56" s="9" t="n">
+      <c r="A56" s="15" t="n">
         <v>55</v>
       </c>
-      <c r="B56" s="10" t="inlineStr">
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C56" s="10" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-3</t>
+        </is>
+      </c>
+      <c r="D56" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="n">
+        <v>301</v>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 끝난 구간의 기간 리뷰가 팝업 캐시 때문에 다음 날까지 보이지 않음</t>
+        </is>
+      </c>
+      <c r="H56" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="n"/>
+      <c r="J56" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="K56" s="20" t="inlineStr">
+        <is>
+          <t>#301</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="9" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
         <is>
           <t>Story 3-5</t>
         </is>
       </c>
-      <c r="D56" s="9" t="n">
+      <c r="D57" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="11" t="inlineStr">
+      <c r="E57" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F56" s="9" t="n">
+      <c r="F57" s="9" t="n">
         <v>270</v>
       </c>
-      <c r="G56" s="12" t="inlineStr">
+      <c r="G57" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 3-5: 참가자마다 익명 ID가 발급되어 데이터가 참가자 단위로 저장된다</t>
         </is>
       </c>
-      <c r="H56" s="23" t="inlineStr">
+      <c r="H57" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I56" s="10" t="n"/>
-      <c r="J56" s="9" t="n">
+      <c r="I57" s="10" t="n"/>
+      <c r="J57" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="K56" s="14" t="inlineStr">
+      <c r="K57" s="14" t="inlineStr">
         <is>
           <t>#270</t>
         </is>
       </c>
     </row>
-    <row r="57" outlineLevel="1">
-      <c r="A57" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
+    <row r="58" outlineLevel="2">
+      <c r="A58" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C57" s="16" t="inlineStr">
+      <c r="C58" s="16" t="inlineStr">
         <is>
           <t>Story 3-5</t>
         </is>
       </c>
-      <c r="D57" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E57" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F57" s="15" t="n">
+      <c r="D58" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F58" s="15" t="n">
         <v>88</v>
       </c>
-      <c r="G57" s="18" t="inlineStr">
+      <c r="G58" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat: 온보딩 시 anonymousId(UUID) 생성</t>
         </is>
       </c>
-      <c r="H57" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
+      <c r="H58" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>#90</t>
         </is>
       </c>
-      <c r="J57" s="15" t="n">
+      <c r="J58" s="15" t="n">
         <v>270</v>
       </c>
-      <c r="K57" s="20" t="inlineStr">
+      <c r="K58" s="20" t="inlineStr">
         <is>
           <t>#88</t>
         </is>
       </c>
     </row>
-    <row r="58" outlineLevel="2">
-      <c r="A58" s="9" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
+    <row r="59" outlineLevel="2">
+      <c r="A59" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C58" s="10" t="inlineStr">
+      <c r="C59" s="10" t="inlineStr">
         <is>
           <t>Story 3-6</t>
         </is>
       </c>
-      <c r="D58" s="9" t="n">
+      <c r="D59" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E58" s="11" t="inlineStr">
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F58" s="9" t="n">
+      <c r="F59" s="9" t="n">
         <v>290</v>
       </c>
-      <c r="G58" s="12" t="inlineStr">
+      <c r="G59" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 3-6: 참가자가 개편된 팝업에서 집단별 화면과 오늘의 시청 현황을 볼 수 있다</t>
         </is>
       </c>
-      <c r="H58" s="23" t="inlineStr">
+      <c r="H59" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I58" s="10" t="n"/>
-      <c r="J58" s="9" t="n">
+      <c r="I59" s="10" t="n"/>
+      <c r="J59" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="K58" s="14" t="inlineStr">
+      <c r="K59" s="14" t="inlineStr">
         <is>
           <t>#290</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" outlineLevel="2">
-      <c r="A59" s="15" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>Epic 3</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>Story 3-6</t>
-        </is>
-      </c>
-      <c r="D59" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F59" s="15" t="n">
-        <v>86</v>
-      </c>
-      <c r="G59" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 팝업 UI 전면 개편(실험군/대조군에 따른 UI 분기)</t>
-        </is>
-      </c>
-      <c r="H59" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>#87</t>
-        </is>
-      </c>
-      <c r="J59" s="15" t="n">
-        <v>290</v>
-      </c>
-      <c r="K59" s="20" t="inlineStr">
-        <is>
-          <t>#86</t>
         </is>
       </c>
     </row>
@@ -3281,11 +3277,11 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G60" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘의 시청 탭 ux 개선</t>
+          <t xml:space="preserve">        feat: 팝업 UI 전면 개편(실험군/대조군에 따른 UI 분기)</t>
         </is>
       </c>
       <c r="H60" s="19" t="inlineStr">
@@ -3295,7 +3291,7 @@
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
-          <t>#96</t>
+          <t>#87</t>
         </is>
       </c>
       <c r="J60" s="15" t="n">
@@ -3303,136 +3299,140 @@
       </c>
       <c r="K60" s="20" t="inlineStr">
         <is>
+          <t>#86</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-6</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="G61" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 오늘의 시청 탭 ux 개선</t>
+        </is>
+      </c>
+      <c r="H61" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>#96</t>
+        </is>
+      </c>
+      <c r="J61" s="15" t="n">
+        <v>290</v>
+      </c>
+      <c r="K61" s="20" t="inlineStr">
+        <is>
           <t>#95</t>
         </is>
       </c>
     </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
+    <row r="62" outlineLevel="2">
+      <c r="A62" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Epic 4</t>
         </is>
       </c>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="3" t="n">
+      <c r="C62" s="4" t="n"/>
+      <c r="D62" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F61" s="3" t="n">
+      <c r="F62" s="3" t="n">
         <v>43</v>
       </c>
-      <c r="G61" s="6" t="inlineStr">
+      <c r="G62" s="6" t="inlineStr">
         <is>
           <t>Epic 4: 백엔드 서버 - API &amp; DB</t>
         </is>
       </c>
-      <c r="H61" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="3" t="n"/>
-      <c r="K61" s="8" t="inlineStr">
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="3" t="n"/>
+      <c r="K62" s="8" t="inlineStr">
         <is>
           <t>#43</t>
         </is>
       </c>
     </row>
-    <row r="62" outlineLevel="2">
-      <c r="A62" s="9" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="10" t="inlineStr">
+    <row r="63" outlineLevel="2">
+      <c r="A63" s="9" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Epic 4</t>
         </is>
       </c>
-      <c r="C62" s="10" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>Story 4-1</t>
         </is>
       </c>
-      <c r="D62" s="9" t="n">
+      <c r="D63" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="11" t="inlineStr">
+      <c r="E63" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F62" s="9" t="n">
+      <c r="F63" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="G62" s="12" t="inlineStr">
+      <c r="G63" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 4-1: 서버가 익명화된 세션 분석 결과를 수신하여 DB에 저장할 수 있다</t>
         </is>
       </c>
-      <c r="H62" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="n"/>
-      <c r="J62" s="9" t="n">
+      <c r="H63" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I63" s="10" t="n"/>
+      <c r="J63" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="K62" s="14" t="inlineStr">
+      <c r="K63" s="14" t="inlineStr">
         <is>
           <t>#44</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" outlineLevel="2">
-      <c r="A63" s="15" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-1</t>
-        </is>
-      </c>
-      <c r="D63" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="G63" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        db.js 작성 - SQLite 연결 및 테이블 초기화</t>
-        </is>
-      </c>
-      <c r="H63" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I63" s="16" t="n"/>
-      <c r="J63" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="K63" s="20" t="inlineStr">
-        <is>
-          <t>#45</t>
         </is>
       </c>
     </row>
@@ -3459,11 +3459,11 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        sessions 테이블 스키마 정의</t>
+          <t xml:space="preserve">        db.js 작성 - SQLite 연결 및 테이블 초기화</t>
         </is>
       </c>
       <c r="H64" s="19" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="K64" s="20" t="inlineStr">
         <is>
-          <t>#46</t>
+          <t>#45</t>
         </is>
       </c>
     </row>
@@ -3504,11 +3504,11 @@
         </is>
       </c>
       <c r="F65" s="15" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        POST /api/sessions 라우터 구현</t>
+          <t xml:space="preserve">        sessions 테이블 스키마 정의</t>
         </is>
       </c>
       <c r="H65" s="19" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K65" s="20" t="inlineStr">
         <is>
-          <t>#47</t>
+          <t>#46</t>
         </is>
       </c>
     </row>
@@ -3549,11 +3549,11 @@
         </is>
       </c>
       <c r="F66" s="15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G66" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        sessions 라우터 입력값 검증 로직 구현</t>
+          <t xml:space="preserve">        POST /api/sessions 라우터 구현</t>
         </is>
       </c>
       <c r="H66" s="19" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="K66" s="20" t="inlineStr">
         <is>
-          <t>#48</t>
+          <t>#47</t>
         </is>
       </c>
     </row>
@@ -3594,11 +3594,11 @@
         </is>
       </c>
       <c r="F67" s="15" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: POST /api/sessions - 익명화된 세션 분석 결과 수신하여 DB에 저장할 수 있다</t>
+          <t xml:space="preserve">        sessions 라우터 입력값 검증 로직 구현</t>
         </is>
       </c>
       <c r="H67" s="19" t="inlineStr">
@@ -3606,17 +3606,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>#74</t>
-        </is>
-      </c>
+      <c r="I67" s="16" t="n"/>
       <c r="J67" s="15" t="n">
         <v>44</v>
       </c>
       <c r="K67" s="20" t="inlineStr">
         <is>
-          <t>#73</t>
+          <t>#48</t>
         </is>
       </c>
     </row>
@@ -3643,11 +3639,11 @@
         </is>
       </c>
       <c r="F68" s="15" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 세션 분석 완료 후 서버 전송</t>
+          <t xml:space="preserve">        feat: POST /api/sessions - 익명화된 세션 분석 결과 수신하여 DB에 저장할 수 있다</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
@@ -3657,7 +3653,7 @@
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
-          <t>#92</t>
+          <t>#74</t>
         </is>
       </c>
       <c r="J68" s="15" t="n">
@@ -3665,52 +3661,56 @@
       </c>
       <c r="K68" s="20" t="inlineStr">
         <is>
+          <t>#73</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-1</t>
+        </is>
+      </c>
+      <c r="D69" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 세션 분석 완료 후 서버 전송</t>
+        </is>
+      </c>
+      <c r="H69" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>#92</t>
+        </is>
+      </c>
+      <c r="J69" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="K69" s="20" t="inlineStr">
+        <is>
           <t>#89</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" outlineLevel="1">
-      <c r="A69" s="9" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Story 4-2</t>
-        </is>
-      </c>
-      <c r="D69" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="G69" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 4-2: 실험 온보딩 및 설문 알림 기능을 사용할 수 있다</t>
-        </is>
-      </c>
-      <c r="H69" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="n"/>
-      <c r="J69" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="K69" s="14" t="inlineStr">
-        <is>
-          <t>#49</t>
         </is>
       </c>
     </row>
@@ -3737,11 +3737,11 @@
         </is>
       </c>
       <c r="F70" s="9" t="n">
-        <v>271</v>
+        <v>49</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 4-2: 서버가 설문 응답을 수신하여 DB에 저장할 수 있다</t>
+          <t xml:space="preserve">    Story 4-2: 실험 온보딩 및 설문 알림 기능을 사용할 수 있다</t>
         </is>
       </c>
       <c r="H70" s="13" t="inlineStr">
@@ -3755,52 +3755,52 @@
       </c>
       <c r="K70" s="14" t="inlineStr">
         <is>
+          <t>#49</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="2">
+      <c r="A71" s="9" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>Story 4-2</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 4-2: 서버가 설문 응답을 수신하여 DB에 저장할 수 있다</t>
+        </is>
+      </c>
+      <c r="H71" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="n"/>
+      <c r="J71" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="K71" s="14" t="inlineStr">
+        <is>
           <t>#271</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" outlineLevel="2">
-      <c r="A71" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C71" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-2</t>
-        </is>
-      </c>
-      <c r="D71" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="G71" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        surveys 테이블 스키마 정의</t>
-        </is>
-      </c>
-      <c r="H71" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I71" s="16" t="n"/>
-      <c r="J71" s="15" t="n">
-        <v>271</v>
-      </c>
-      <c r="K71" s="20" t="inlineStr">
-        <is>
-          <t>#50</t>
         </is>
       </c>
     </row>
@@ -3827,11 +3827,11 @@
         </is>
       </c>
       <c r="F72" s="15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G72" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: POST /api/surveys 라우터 구현</t>
+          <t xml:space="preserve">        surveys 테이블 스키마 정의</t>
         </is>
       </c>
       <c r="H72" s="19" t="inlineStr">
@@ -3845,97 +3845,97 @@
       </c>
       <c r="K72" s="20" t="inlineStr">
         <is>
+          <t>#50</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="2">
+      <c r="A73" s="15" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-2</t>
+        </is>
+      </c>
+      <c r="D73" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="n">
+        <v>51</v>
+      </c>
+      <c r="G73" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: POST /api/surveys 라우터 구현</t>
+        </is>
+      </c>
+      <c r="H73" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I73" s="16" t="n"/>
+      <c r="J73" s="15" t="n">
+        <v>271</v>
+      </c>
+      <c r="K73" s="20" t="inlineStr">
+        <is>
           <t>#51</t>
         </is>
       </c>
     </row>
-    <row r="73" outlineLevel="2">
-      <c r="A73" s="9" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
+    <row r="74" outlineLevel="2">
+      <c r="A74" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>Epic 4</t>
         </is>
       </c>
-      <c r="C73" s="10" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
         <is>
           <t>Story 4-3</t>
         </is>
       </c>
-      <c r="D73" s="9" t="n">
+      <c r="D74" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E73" s="11" t="inlineStr">
+      <c r="E74" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F73" s="9" t="n">
+      <c r="F74" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="G73" s="12" t="inlineStr">
+      <c r="G74" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 4-3: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
         </is>
       </c>
-      <c r="H73" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I73" s="10" t="n"/>
-      <c r="J73" s="9" t="n">
+      <c r="H74" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="n"/>
+      <c r="J74" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="K73" s="14" t="inlineStr">
+      <c r="K74" s="14" t="inlineStr">
         <is>
           <t>#78</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" outlineLevel="2">
-      <c r="A74" s="15" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C74" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-3</t>
-        </is>
-      </c>
-      <c r="D74" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E74" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F74" s="15" t="n">
-        <v>52</v>
-      </c>
-      <c r="G74" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        chore: 서버 외부 배포 및 /health 확인</t>
-        </is>
-      </c>
-      <c r="H74" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I74" s="16" t="n"/>
-      <c r="J74" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="K74" s="20" t="inlineStr">
-        <is>
-          <t>#52</t>
         </is>
       </c>
     </row>
@@ -3962,11 +3962,11 @@
         </is>
       </c>
       <c r="F75" s="15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G75" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        docs: .env.example 파일 작성</t>
+          <t xml:space="preserve">        chore: 서버 외부 배포 및 /health 확인</t>
         </is>
       </c>
       <c r="H75" s="19" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="K75" s="20" t="inlineStr">
         <is>
-          <t>#53</t>
+          <t>#52</t>
         </is>
       </c>
     </row>
@@ -4007,11 +4007,11 @@
         </is>
       </c>
       <c r="F76" s="15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G76" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        deploy: 서버 배포</t>
+          <t xml:space="preserve">        docs: .env.example 파일 작성</t>
         </is>
       </c>
       <c r="H76" s="19" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="K76" s="20" t="inlineStr">
         <is>
-          <t>#54</t>
+          <t>#53</t>
         </is>
       </c>
     </row>
@@ -4052,11 +4052,11 @@
         </is>
       </c>
       <c r="F77" s="15" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
+          <t xml:space="preserve">        deploy: 서버 배포</t>
         </is>
       </c>
       <c r="H77" s="19" t="inlineStr">
@@ -4064,105 +4064,101 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>#80</t>
-        </is>
-      </c>
+      <c r="I77" s="16" t="n"/>
       <c r="J77" s="15" t="n">
         <v>78</v>
       </c>
       <c r="K77" s="20" t="inlineStr">
         <is>
+          <t>#54</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="15" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="16" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C78" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-3</t>
+        </is>
+      </c>
+      <c r="D78" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="G78" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
+        </is>
+      </c>
+      <c r="H78" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>#80</t>
+        </is>
+      </c>
+      <c r="J78" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="K78" s="20" t="inlineStr">
+        <is>
           <t>#79</t>
         </is>
       </c>
     </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="3" t="n">
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F78" s="3" t="n">
+      <c r="F79" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Epic 5: 데이터·개인정보 보강</t>
         </is>
       </c>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I78" s="4" t="n"/>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="8" t="inlineStr">
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="8" t="inlineStr">
         <is>
           <t>#127</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" outlineLevel="1">
-      <c r="A79" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>Epic 5</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>Story 10-1</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F79" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="G79" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 10-1: 가명처리 기반 식별자 체계 및 IRB / 개인정보 처리방침 재설계</t>
-        </is>
-      </c>
-      <c r="H79" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I79" s="10" t="inlineStr">
-        <is>
-          <t>#129</t>
-        </is>
-      </c>
-      <c r="J79" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="K79" s="14" t="inlineStr">
-        <is>
-          <t>#128</t>
         </is>
       </c>
     </row>
@@ -4177,7 +4173,7 @@
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Story 5-2</t>
+          <t>Story 10-1</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
@@ -4189,11 +4185,11 @@
         </is>
       </c>
       <c r="F80" s="9" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-2: 데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
+          <t xml:space="preserve">    Story 10-1: 가명처리 기반 식별자 체계 및 IRB / 개인정보 처리방침 재설계</t>
         </is>
       </c>
       <c r="H80" s="13" t="inlineStr">
@@ -4203,7 +4199,7 @@
       </c>
       <c r="I80" s="10" t="inlineStr">
         <is>
-          <t>#131</t>
+          <t>#129</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
@@ -4211,105 +4207,105 @@
       </c>
       <c r="K80" s="14" t="inlineStr">
         <is>
+          <t>#128</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>Story 5-2</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F81" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 5-2: 데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
+        </is>
+      </c>
+      <c r="H81" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I81" s="10" t="inlineStr">
+        <is>
+          <t>#131</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="K81" s="14" t="inlineStr">
+        <is>
           <t>#130</t>
         </is>
       </c>
     </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="15" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C82" s="16" t="inlineStr">
         <is>
           <t>Story 5-2</t>
         </is>
       </c>
-      <c r="D81" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E81" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="n">
+      <c r="D82" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="n">
         <v>116</v>
       </c>
-      <c r="G81" s="21" t="inlineStr">
+      <c r="G82" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">        데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
         </is>
       </c>
-      <c r="H81" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
+      <c r="H82" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
         <is>
           <t>#121</t>
         </is>
       </c>
-      <c r="J81" s="15" t="n">
+      <c r="J82" s="15" t="n">
         <v>130</v>
       </c>
-      <c r="K81" s="20" t="inlineStr">
+      <c r="K82" s="20" t="inlineStr">
         <is>
           <t>#116</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="A82" s="9" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="10" t="inlineStr">
-        <is>
-          <t>Epic 5</t>
-        </is>
-      </c>
-      <c r="C82" s="10" t="inlineStr">
-        <is>
-          <t>Story 5-3</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F82" s="9" t="n">
-        <v>117</v>
-      </c>
-      <c r="G82" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 5-3: 세션 처리 지연시간(Latency) 로깅</t>
-        </is>
-      </c>
-      <c r="H82" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I82" s="10" t="inlineStr">
-        <is>
-          <t>#125</t>
-        </is>
-      </c>
-      <c r="J82" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="K82" s="14" t="inlineStr">
-        <is>
-          <t>#117</t>
         </is>
       </c>
     </row>
@@ -4324,7 +4320,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Story 5-4</t>
+          <t>Story 5-3</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
@@ -4336,11 +4332,11 @@
         </is>
       </c>
       <c r="F83" s="9" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-4: LLM 실패·폴백 작동 로깅</t>
+          <t xml:space="preserve">    Story 5-3: 세션 처리 지연시간(Latency) 로깅</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -4358,7 +4354,7 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>#118</t>
+          <t>#117</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4369,7 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Story 5-5</t>
+          <t>Story 5-4</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
@@ -4385,11 +4381,11 @@
         </is>
       </c>
       <c r="F84" s="9" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-5: 팝업 상호작용(체류시간·탭 클릭) 마이크로 로그</t>
+          <t xml:space="preserve">    Story 5-4: LLM 실패·폴백 작동 로깅</t>
         </is>
       </c>
       <c r="H84" s="13" t="inlineStr">
@@ -4407,7 +4403,7 @@
       </c>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>#119</t>
+          <t>#118</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4418,7 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Story 5-6</t>
+          <t>Story 5-5</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
@@ -4434,11 +4430,11 @@
         </is>
       </c>
       <c r="F85" s="9" t="n">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-6: 세션 분석 완료 알림 및 피드백 열람 유도</t>
+          <t xml:space="preserve">    Story 5-5: 팝업 상호작용(체류시간·탭 클릭) 마이크로 로그</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4448,7 +4444,7 @@
       </c>
       <c r="I85" s="10" t="inlineStr">
         <is>
-          <t>#133</t>
+          <t>#125</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
@@ -4456,7 +4452,7 @@
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>#132</t>
+          <t>#119</t>
         </is>
       </c>
     </row>
@@ -4471,7 +4467,7 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Story 5-7</t>
+          <t>Story 5-6</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
@@ -4483,11 +4479,11 @@
         </is>
       </c>
       <c r="F86" s="9" t="n">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-7: 세밀 다양성 신호(토픽·채널·발견 경로)</t>
+          <t xml:space="preserve">    Story 5-6: 세션 분석 완료 알림 및 피드백 열람 유도</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
@@ -4497,7 +4493,7 @@
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>#141</t>
+          <t>#133</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
@@ -4505,7 +4501,7 @@
       </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>#140</t>
+          <t>#132</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4516,7 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Story 5-8</t>
+          <t>Story 5-7</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
@@ -4532,11 +4528,11 @@
         </is>
       </c>
       <c r="F87" s="9" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-8: 2주 베이스라인 이후 그룹(CON/EXP) 분기 전달</t>
+          <t xml:space="preserve">    Story 5-7: 세밀 다양성 신호(토픽·채널·발견 경로)</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4546,7 +4542,7 @@
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>#137</t>
+          <t>#141</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
@@ -4554,7 +4550,7 @@
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>#136</t>
+          <t>#140</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4565,7 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Story 5-9</t>
+          <t>Story 5-8</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
@@ -4581,25 +4577,29 @@
         </is>
       </c>
       <c r="F88" s="9" t="n">
-        <v>291</v>
+        <v>136</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-9: 설문 척도 설계·검증 (다문항화·파일럿)</t>
-        </is>
-      </c>
-      <c r="H88" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I88" s="10" t="n"/>
+          <t xml:space="preserve">    Story 5-8: 2주 베이스라인 이후 그룹(CON/EXP) 분기 전달</t>
+        </is>
+      </c>
+      <c r="H88" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>#137</t>
+        </is>
+      </c>
       <c r="J88" s="9" t="n">
         <v>127</v>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>#291</t>
+          <t>#136</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Story 10-11</t>
+          <t>Story 5-9</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
@@ -4626,33 +4626,29 @@
         </is>
       </c>
       <c r="F89" s="9" t="n">
-        <v>138</v>
+        <v>291</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 10-11: llm.js 피드백 보강 (서버 저장·문구 톤 통일·프롬프트 버전·가드레일 필터)</t>
-        </is>
-      </c>
-      <c r="H89" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="inlineStr">
-        <is>
-          <t>#139</t>
-        </is>
-      </c>
+          <t xml:space="preserve">    Story 5-9: 설문 척도 설계·검증 (다문항화·파일럿)</t>
+        </is>
+      </c>
+      <c r="H89" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="n"/>
       <c r="J89" s="9" t="n">
         <v>127</v>
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>#138</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" outlineLevel="2" ht="25.5" customHeight="1">
+          <t>#291</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" outlineLevel="2">
       <c r="A90" s="9" t="n">
         <v>89</v>
       </c>
@@ -4663,7 +4659,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Story 5-11</t>
+          <t>Story 10-11</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
@@ -4675,11 +4671,11 @@
         </is>
       </c>
       <c r="F90" s="9" t="n">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-11: 기간 리뷰를 다시 생성해도 참가자가 본 이전 버전이 보존된다</t>
+          <t xml:space="preserve">    Story 10-11: llm.js 피드백 보강 (서버 저장·문구 톤 통일·프롬프트 버전·가드레일 필터)</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4687,148 +4683,152 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I90" s="10" t="n"/>
+      <c r="I90" s="10" t="inlineStr">
+        <is>
+          <t>#139</t>
+        </is>
+      </c>
       <c r="J90" s="9" t="n">
         <v>127</v>
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
+          <t>#138</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="25.5" customHeight="1">
+      <c r="A91" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>Story 5-11</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="n">
+        <v>273</v>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 5-11: 기간 리뷰를 다시 생성해도 참가자가 본 이전 버전이 보존된다</t>
+        </is>
+      </c>
+      <c r="H91" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I91" s="10" t="n"/>
+      <c r="J91" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="K91" s="14" t="inlineStr">
+        <is>
           <t>#273</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="15" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="16" t="inlineStr">
+    <row r="92" outlineLevel="1">
+      <c r="A92" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr">
+      <c r="C92" s="16" t="inlineStr">
         <is>
           <t>Story 5-11</t>
         </is>
       </c>
-      <c r="D91" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E91" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F91" s="15" t="n">
+      <c r="D92" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="n">
         <v>224</v>
       </c>
-      <c r="G91" s="18" t="inlineStr">
+      <c r="G92" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat: 기간 리뷰를 다시 생성해도 참여자가 본 이전 버전이 남도록 append-only 이력 테이블 추가</t>
         </is>
       </c>
-      <c r="H91" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I91" s="16" t="n"/>
-      <c r="J91" s="15" t="n">
+      <c r="H92" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I92" s="16" t="n"/>
+      <c r="J92" s="15" t="n">
         <v>273</v>
       </c>
-      <c r="K91" s="20" t="inlineStr">
+      <c r="K92" s="20" t="inlineStr">
         <is>
           <t>#224</t>
         </is>
       </c>
     </row>
-    <row r="92" outlineLevel="1">
-      <c r="A92" s="9" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="10" t="inlineStr">
+    <row r="93" outlineLevel="2">
+      <c r="A93" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>Story 5-12</t>
         </is>
       </c>
-      <c r="D92" s="9" t="n">
+      <c r="D93" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E92" s="11" t="inlineStr">
+      <c r="E93" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F92" s="9" t="n">
+      <c r="F93" s="9" t="n">
         <v>292</v>
       </c>
-      <c r="G92" s="12" t="inlineStr">
+      <c r="G93" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 5-12: 시청 맥락(유입 경로·영상·채널 메타데이터)을 함께 수집한다</t>
         </is>
       </c>
-      <c r="H92" s="23" t="inlineStr">
+      <c r="H93" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I92" s="10" t="n"/>
-      <c r="J92" s="9" t="n">
+      <c r="I93" s="10" t="n"/>
+      <c r="J93" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="K92" s="14" t="inlineStr">
+      <c r="K93" s="14" t="inlineStr">
         <is>
           <t>#292</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" outlineLevel="2">
-      <c r="A93" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>Epic 5</t>
-        </is>
-      </c>
-      <c r="C93" s="16" t="inlineStr">
-        <is>
-          <t>Story 5-12</t>
-        </is>
-      </c>
-      <c r="D93" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E93" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F93" s="15" t="n">
-        <v>178</v>
-      </c>
-      <c r="G93" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 영상 시청 이벤트에 유입 경로 라벨링 및 자동재생/클릭 구분 로직 추가</t>
-        </is>
-      </c>
-      <c r="H93" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I93" s="16" t="n"/>
-      <c r="J93" s="15" t="n">
-        <v>292</v>
-      </c>
-      <c r="K93" s="20" t="inlineStr">
-        <is>
-          <t>#178</t>
         </is>
       </c>
     </row>
@@ -4855,11 +4855,11 @@
         </is>
       </c>
       <c r="F94" s="15" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G94" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat:YouTube 영상·채널 메타데이터 수집 확장</t>
+          <t xml:space="preserve">        feat: 영상 시청 이벤트에 유입 경로 라벨링 및 자동재생/클릭 구분 로직 추가</t>
         </is>
       </c>
       <c r="H94" s="19" t="inlineStr">
@@ -4873,136 +4873,136 @@
       </c>
       <c r="K94" s="20" t="inlineStr">
         <is>
+          <t>#178</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="2">
+      <c r="A95" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="inlineStr">
+        <is>
+          <t>Story 5-12</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="G95" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat:YouTube 영상·채널 메타데이터 수집 확장</t>
+        </is>
+      </c>
+      <c r="H95" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I95" s="16" t="n"/>
+      <c r="J95" s="15" t="n">
+        <v>292</v>
+      </c>
+      <c r="K95" s="20" t="inlineStr">
+        <is>
           <t>#180</t>
         </is>
       </c>
     </row>
-    <row r="95" outlineLevel="2">
-      <c r="A95" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
+    <row r="96" outlineLevel="2">
+      <c r="A96" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="3" t="n">
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="F96" s="3" t="n">
         <v>145</v>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Epic 6. 본 연구 착수 전 기능 안정화</t>
         </is>
       </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="n"/>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="8" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="8" t="inlineStr">
         <is>
           <t>#145</t>
         </is>
       </c>
     </row>
-    <row r="96" outlineLevel="2">
-      <c r="A96" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="10" t="inlineStr">
+    <row r="97" outlineLevel="1">
+      <c r="A97" s="9" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C96" s="10" t="inlineStr">
+      <c r="C97" s="10" t="inlineStr">
         <is>
           <t>Story 6-1</t>
         </is>
       </c>
-      <c r="D96" s="9" t="n">
+      <c r="D97" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E96" s="11" t="inlineStr">
+      <c r="E97" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F96" s="9" t="n">
+      <c r="F97" s="9" t="n">
         <v>274</v>
       </c>
-      <c r="G96" s="12" t="inlineStr">
+      <c r="G97" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-1: 대조군 참가자가 연구 종료 후 6주 누적 리뷰를 열람할 수 있다</t>
         </is>
       </c>
-      <c r="H96" s="23" t="inlineStr">
+      <c r="H97" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I96" s="10" t="n"/>
-      <c r="J96" s="9" t="n">
+      <c r="I97" s="10" t="n"/>
+      <c r="J97" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K96" s="14" t="inlineStr">
+      <c r="K97" s="14" t="inlineStr">
         <is>
           <t>#274</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" outlineLevel="1">
-      <c r="A97" s="15" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C97" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-1</t>
-        </is>
-      </c>
-      <c r="D97" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E97" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F97" s="15" t="n">
-        <v>146</v>
-      </c>
-      <c r="G97" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 대조군 period_reviews 사전 생성 활성화</t>
-        </is>
-      </c>
-      <c r="H97" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I97" s="16" t="n"/>
-      <c r="J97" s="15" t="n">
-        <v>274</v>
-      </c>
-      <c r="K97" s="20" t="inlineStr">
-        <is>
-          <t>#146</t>
         </is>
       </c>
     </row>
@@ -5029,11 +5029,11 @@
         </is>
       </c>
       <c r="F98" s="15" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 대조군 6주 리뷰 열람 접근 제어 + 열람 이벤트 로깅</t>
+          <t xml:space="preserve">        feat: 대조군 period_reviews 사전 생성 활성화</t>
         </is>
       </c>
       <c r="H98" s="19" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="K98" s="20" t="inlineStr">
         <is>
-          <t>#147</t>
+          <t>#146</t>
         </is>
       </c>
     </row>
@@ -5074,11 +5074,11 @@
         </is>
       </c>
       <c r="F99" s="15" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 종료 안내 모달 + 6주 누적 리뷰 화면</t>
+          <t xml:space="preserve">        feat: 대조군 6주 리뷰 열람 접근 제어 + 열람 이벤트 로깅</t>
         </is>
       </c>
       <c r="H99" s="19" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="K99" s="20" t="inlineStr">
         <is>
-          <t>#148</t>
+          <t>#147</t>
         </is>
       </c>
     </row>
@@ -5119,11 +5119,11 @@
         </is>
       </c>
       <c r="F100" s="15" t="n">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 완료 코드 기반 리뷰 열람 게이트</t>
+          <t xml:space="preserve">        feat: 종료 안내 모달 + 6주 누적 리뷰 화면</t>
         </is>
       </c>
       <c r="H100" s="19" t="inlineStr">
@@ -5137,97 +5137,97 @@
       </c>
       <c r="K100" s="20" t="inlineStr">
         <is>
+          <t>#148</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" outlineLevel="2">
+      <c r="A101" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C101" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-1</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="n">
+        <v>159</v>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 연구 완료 코드 기반 리뷰 열람 게이트</t>
+        </is>
+      </c>
+      <c r="H101" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I101" s="16" t="n"/>
+      <c r="J101" s="15" t="n">
+        <v>274</v>
+      </c>
+      <c r="K101" s="20" t="inlineStr">
+        <is>
           <t>#159</t>
         </is>
       </c>
     </row>
-    <row r="101" outlineLevel="2">
-      <c r="A101" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="10" t="inlineStr">
+    <row r="102" outlineLevel="2">
+      <c r="A102" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
+      <c r="C102" s="10" t="inlineStr">
         <is>
           <t>Story 6-2</t>
         </is>
       </c>
-      <c r="D101" s="9" t="n">
+      <c r="D102" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E101" s="11" t="inlineStr">
+      <c r="E102" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F101" s="9" t="n">
+      <c r="F102" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="G101" s="12" t="inlineStr">
+      <c r="G102" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-2: 참가자가 재설치해도 참여코드로 상태를 복구할 수 있다</t>
         </is>
       </c>
-      <c r="H101" s="23" t="inlineStr">
+      <c r="H102" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I101" s="10" t="n"/>
-      <c r="J101" s="9" t="n">
+      <c r="I102" s="10" t="n"/>
+      <c r="J102" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K101" s="14" t="inlineStr">
+      <c r="K102" s="14" t="inlineStr">
         <is>
           <t>#275</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="2">
-      <c r="A102" s="15" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C102" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-2</t>
-        </is>
-      </c>
-      <c r="D102" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E102" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F102" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="G102" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 참여코드 기반 재설치 복구</t>
-        </is>
-      </c>
-      <c r="H102" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I102" s="16" t="n"/>
-      <c r="J102" s="15" t="n">
-        <v>275</v>
-      </c>
-      <c r="K102" s="20" t="inlineStr">
-        <is>
-          <t>#149</t>
         </is>
       </c>
     </row>
@@ -5248,22 +5248,22 @@
       <c r="D103" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E103" s="22" t="inlineStr">
-        <is>
-          <t>Bug</t>
+      <c r="E103" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
         </is>
       </c>
       <c r="F103" s="15" t="n">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 참여자 등록 시 시간대가 없는 installDate를 거부하고 저장 형식을 UTC ISO로 통일</t>
-        </is>
-      </c>
-      <c r="H103" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 참여코드 기반 재설치 복구</t>
+        </is>
+      </c>
+      <c r="H103" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I103" s="16" t="n"/>
@@ -5272,97 +5272,97 @@
       </c>
       <c r="K103" s="20" t="inlineStr">
         <is>
+          <t>#149</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" outlineLevel="2">
+      <c r="A104" s="15" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C104" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-2</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" s="22" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>223</v>
+      </c>
+      <c r="G104" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 참여자 등록 시 시간대가 없는 installDate를 거부하고 저장 형식을 UTC ISO로 통일</t>
+        </is>
+      </c>
+      <c r="H104" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I104" s="16" t="n"/>
+      <c r="J104" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="K104" s="20" t="inlineStr">
+        <is>
           <t>#223</t>
         </is>
       </c>
     </row>
-    <row r="104" outlineLevel="2">
-      <c r="A104" s="9" t="n">
-        <v>103</v>
-      </c>
-      <c r="B104" s="10" t="inlineStr">
+    <row r="105" outlineLevel="1">
+      <c r="A105" s="9" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C104" s="10" t="inlineStr">
+      <c r="C105" s="10" t="inlineStr">
         <is>
           <t>Story 6-3</t>
         </is>
       </c>
-      <c r="D104" s="9" t="n">
+      <c r="D105" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E104" s="11" t="inlineStr">
+      <c r="E105" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F104" s="9" t="n">
+      <c r="F105" s="9" t="n">
         <v>276</v>
       </c>
-      <c r="G104" s="12" t="inlineStr">
+      <c r="G105" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-3: 참가자가 자정 기준 하루 누적 리뷰를 확인할 수 있다</t>
         </is>
       </c>
-      <c r="H104" s="23" t="inlineStr">
+      <c r="H105" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I104" s="10" t="n"/>
-      <c r="J104" s="9" t="n">
+      <c r="I105" s="10" t="n"/>
+      <c r="J105" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K104" s="14" t="inlineStr">
+      <c r="K105" s="14" t="inlineStr">
         <is>
           <t>#276</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1">
-      <c r="A105" s="15" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C105" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-3</t>
-        </is>
-      </c>
-      <c r="D105" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E105" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F105" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="G105" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 세션-종료 트리거를 오늘 누적 계산으로 통합</t>
-        </is>
-      </c>
-      <c r="H105" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I105" s="16" t="n"/>
-      <c r="J105" s="15" t="n">
-        <v>276</v>
-      </c>
-      <c r="K105" s="20" t="inlineStr">
-        <is>
-          <t>#152</t>
         </is>
       </c>
     </row>
@@ -5389,11 +5389,11 @@
         </is>
       </c>
       <c r="F106" s="15" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G106" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 자정 경계 처리 + "어제 돌아보기" 리빌 애니메이션</t>
+          <t xml:space="preserve">        feat: 세션-종료 트리거를 오늘 누적 계산으로 통합</t>
         </is>
       </c>
       <c r="H106" s="19" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="K106" s="20" t="inlineStr">
         <is>
-          <t>#153</t>
+          <t>#152</t>
         </is>
       </c>
     </row>
@@ -5434,11 +5434,11 @@
         </is>
       </c>
       <c r="F107" s="15" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G107" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 리뷰 카드 헤드라인 문구 스코프별 분기</t>
+          <t xml:space="preserve">        feat: 자정 경계 처리 + "어제 돌아보기" 리빌 애니메이션</t>
         </is>
       </c>
       <c r="H107" s="19" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="K107" s="20" t="inlineStr">
         <is>
-          <t>#154</t>
+          <t>#153</t>
         </is>
       </c>
     </row>
@@ -5473,22 +5473,22 @@
       <c r="D108" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E108" s="22" t="inlineStr">
-        <is>
-          <t>Bug</t>
+      <c r="E108" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
         </is>
       </c>
       <c r="F108" s="15" t="n">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        bug: 피드백 생성 완료 직후 날짜 이동 시 "오늘" 탭이 갱신되지 않음</t>
-        </is>
-      </c>
-      <c r="H108" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 리뷰 카드 헤드라인 문구 스코프별 분기</t>
+        </is>
+      </c>
+      <c r="H108" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I108" s="16" t="n"/>
@@ -5497,97 +5497,97 @@
       </c>
       <c r="K108" s="20" t="inlineStr">
         <is>
+          <t>#154</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C109" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-3</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" s="22" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>261</v>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        bug: 피드백 생성 완료 직후 날짜 이동 시 "오늘" 탭이 갱신되지 않음</t>
+        </is>
+      </c>
+      <c r="H109" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I109" s="16" t="n"/>
+      <c r="J109" s="15" t="n">
+        <v>276</v>
+      </c>
+      <c r="K109" s="20" t="inlineStr">
+        <is>
           <t>#261</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="n">
-        <v>108</v>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
+    <row r="110" outlineLevel="1">
+      <c r="A110" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C109" s="10" t="inlineStr">
+      <c r="C110" s="10" t="inlineStr">
         <is>
           <t>Story 6-4</t>
         </is>
       </c>
-      <c r="D109" s="9" t="n">
+      <c r="D110" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E109" s="11" t="inlineStr">
+      <c r="E110" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F109" s="9" t="n">
+      <c r="F110" s="9" t="n">
         <v>277</v>
       </c>
-      <c r="G109" s="12" t="inlineStr">
+      <c r="G110" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-4: 네트워크·인증 오류가 나도 데이터 전송과 참여자 등록이 자동 복구된다</t>
         </is>
       </c>
-      <c r="H109" s="23" t="inlineStr">
+      <c r="H110" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I109" s="10" t="n"/>
-      <c r="J109" s="9" t="n">
+      <c r="I110" s="10" t="n"/>
+      <c r="J110" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K109" s="14" t="inlineStr">
+      <c r="K110" s="14" t="inlineStr">
         <is>
           <t>#277</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1">
-      <c r="A110" s="15" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C110" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-4</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E110" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F110" s="15" t="n">
-        <v>193</v>
-      </c>
-      <c r="G110" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 전송 큐 재시도에 큐 레벨 fail-fast·재진입 가드·타임아웃 도입</t>
-        </is>
-      </c>
-      <c r="H110" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I110" s="16" t="n"/>
-      <c r="J110" s="15" t="n">
-        <v>277</v>
-      </c>
-      <c r="K110" s="20" t="inlineStr">
-        <is>
-          <t>#193</t>
         </is>
       </c>
     </row>
@@ -5614,11 +5614,11 @@
         </is>
       </c>
       <c r="F111" s="15" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G111" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참여자 등록 게이트를 백그라운드에서 자동 복구하고 403 무효화 경로 추가</t>
+          <t xml:space="preserve">        feat: 전송 큐 재시도에 큐 레벨 fail-fast·재진입 가드·타임아웃 도입</t>
         </is>
       </c>
       <c r="H111" s="19" t="inlineStr">
@@ -5632,181 +5632,181 @@
       </c>
       <c r="K111" s="20" t="inlineStr">
         <is>
+          <t>#193</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" outlineLevel="2">
+      <c r="A112" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C112" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-4</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="n">
+        <v>196</v>
+      </c>
+      <c r="G112" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 참여자 등록 게이트를 백그라운드에서 자동 복구하고 403 무효화 경로 추가</t>
+        </is>
+      </c>
+      <c r="H112" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I112" s="16" t="n"/>
+      <c r="J112" s="15" t="n">
+        <v>277</v>
+      </c>
+      <c r="K112" s="20" t="inlineStr">
+        <is>
           <t>#196</t>
         </is>
       </c>
     </row>
-    <row r="112" outlineLevel="2">
-      <c r="A112" s="9" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="10" t="inlineStr">
+    <row r="113" outlineLevel="2">
+      <c r="A113" s="9" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C112" s="10" t="inlineStr">
+      <c r="C113" s="10" t="inlineStr">
         <is>
           <t>Story 6-5</t>
         </is>
       </c>
-      <c r="D112" s="9" t="n">
+      <c r="D113" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E112" s="11" t="inlineStr">
+      <c r="E113" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F112" s="9" t="n">
+      <c r="F113" s="9" t="n">
         <v>278</v>
       </c>
-      <c r="G112" s="12" t="inlineStr">
+      <c r="G113" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-5: 참가자가 오류 발생 시 팝업에서 안내를 볼 수 있다</t>
         </is>
       </c>
-      <c r="H112" s="23" t="inlineStr">
+      <c r="H113" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I112" s="10" t="n"/>
-      <c r="J112" s="9" t="n">
+      <c r="I113" s="10" t="n"/>
+      <c r="J113" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K112" s="14" t="inlineStr">
+      <c r="K113" s="14" t="inlineStr">
         <is>
           <t>#278</t>
         </is>
       </c>
     </row>
-    <row r="113" outlineLevel="2" ht="26.25" customHeight="1">
-      <c r="A113" s="3" t="n">
-        <v>112</v>
-      </c>
-      <c r="B113" s="4" t="inlineStr">
+    <row r="114" outlineLevel="2" ht="26.25" customHeight="1">
+      <c r="A114" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="3" t="n">
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E114" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F113" s="3" t="n">
+      <c r="F114" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="G113" s="6" t="inlineStr">
+      <c r="G114" s="6" t="inlineStr">
         <is>
           <t>Epic 7. 관측 체계 구축 및 운영</t>
         </is>
       </c>
-      <c r="H113" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I113" s="4" t="n"/>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="8" t="inlineStr">
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="n"/>
+      <c r="J114" s="3" t="n"/>
+      <c r="K114" s="8" t="inlineStr">
         <is>
           <t>#202</t>
         </is>
       </c>
     </row>
-    <row r="114" outlineLevel="2">
-      <c r="A114" s="9" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="10" t="inlineStr">
+    <row r="115" outlineLevel="1">
+      <c r="A115" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="10" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C114" s="10" t="inlineStr">
+      <c r="C115" s="10" t="inlineStr">
         <is>
           <t>Story 7-1</t>
         </is>
       </c>
-      <c r="D114" s="9" t="n">
+      <c r="D115" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E114" s="11" t="inlineStr">
+      <c r="E115" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F114" s="9" t="n">
+      <c r="F115" s="9" t="n">
         <v>172</v>
       </c>
-      <c r="G114" s="12" t="inlineStr">
+      <c r="G115" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 7-1: 운영자가 서버·cron·결측 이상을 즉시 알림으로 받을 수 있다(최소 관제 체계(MVM) 구축)</t>
         </is>
       </c>
-      <c r="H114" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I114" s="10" t="n"/>
-      <c r="J114" s="9" t="n">
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I115" s="10" t="n"/>
+      <c r="J115" s="9" t="n">
         <v>202</v>
       </c>
-      <c r="K114" s="14" t="inlineStr">
+      <c r="K115" s="14" t="inlineStr">
         <is>
           <t>#172</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1">
-      <c r="A115" s="15" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C115" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-1</t>
-        </is>
-      </c>
-      <c r="D115" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E115" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F115" s="15" t="n">
-        <v>192</v>
-      </c>
-      <c r="G115" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 접근 로그에 실제 API 경로 기록 및 error-monitor 알림을 /api/* 4xx로 한정</t>
-        </is>
-      </c>
-      <c r="H115" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I115" s="16" t="n"/>
-      <c r="J115" s="15" t="n">
-        <v>172</v>
-      </c>
-      <c r="K115" s="20" t="inlineStr">
-        <is>
-          <t>#192</t>
         </is>
       </c>
     </row>
@@ -5833,11 +5833,11 @@
         </is>
       </c>
       <c r="F116" s="15" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G116" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog Monitor로 세션 API 지연·Agent 무응답 알림 추가</t>
+          <t xml:space="preserve">        feat: 접근 로그에 실제 API 경로 기록 및 error-monitor 알림을 /api/* 4xx로 한정</t>
         </is>
       </c>
       <c r="H116" s="19" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="K116" s="20" t="inlineStr">
         <is>
-          <t>#204</t>
+          <t>#192</t>
         </is>
       </c>
     </row>
@@ -5878,11 +5878,11 @@
         </is>
       </c>
       <c r="F117" s="15" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: LLM fallback 비율·Gemini 응답 시간을 Datadog 커스텀 메트릭으로 추세 감시</t>
+          <t xml:space="preserve">        feat: Datadog Monitor로 세션 API 지연·Agent 무응답 알림 추가</t>
         </is>
       </c>
       <c r="H117" s="19" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="K117" s="20" t="inlineStr">
         <is>
-          <t>#205</t>
+          <t>#204</t>
         </is>
       </c>
     </row>
@@ -5923,11 +5923,11 @@
         </is>
       </c>
       <c r="F118" s="15" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참가자별 결측 감지 cron 가동과 결측 의심 시 인원수 알림</t>
+          <t xml:space="preserve">        feat: LLM fallback 비율·Gemini 응답 시간을 Datadog 커스텀 메트릭으로 추세 감시</t>
         </is>
       </c>
       <c r="H118" s="19" t="inlineStr">
@@ -5941,101 +5941,101 @@
       </c>
       <c r="K118" s="20" t="inlineStr">
         <is>
+          <t>#205</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" outlineLevel="2">
+      <c r="A119" s="15" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-1</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>206</v>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 참가자별 결측 감지 cron 가동과 결측 의심 시 인원수 알림</t>
+        </is>
+      </c>
+      <c r="H119" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I119" s="16" t="n"/>
+      <c r="J119" s="15" t="n">
+        <v>172</v>
+      </c>
+      <c r="K119" s="20" t="inlineStr">
+        <is>
           <t>#206</t>
         </is>
       </c>
     </row>
-    <row r="119" outlineLevel="2">
-      <c r="A119" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
+    <row r="120" outlineLevel="2">
+      <c r="A120" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>Story 7-2</t>
         </is>
       </c>
-      <c r="D119" s="9" t="n">
+      <c r="D120" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E119" s="11" t="inlineStr">
+      <c r="E120" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F119" s="9" t="n">
+      <c r="F120" s="9" t="n">
         <v>279</v>
       </c>
-      <c r="G119" s="12" t="inlineStr">
+      <c r="G120" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 7-2: 운영자가 오류 원인을 로그·트레이스로 추적할 수 있다</t>
         </is>
       </c>
-      <c r="H119" s="23" t="inlineStr">
+      <c r="H120" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I119" s="10" t="n"/>
-      <c r="J119" s="9" t="n">
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="9" t="n">
         <v>202</v>
       </c>
-      <c r="K119" s="14" t="inlineStr">
+      <c r="K120" s="14" t="inlineStr">
         <is>
           <t>#279</t>
         </is>
       </c>
     </row>
-    <row r="120" outlineLevel="2" ht="25.5" customHeight="1">
-      <c r="A120" s="15" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E120" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="n">
-        <v>203</v>
-      </c>
-      <c r="G120" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 확장 프로그램 오류를 연구 서버로 원격 수집</t>
-        </is>
-      </c>
-      <c r="H120" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I120" s="16" t="n"/>
-      <c r="J120" s="15" t="n">
-        <v>279</v>
-      </c>
-      <c r="K120" s="20" t="inlineStr">
-        <is>
-          <t>#203</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" outlineLevel="2">
+    <row r="121" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="A121" s="15" t="n">
         <v>120</v>
       </c>
@@ -6058,11 +6058,11 @@
         </is>
       </c>
       <c r="F121" s="15" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog에서 가명 사용자 ID(anonymousId)로 로그·요청을 조회할 수 있게 UUID 마스킹 해제</t>
+          <t xml:space="preserve">        feat: 확장 프로그램 오류를 연구 서버로 원격 수집</t>
         </is>
       </c>
       <c r="H121" s="19" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="K121" s="20" t="inlineStr">
         <is>
-          <t>#225</t>
+          <t>#203</t>
         </is>
       </c>
     </row>
@@ -6103,11 +6103,11 @@
         </is>
       </c>
       <c r="F122" s="15" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G122" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 서버 예외의 스택 트레이스를 확인할 수 있게 하기</t>
+          <t xml:space="preserve">        feat: Datadog에서 가명 사용자 ID(anonymousId)로 로그·요청을 조회할 수 있게 UUID 마스킹 해제</t>
         </is>
       </c>
       <c r="H122" s="19" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="K122" s="20" t="inlineStr">
         <is>
-          <t>#226</t>
+          <t>#225</t>
         </is>
       </c>
     </row>
@@ -6148,11 +6148,11 @@
         </is>
       </c>
       <c r="F123" s="15" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G123" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 서버 로그 줄에 trace ID를 넣어 Datadog Logs와 APM trace를 연결</t>
+          <t xml:space="preserve">        feat: 서버 예외의 스택 트레이스를 확인할 수 있게 하기</t>
         </is>
       </c>
       <c r="H123" s="19" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="K123" s="20" t="inlineStr">
         <is>
-          <t>#227</t>
+          <t>#226</t>
         </is>
       </c>
     </row>
@@ -6193,11 +6193,11 @@
         </is>
       </c>
       <c r="F124" s="15" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G124" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 지문·anonymousId·참여 코드로 참여자 상태를 조회하는 읽기 전용 스크립트</t>
+          <t xml:space="preserve">        feat: 서버 로그 줄에 trace ID를 넣어 Datadog Logs와 APM trace를 연결</t>
         </is>
       </c>
       <c r="H124" s="19" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="K124" s="20" t="inlineStr">
         <is>
-          <t>#228</t>
+          <t>#227</t>
         </is>
       </c>
     </row>
@@ -6238,11 +6238,11 @@
         </is>
       </c>
       <c r="F125" s="15" t="n">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="G125" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: Datadog Agent 설치 및 Log Management 연동</t>
+          <t xml:space="preserve">        feat: 지문·anonymousId·참여 코드로 참여자 상태를 조회하는 읽기 전용 스크립트</t>
         </is>
       </c>
       <c r="H125" s="19" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="K125" s="20" t="inlineStr">
         <is>
-          <t>#267</t>
+          <t>#228</t>
         </is>
       </c>
     </row>
@@ -6283,11 +6283,11 @@
         </is>
       </c>
       <c r="F126" s="15" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G126" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog APM(dd-trace) 계측 도입</t>
+          <t xml:space="preserve">        chore: Datadog Agent 설치 및 Log Management 연동</t>
         </is>
       </c>
       <c r="H126" s="19" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="K126" s="20" t="inlineStr">
         <is>
-          <t>#268</t>
+          <t>#267</t>
         </is>
       </c>
     </row>
@@ -6314,21 +6314,25 @@
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C127" s="16" t="n"/>
+      <c r="C127" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-2</t>
+        </is>
+      </c>
       <c r="D127" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E127" s="22" t="inlineStr">
-        <is>
-          <t>Bug</t>
+        <v>3</v>
+      </c>
+      <c r="E127" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
         </is>
       </c>
       <c r="F127" s="15" t="n">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    fix: 본문 필드가 문자열이 아닐 때 서버가 500을 반환하는 문제</t>
+          <t xml:space="preserve">        feat: Datadog APM(dd-trace) 계측 도입</t>
         </is>
       </c>
       <c r="H127" s="19" t="inlineStr">
@@ -6338,140 +6342,136 @@
       </c>
       <c r="I127" s="16" t="n"/>
       <c r="J127" s="15" t="n">
+        <v>279</v>
+      </c>
+      <c r="K127" s="20" t="inlineStr">
+        <is>
+          <t>#268</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" outlineLevel="2">
+      <c r="A128" s="15" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C128" s="16" t="n"/>
+      <c r="D128" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E128" s="22" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F128" s="15" t="n">
+        <v>232</v>
+      </c>
+      <c r="G128" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    fix: 본문 필드가 문자열이 아닐 때 서버가 500을 반환하는 문제</t>
+        </is>
+      </c>
+      <c r="H128" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I128" s="16" t="n"/>
+      <c r="J128" s="15" t="n">
         <v>202</v>
       </c>
-      <c r="K127" s="20" t="inlineStr">
+      <c r="K128" s="20" t="inlineStr">
         <is>
           <t>#232</t>
         </is>
       </c>
     </row>
-    <row r="128" outlineLevel="2">
-      <c r="A128" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="4" t="inlineStr">
+    <row r="129" outlineLevel="1">
+      <c r="A129" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C128" s="4" t="n"/>
-      <c r="D128" s="3" t="n">
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F128" s="3" t="n">
+      <c r="F129" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="G128" s="6" t="inlineStr">
+      <c r="G129" s="6" t="inlineStr">
         <is>
           <t>Epic 8. 본 연구 착수 전 IRB 정합성 확보 및 시스템 정비</t>
         </is>
       </c>
-      <c r="H128" s="25" t="inlineStr">
+      <c r="H129" s="25" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I128" s="4" t="n"/>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="8" t="inlineStr">
+      <c r="I129" s="4" t="n"/>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="8" t="inlineStr">
         <is>
           <t>#207</t>
         </is>
       </c>
     </row>
-    <row r="129" outlineLevel="1">
-      <c r="A129" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="10" t="inlineStr">
+    <row r="130" outlineLevel="2">
+      <c r="A130" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C129" s="10" t="inlineStr">
+      <c r="C130" s="10" t="inlineStr">
         <is>
           <t>Story 8-1</t>
         </is>
       </c>
-      <c r="D129" s="9" t="n">
+      <c r="D130" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E129" s="11" t="inlineStr">
+      <c r="E130" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F129" s="9" t="n">
+      <c r="F130" s="9" t="n">
         <v>280</v>
       </c>
-      <c r="G129" s="12" t="inlineStr">
+      <c r="G130" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-1: 연구 기간이 끝나면 수집·전송이 자동으로 멈추고 참가자에게 안내된다</t>
         </is>
       </c>
-      <c r="H129" s="23" t="inlineStr">
+      <c r="H130" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I129" s="10" t="n"/>
-      <c r="J129" s="9" t="n">
+      <c r="I130" s="10" t="n"/>
+      <c r="J130" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K129" s="14" t="inlineStr">
+      <c r="K130" s="14" t="inlineStr">
         <is>
           <t>#280</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" outlineLevel="2">
-      <c r="A130" s="15" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="16" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C130" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-1</t>
-        </is>
-      </c>
-      <c r="D130" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E130" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F130" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="G130" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 연구 종료 후 수집·생성 중단 + "오늘" 탭 마지막 날짜 고정</t>
-        </is>
-      </c>
-      <c r="H130" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I130" s="16" t="n"/>
-      <c r="J130" s="15" t="n">
-        <v>280</v>
-      </c>
-      <c r="K130" s="20" t="inlineStr">
-        <is>
-          <t>#160</t>
         </is>
       </c>
     </row>
@@ -6498,11 +6498,11 @@
         </is>
       </c>
       <c r="F131" s="15" t="n">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 기간 종료 시 확장 프로그램 수집·전송 자동 중단 및 제거 안내</t>
+          <t xml:space="preserve">        feat: 연구 종료 후 수집·생성 중단 + "오늘" 탭 마지막 날짜 고정</t>
         </is>
       </c>
       <c r="H131" s="19" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="K131" s="20" t="inlineStr">
         <is>
-          <t>#197</t>
+          <t>#160</t>
         </is>
       </c>
     </row>
@@ -6543,11 +6543,11 @@
         </is>
       </c>
       <c r="F132" s="15" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 기간에 따라 달라지는 문구를 상수에서 생성하고 기간 상수 일치를 테스트로 고정</t>
+          <t xml:space="preserve">        feat: 연구 기간 종료 시 확장 프로그램 수집·전송 자동 중단 및 제거 안내</t>
         </is>
       </c>
       <c r="H132" s="19" t="inlineStr">
@@ -6561,191 +6561,191 @@
       </c>
       <c r="K132" s="20" t="inlineStr">
         <is>
+          <t>#197</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" outlineLevel="2">
+      <c r="A133" s="15" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C133" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-1</t>
+        </is>
+      </c>
+      <c r="D133" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E133" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F133" s="15" t="n">
+        <v>210</v>
+      </c>
+      <c r="G133" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 연구 기간에 따라 달라지는 문구를 상수에서 생성하고 기간 상수 일치를 테스트로 고정</t>
+        </is>
+      </c>
+      <c r="H133" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I133" s="16" t="n"/>
+      <c r="J133" s="15" t="n">
+        <v>280</v>
+      </c>
+      <c r="K133" s="20" t="inlineStr">
+        <is>
           <t>#210</t>
         </is>
       </c>
     </row>
-    <row r="133" outlineLevel="2">
-      <c r="A133" s="9" t="n">
-        <v>132</v>
-      </c>
-      <c r="B133" s="10" t="inlineStr">
+    <row r="134" outlineLevel="2">
+      <c r="A134" s="9" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C133" s="10" t="inlineStr">
+      <c r="C134" s="10" t="inlineStr">
         <is>
           <t>Story 8-2</t>
         </is>
       </c>
-      <c r="D133" s="9" t="n">
+      <c r="D134" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E133" s="11" t="inlineStr">
+      <c r="E134" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F133" s="9" t="n">
+      <c r="F134" s="9" t="n">
         <v>281</v>
       </c>
-      <c r="G133" s="12" t="inlineStr">
+      <c r="G134" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-2: 참가자에게 집단(실험/대조) 정보가 노출되지 않는다</t>
         </is>
       </c>
-      <c r="H133" s="23" t="inlineStr">
+      <c r="H134" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I133" s="10" t="n"/>
-      <c r="J133" s="9" t="n">
+      <c r="I134" s="10" t="n"/>
+      <c r="J134" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K133" s="14" t="inlineStr">
+      <c r="K134" s="14" t="inlineStr">
         <is>
           <t>#281</t>
         </is>
       </c>
     </row>
-    <row r="134" outlineLevel="2">
-      <c r="A134" s="15" t="n">
-        <v>133</v>
-      </c>
-      <c r="B134" s="16" t="inlineStr">
+    <row r="135" outlineLevel="2">
+      <c r="A135" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="16" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C134" s="16" t="inlineStr">
+      <c r="C135" s="16" t="inlineStr">
         <is>
           <t>Story 8-2</t>
         </is>
       </c>
-      <c r="D134" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E134" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F134" s="15" t="n">
+      <c r="D135" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E135" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F135" s="15" t="n">
         <v>209</v>
       </c>
-      <c r="G134" s="18" t="inlineStr">
+      <c r="G135" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat: 참여코드에서 집단 표식 제거</t>
         </is>
       </c>
-      <c r="H134" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I134" s="16" t="n"/>
-      <c r="J134" s="15" t="n">
+      <c r="H135" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I135" s="16" t="n"/>
+      <c r="J135" s="15" t="n">
         <v>281</v>
       </c>
-      <c r="K134" s="20" t="inlineStr">
+      <c r="K135" s="20" t="inlineStr">
         <is>
           <t>#209</t>
         </is>
       </c>
     </row>
-    <row r="135" outlineLevel="2">
-      <c r="A135" s="9" t="n">
-        <v>134</v>
-      </c>
-      <c r="B135" s="10" t="inlineStr">
+    <row r="136" outlineLevel="2">
+      <c r="A136" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C136" s="10" t="inlineStr">
         <is>
           <t>Story 8-3</t>
         </is>
       </c>
-      <c r="D135" s="9" t="n">
+      <c r="D136" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E135" s="11" t="inlineStr">
+      <c r="E136" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F135" s="9" t="n">
+      <c r="F136" s="9" t="n">
         <v>218</v>
       </c>
-      <c r="G135" s="12" t="inlineStr">
+      <c r="G136" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-3: 화면·피드백·분석의 시청 집계 기준을 유효 시청·시청 시간으로 통일한다</t>
         </is>
       </c>
-      <c r="H135" s="23" t="inlineStr">
+      <c r="H136" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I135" s="10" t="n"/>
-      <c r="J135" s="9" t="n">
+      <c r="I136" s="10" t="n"/>
+      <c r="J136" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K135" s="14" t="inlineStr">
+      <c r="K136" s="14" t="inlineStr">
         <is>
           <t>#218</t>
         </is>
       </c>
     </row>
-    <row r="136" outlineLevel="2" ht="25.5" customHeight="1">
-      <c r="A136" s="15" t="n">
-        <v>135</v>
-      </c>
-      <c r="B136" s="16" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C136" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
-      <c r="D136" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E136" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F136" s="15" t="n">
-        <v>211</v>
-      </c>
-      <c r="G136" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 기간별 리뷰 첫 줄에 분야별 비중과 지난 구간 대비 변화를 사실 문장으로 추가</t>
-        </is>
-      </c>
-      <c r="H136" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I136" s="16" t="n"/>
-      <c r="J136" s="15" t="n">
-        <v>218</v>
-      </c>
-      <c r="K136" s="20" t="inlineStr">
-        <is>
-          <t>#211</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" outlineLevel="2">
+    <row r="137" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="A137" s="15" t="n">
         <v>136</v>
       </c>
@@ -6768,11 +6768,11 @@
         </is>
       </c>
       <c r="F137" s="15" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 팝업 화면 숫자를 서버 집계 기준으로 통일하고 기간별 탭을 분야별 시청 시간 꺾은선으로 교체</t>
+          <t xml:space="preserve">        feat: 기간별 리뷰 첫 줄에 분야별 비중과 지난 구간 대비 변화를 사실 문장으로 추가</t>
         </is>
       </c>
       <c r="H137" s="19" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="K137" s="20" t="inlineStr">
         <is>
-          <t>#217</t>
+          <t>#211</t>
         </is>
       </c>
     </row>
@@ -6813,16 +6813,16 @@
         </is>
       </c>
       <c r="F138" s="15" t="n">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="G138" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        docs: 시청 집계 기준·화면 지표 결정을 기록하고 사전등록 문서에 반영</t>
-        </is>
-      </c>
-      <c r="H138" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 팝업 화면 숫자를 서버 집계 기준으로 통일하고 기간별 탭을 분야별 시청 시간 꺾은선으로 교체</t>
+        </is>
+      </c>
+      <c r="H138" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I138" s="16" t="n"/>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="K138" s="20" t="inlineStr">
         <is>
-          <t>#253</t>
+          <t>#217</t>
         </is>
       </c>
     </row>
@@ -6858,16 +6858,16 @@
         </is>
       </c>
       <c r="F139" s="15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G139" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 집계를 원본 영상 데이터에서 유효 시청·시청 시간 기준으로 계산</t>
-        </is>
-      </c>
-      <c r="H139" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t xml:space="preserve">        docs: 시청 집계 기준·화면 지표 결정을 기록하고 사전등록 문서에 반영</t>
+        </is>
+      </c>
+      <c r="H139" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="I139" s="16" t="n"/>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="K139" s="20" t="inlineStr">
         <is>
-          <t>#254</t>
+          <t>#253</t>
         </is>
       </c>
     </row>
@@ -6903,11 +6903,11 @@
         </is>
       </c>
       <c r="F140" s="15" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G140" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 리뷰의 LLM 입력과 대체 문구를 유효 시청 기준으로 정렬</t>
+          <t xml:space="preserve">        feat: 오늘·기간 집계를 원본 영상 데이터에서 유효 시청·시청 시간 기준으로 계산</t>
         </is>
       </c>
       <c r="H140" s="19" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="K140" s="20" t="inlineStr">
         <is>
-          <t>#255</t>
+          <t>#254</t>
         </is>
       </c>
     </row>
@@ -6948,11 +6948,11 @@
         </is>
       </c>
       <c r="F141" s="15" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G141" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘 리뷰를 유효 영상이 늘었을 때만 최소 간격을 두고 생성</t>
+          <t xml:space="preserve">        feat: 오늘·기간 리뷰의 LLM 입력과 대체 문구를 유효 시청 기준으로 정렬</t>
         </is>
       </c>
       <c r="H141" s="19" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="K141" s="20" t="inlineStr">
         <is>
-          <t>#256</t>
+          <t>#255</t>
         </is>
       </c>
     </row>
@@ -6993,16 +6993,16 @@
         </is>
       </c>
       <c r="F142" s="15" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 기간별 리뷰 카테고리 분포 카드</t>
-        </is>
-      </c>
-      <c r="H142" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 오늘 리뷰를 유효 영상이 늘었을 때만 최소 간격을 두고 생성</t>
+        </is>
+      </c>
+      <c r="H142" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I142" s="16" t="n"/>
@@ -7011,52 +7011,52 @@
       </c>
       <c r="K142" s="20" t="inlineStr">
         <is>
+          <t>#256</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" outlineLevel="2">
+      <c r="A143" s="15" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C143" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D143" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E143" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F143" s="15" t="n">
+        <v>262</v>
+      </c>
+      <c r="G143" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 오늘·기간 탭에서 제목을 먼저 보이고 시청 현황(개수) 표시를 정리</t>
+        </is>
+      </c>
+      <c r="H143" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I143" s="16" t="n"/>
+      <c r="J143" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K143" s="20" t="inlineStr">
+        <is>
           <t>#262</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" outlineLevel="2">
-      <c r="A143" s="9" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="10" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>Story 8-4</t>
-        </is>
-      </c>
-      <c r="D143" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F143" s="9" t="n">
-        <v>282</v>
-      </c>
-      <c r="G143" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 8-4: IRB 변경심의를 신청하고 승인받는다</t>
-        </is>
-      </c>
-      <c r="H143" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I143" s="10" t="n"/>
-      <c r="J143" s="9" t="n">
-        <v>207</v>
-      </c>
-      <c r="K143" s="14" t="inlineStr">
-        <is>
-          <t>#282</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C144" s="16" t="inlineStr">
         <is>
-          <t>Story 8-4</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D144" s="15" t="n">
@@ -7079,68 +7079,74 @@
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F144" s="15" t="n">
-        <v>213</v>
+        <v>302</v>
       </c>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        docs: IRB 변경심의 신청</t>
-        </is>
-      </c>
-      <c r="H144" s="24" t="inlineStr">
+          <t xml:space="preserve">        fix: 탭을 닫을 때 마지막 영상의 시청 시간이 유실돼 "확인 중"으로 영구히 남음</t>
+        </is>
+      </c>
+      <c r="H144" s="19" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
       <c r="I144" s="16" t="n"/>
       <c r="J144" s="15" t="n">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="K144" s="20" t="inlineStr">
         <is>
-          <t>#213</t>
+          <t>#302</t>
         </is>
       </c>
     </row>
     <row r="145" outlineLevel="2">
-      <c r="A145" s="3" t="n">
+      <c r="A145" s="15" t="n">
         <v>144</v>
       </c>
-      <c r="B145" s="4" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C145" s="4" t="n"/>
-      <c r="D145" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E145" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="G145" s="6" t="inlineStr">
-        <is>
-          <t>Epic 9. 테스트 및 품질 보강</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I145" s="4" t="n"/>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="8" t="inlineStr">
-        <is>
-          <t>#208</t>
+      <c r="B145" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C145" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D145" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E145" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F145" s="15" t="n">
+        <v>303</v>
+      </c>
+      <c r="G145" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: Shorts 시청 시간이 측정되지 않고 0초로 기록돼 유효 시청에서 빠짐</t>
+        </is>
+      </c>
+      <c r="H145" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I145" s="16" t="n"/>
+      <c r="J145" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K145" s="20" t="inlineStr">
+        <is>
+          <t>#303</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7156,12 @@
       </c>
       <c r="B146" s="10" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Story 9-1</t>
+          <t>Story 8-4</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
@@ -7167,11 +7173,11 @@
         </is>
       </c>
       <c r="F146" s="9" t="n">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 9-1: 위험 기반 테스트로 연구 데이터 오염 위험을 제거한다</t>
+          <t xml:space="preserve">    Story 8-4: IRB 변경심의를 신청하고 승인받는다</t>
         </is>
       </c>
       <c r="H146" s="23" t="inlineStr">
@@ -7181,11 +7187,11 @@
       </c>
       <c r="I146" s="10" t="n"/>
       <c r="J146" s="9" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>#283</t>
+          <t>#282</t>
         </is>
       </c>
     </row>
@@ -7195,12 +7201,12 @@
       </c>
       <c r="B147" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C147" s="16" t="inlineStr">
         <is>
-          <t>Story 9-1</t>
+          <t>Story 8-4</t>
         </is>
       </c>
       <c r="D147" s="15" t="n">
@@ -7212,115 +7218,109 @@
         </is>
       </c>
       <c r="F147" s="15" t="n">
-        <v>165</v>
+        <v>213</v>
       </c>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 위험 기반 테스트 보강 및 커버리지 측정 도입</t>
-        </is>
-      </c>
-      <c r="H147" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t xml:space="preserve">        docs: IRB 변경심의 신청</t>
+        </is>
+      </c>
+      <c r="H147" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="I147" s="16" t="n"/>
       <c r="J147" s="15" t="n">
+        <v>282</v>
+      </c>
+      <c r="K147" s="20" t="inlineStr">
+        <is>
+          <t>#213</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" outlineLevel="2">
+      <c r="A148" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="G148" s="6" t="inlineStr">
+        <is>
+          <t>Epic 9. 테스트 및 품질 보강</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="n"/>
+      <c r="J148" s="3" t="n"/>
+      <c r="K148" s="8" t="inlineStr">
+        <is>
+          <t>#208</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" outlineLevel="2">
+      <c r="A149" s="9" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="10" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="inlineStr">
+        <is>
+          <t>Story 9-1</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F149" s="9" t="n">
         <v>283</v>
       </c>
-      <c r="K147" s="20" t="inlineStr">
-        <is>
-          <t>#165</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" outlineLevel="2">
-      <c r="A148" s="15" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C148" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-1</t>
-        </is>
-      </c>
-      <c r="D148" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E148" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F148" s="15" t="n">
-        <v>167</v>
-      </c>
-      <c r="G148" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 위험 기반 테스트 4개 항목 구현 및 리팩터링</t>
-        </is>
-      </c>
-      <c r="H148" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I148" s="16" t="n"/>
-      <c r="J148" s="15" t="n">
-        <v>283</v>
-      </c>
-      <c r="K148" s="20" t="inlineStr">
-        <is>
-          <t>#167</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" outlineLevel="2">
-      <c r="A149" s="15" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C149" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-1</t>
-        </is>
-      </c>
-      <c r="D149" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E149" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F149" s="15" t="n">
-        <v>169</v>
-      </c>
-      <c r="G149" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 테스트 공백 보완 및 진행 기록</t>
-        </is>
-      </c>
-      <c r="H149" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I149" s="16" t="n"/>
-      <c r="J149" s="15" t="n">
-        <v>283</v>
-      </c>
-      <c r="K149" s="20" t="inlineStr">
-        <is>
-          <t>#169</t>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-1: 위험 기반 테스트로 연구 데이터 오염 위험을 제거한다</t>
+        </is>
+      </c>
+      <c r="H149" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I149" s="10" t="n"/>
+      <c r="J149" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K149" s="14" t="inlineStr">
+        <is>
+          <t>#283</t>
         </is>
       </c>
     </row>
@@ -7343,15 +7343,15 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F150" s="15" t="n">
-        <v>294</v>
+        <v>165</v>
       </c>
       <c r="G150" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 클라이언트가 보내는 시각도 시간대가 없으면 거부하고 UTC ISO로 정규화</t>
+          <t xml:space="preserve">        test: 위험 기반 테스트 보강 및 커버리지 측정 도입</t>
         </is>
       </c>
       <c r="H150" s="19" t="inlineStr">
@@ -7359,62 +7359,58 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>#295</t>
-        </is>
-      </c>
+      <c r="I150" s="16" t="n"/>
       <c r="J150" s="15" t="n">
         <v>283</v>
       </c>
       <c r="K150" s="20" t="inlineStr">
         <is>
-          <t>#294</t>
+          <t>#165</t>
         </is>
       </c>
     </row>
     <row r="151" outlineLevel="1">
-      <c r="A151" s="9" t="n">
+      <c r="A151" s="15" t="n">
         <v>150</v>
       </c>
-      <c r="B151" s="10" t="inlineStr">
+      <c r="B151" s="16" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C151" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-2</t>
-        </is>
-      </c>
-      <c r="D151" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E151" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F151" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="G151" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-2: 핵심 API 경로가 실제 라우터 기준 통합 테스트로 보호된다</t>
-        </is>
-      </c>
-      <c r="H151" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I151" s="10" t="n"/>
-      <c r="J151" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K151" s="14" t="inlineStr">
-        <is>
-          <t>#285</t>
+      <c r="C151" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-1</t>
+        </is>
+      </c>
+      <c r="D151" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E151" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F151" s="15" t="n">
+        <v>167</v>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 위험 기반 테스트 4개 항목 구현 및 리팩터링</t>
+        </is>
+      </c>
+      <c r="H151" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I151" s="16" t="n"/>
+      <c r="J151" s="15" t="n">
+        <v>283</v>
+      </c>
+      <c r="K151" s="20" t="inlineStr">
+        <is>
+          <t>#167</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7425,7 @@
       </c>
       <c r="C152" s="16" t="inlineStr">
         <is>
-          <t>Story 9-2</t>
+          <t>Story 9-1</t>
         </is>
       </c>
       <c r="D152" s="15" t="n">
@@ -7441,11 +7437,11 @@
         </is>
       </c>
       <c r="F152" s="15" t="n">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="G152" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 종료 게이트 API 실제 라우터 배선 테스트</t>
+          <t xml:space="preserve">        test: 테스트 공백 보완 및 진행 기록</t>
         </is>
       </c>
       <c r="H152" s="19" t="inlineStr">
@@ -7455,11 +7451,11 @@
       </c>
       <c r="I152" s="16" t="n"/>
       <c r="J152" s="15" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="K152" s="20" t="inlineStr">
         <is>
-          <t>#234</t>
+          <t>#169</t>
         </is>
       </c>
     </row>
@@ -7474,82 +7470,86 @@
       </c>
       <c r="C153" s="16" t="inlineStr">
         <is>
+          <t>Story 9-1</t>
+        </is>
+      </c>
+      <c r="D153" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E153" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F153" s="15" t="n">
+        <v>294</v>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 클라이언트가 보내는 시각도 시간대가 없으면 거부하고 UTC ISO로 정규화</t>
+        </is>
+      </c>
+      <c r="H153" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>#295</t>
+        </is>
+      </c>
+      <c r="J153" s="15" t="n">
+        <v>283</v>
+      </c>
+      <c r="K153" s="20" t="inlineStr">
+        <is>
+          <t>#294</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" outlineLevel="2">
+      <c r="A154" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="inlineStr">
+        <is>
           <t>Story 9-2</t>
         </is>
       </c>
-      <c r="D153" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E153" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F153" s="15" t="n">
-        <v>235</v>
-      </c>
-      <c r="G153" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: CORS 허용 출처 규칙 회귀 테스트</t>
-        </is>
-      </c>
-      <c r="H153" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I153" s="16" t="n"/>
-      <c r="J153" s="15" t="n">
+      <c r="D154" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E154" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F154" s="9" t="n">
         <v>285</v>
       </c>
-      <c r="K153" s="20" t="inlineStr">
-        <is>
-          <t>#235</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" outlineLevel="2">
-      <c r="A154" s="15" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C154" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-2</t>
-        </is>
-      </c>
-      <c r="D154" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E154" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F154" s="15" t="n">
-        <v>236</v>
-      </c>
-      <c r="G154" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: cron 스크립트(백업·모니터링) 테스트 가능 구조 및 테스트</t>
-        </is>
-      </c>
-      <c r="H154" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I154" s="16" t="n"/>
-      <c r="J154" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="K154" s="20" t="inlineStr">
-        <is>
-          <t>#236</t>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-2: 핵심 API 경로가 실제 라우터 기준 통합 테스트로 보호된다</t>
+        </is>
+      </c>
+      <c r="H154" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I154" s="10" t="n"/>
+      <c r="J154" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K154" s="14" t="inlineStr">
+        <is>
+          <t>#285</t>
         </is>
       </c>
     </row>
@@ -7576,11 +7576,11 @@
         </is>
       </c>
       <c r="F155" s="15" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="G155" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 연구 종료 게이트 통합 테스트를 실제 라우터로 전환</t>
+          <t xml:space="preserve">        test: 종료 게이트 API 실제 라우터 배선 테스트</t>
         </is>
       </c>
       <c r="H155" s="19" t="inlineStr">
@@ -7594,52 +7594,52 @@
       </c>
       <c r="K155" s="20" t="inlineStr">
         <is>
-          <t>#240</t>
+          <t>#234</t>
         </is>
       </c>
     </row>
     <row r="156" outlineLevel="2">
-      <c r="A156" s="9" t="n">
+      <c r="A156" s="15" t="n">
         <v>155</v>
       </c>
-      <c r="B156" s="10" t="inlineStr">
+      <c r="B156" s="16" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C156" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D156" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E156" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F156" s="9" t="n">
-        <v>286</v>
-      </c>
-      <c r="G156" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-3: 커버리지를 정확히 측정하고 목표치를 유지한다</t>
-        </is>
-      </c>
-      <c r="H156" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I156" s="10" t="n"/>
-      <c r="J156" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K156" s="14" t="inlineStr">
-        <is>
-          <t>#286</t>
+      <c r="C156" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D156" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E156" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F156" s="15" t="n">
+        <v>235</v>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: CORS 허용 출처 규칙 회귀 테스트</t>
+        </is>
+      </c>
+      <c r="H156" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I156" s="16" t="n"/>
+      <c r="J156" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K156" s="20" t="inlineStr">
+        <is>
+          <t>#235</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="C157" s="16" t="inlineStr">
         <is>
-          <t>Story 9-3</t>
+          <t>Story 9-2</t>
         </is>
       </c>
       <c r="D157" s="15" t="n">
@@ -7666,11 +7666,11 @@
         </is>
       </c>
       <c r="F157" s="15" t="n">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="G157" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 커버리지 측정 보정 및 CI 정비</t>
+          <t xml:space="preserve">        test: cron 스크립트(백업·모니터링) 테스트 가능 구조 및 테스트</t>
         </is>
       </c>
       <c r="H157" s="19" t="inlineStr">
@@ -7680,11 +7680,11 @@
       </c>
       <c r="I157" s="16" t="n"/>
       <c r="J157" s="15" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K157" s="20" t="inlineStr">
         <is>
-          <t>#233</t>
+          <t>#236</t>
         </is>
       </c>
     </row>
@@ -7699,90 +7699,82 @@
       </c>
       <c r="C158" s="16" t="inlineStr">
         <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F158" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 연구 종료 게이트 통합 테스트를 실제 라우터로 전환</t>
+        </is>
+      </c>
+      <c r="H158" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I158" s="16" t="n"/>
+      <c r="J158" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K158" s="20" t="inlineStr">
+        <is>
+          <t>#240</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" outlineLevel="2">
+      <c r="A159" s="9" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="10" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C159" s="10" t="inlineStr">
+        <is>
           <t>Story 9-3</t>
         </is>
       </c>
-      <c r="D158" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E158" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F158" s="15" t="n">
-        <v>259</v>
-      </c>
-      <c r="G158" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: content.js를 커버리지로 측정되게 하고 80% 이상으로 보강</t>
-        </is>
-      </c>
-      <c r="H158" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I158" s="16" t="inlineStr">
-        <is>
-          <t>#266</t>
-        </is>
-      </c>
-      <c r="J158" s="15" t="n">
+      <c r="D159" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F159" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="K158" s="20" t="inlineStr">
-        <is>
-          <t>#259</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" outlineLevel="2">
-      <c r="A159" s="15" t="n">
-        <v>158</v>
-      </c>
-      <c r="B159" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C159" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D159" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E159" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F159" s="15" t="n">
-        <v>265</v>
-      </c>
-      <c r="G159" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 팝업 파일을 커버리지로 측정되게 전환</t>
-        </is>
-      </c>
-      <c r="H159" s="24" t="inlineStr">
+      <c r="G159" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-3: 커버리지를 정확히 측정하고 목표치를 유지한다</t>
+        </is>
+      </c>
+      <c r="H159" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I159" s="16" t="inlineStr">
-        <is>
-          <t>#284</t>
-        </is>
-      </c>
-      <c r="J159" s="15" t="n">
-        <v>286</v>
-      </c>
-      <c r="K159" s="20" t="inlineStr">
-        <is>
-          <t>#265</t>
+      <c r="I159" s="10" t="n"/>
+      <c r="J159" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K159" s="14" t="inlineStr">
+        <is>
+          <t>#286</t>
         </is>
       </c>
     </row>
@@ -7809,29 +7801,25 @@
         </is>
       </c>
       <c r="F160" s="15" t="n">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="G160" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 앱 조립을 create-app.js로 분리하고 실제 조립된 앱(미들웨어 순서·라우터 마운트)을 테스트로 검증</t>
-        </is>
-      </c>
-      <c r="H160" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I160" s="16" t="inlineStr">
-        <is>
-          <t>#298</t>
-        </is>
-      </c>
+          <t xml:space="preserve">        test: 커버리지 측정 보정 및 CI 정비</t>
+        </is>
+      </c>
+      <c r="H160" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I160" s="16" t="n"/>
       <c r="J160" s="15" t="n">
         <v>286</v>
       </c>
       <c r="K160" s="20" t="inlineStr">
         <is>
-          <t>#296</t>
+          <t>#233</t>
         </is>
       </c>
     </row>
@@ -7858,70 +7846,78 @@
         </is>
       </c>
       <c r="F161" s="15" t="n">
-        <v>297</v>
+        <v>259</v>
       </c>
       <c r="G161" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: seed-codes.js를 scripts/로 옮겨 테스트 가능한 구조로 바꾸고, 잘못된 group이 있으면 명단 등록을 거부</t>
-        </is>
-      </c>
-      <c r="H161" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I161" s="16" t="n"/>
+          <t xml:space="preserve">        test: content.js를 커버리지로 측정되게 하고 80% 이상으로 보강</t>
+        </is>
+      </c>
+      <c r="H161" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>#266</t>
+        </is>
+      </c>
       <c r="J161" s="15" t="n">
         <v>286</v>
       </c>
       <c r="K161" s="20" t="inlineStr">
         <is>
-          <t>#297</t>
+          <t>#259</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="9" t="n">
+      <c r="A162" s="15" t="n">
         <v>161</v>
       </c>
-      <c r="B162" s="10" t="inlineStr">
+      <c r="B162" s="16" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C162" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-4</t>
-        </is>
-      </c>
-      <c r="D162" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F162" s="9" t="n">
-        <v>287</v>
-      </c>
-      <c r="G162" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-4: 코드 형식·정적 분석·CI가 자동으로 관리된다</t>
-        </is>
-      </c>
-      <c r="H162" s="23" t="inlineStr">
+      <c r="C162" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D162" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F162" s="15" t="n">
+        <v>265</v>
+      </c>
+      <c r="G162" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 팝업 파일을 커버리지로 측정되게 전환</t>
+        </is>
+      </c>
+      <c r="H162" s="24" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I162" s="10" t="n"/>
-      <c r="J162" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K162" s="14" t="inlineStr">
-        <is>
-          <t>#287</t>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>#284</t>
+        </is>
+      </c>
+      <c r="J162" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K162" s="20" t="inlineStr">
+        <is>
+          <t>#265</t>
         </is>
       </c>
     </row>
@@ -7936,7 +7932,7 @@
       </c>
       <c r="C163" s="16" t="inlineStr">
         <is>
-          <t>Story 9-4</t>
+          <t>Story 9-3</t>
         </is>
       </c>
       <c r="D163" s="15" t="n">
@@ -7948,29 +7944,29 @@
         </is>
       </c>
       <c r="F163" s="15" t="n">
-        <v>134</v>
+        <v>296</v>
       </c>
       <c r="G163" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: ESLint 설정 복구 및 핵심 로직(analysis/llm) 단위 테스트 도입</t>
-        </is>
-      </c>
-      <c r="H163" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t xml:space="preserve">        test: 앱 조립을 create-app.js로 분리하고 실제 조립된 앱(미들웨어 순서·라우터 마운트)을 테스트로 검증</t>
+        </is>
+      </c>
+      <c r="H163" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="I163" s="16" t="inlineStr">
         <is>
-          <t>#135</t>
+          <t>#298</t>
         </is>
       </c>
       <c r="J163" s="15" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="K163" s="20" t="inlineStr">
         <is>
-          <t>#134</t>
+          <t>#296</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7981,7 @@
       </c>
       <c r="C164" s="16" t="inlineStr">
         <is>
-          <t>Story 9-4</t>
+          <t>Story 9-3</t>
         </is>
       </c>
       <c r="D164" s="15" t="n">
@@ -7997,70 +7993,70 @@
         </is>
       </c>
       <c r="F164" s="15" t="n">
-        <v>241</v>
+        <v>297</v>
       </c>
       <c r="G164" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: prettier 형식 일괄 정리 및 CI 형식 검사 추가</t>
-        </is>
-      </c>
-      <c r="H164" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
+          <t xml:space="preserve">        test: seed-codes.js를 scripts/로 옮겨 테스트 가능한 구조로 바꾸고, 잘못된 group이 있으면 명단 등록을 거부</t>
+        </is>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
         </is>
       </c>
       <c r="I164" s="16" t="n"/>
       <c r="J164" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K164" s="20" t="inlineStr">
+        <is>
+          <t>#297</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="10" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C165" s="10" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F165" s="9" t="n">
         <v>287</v>
       </c>
-      <c r="K164" s="20" t="inlineStr">
-        <is>
-          <t>#241</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="15" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C165" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-4</t>
-        </is>
-      </c>
-      <c r="D165" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E165" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F165" s="15" t="n">
-        <v>244</v>
-      </c>
-      <c r="G165" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        chore: CI action을 Node 24 지원 버전으로 올리고 Dependabot으로 버전 업데이트 자동화</t>
-        </is>
-      </c>
-      <c r="H165" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I165" s="16" t="n"/>
-      <c r="J165" s="15" t="n">
-        <v>287</v>
-      </c>
-      <c r="K165" s="20" t="inlineStr">
-        <is>
-          <t>#244</t>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-4: 코드 형식·정적 분석·CI가 자동으로 관리된다</t>
+        </is>
+      </c>
+      <c r="H165" s="23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I165" s="10" t="n"/>
+      <c r="J165" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K165" s="14" t="inlineStr">
+        <is>
+          <t>#287</t>
         </is>
       </c>
     </row>
@@ -8087,81 +8083,220 @@
         </is>
       </c>
       <c r="F166" s="15" t="n">
-        <v>288</v>
+        <v>134</v>
       </c>
       <c r="G166" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: SonarQube 코드 품질 측정 도입</t>
-        </is>
-      </c>
-      <c r="H166" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I166" s="16" t="n"/>
+          <t xml:space="preserve">        test: ESLint 설정 복구 및 핵심 로직(analysis/llm) 단위 테스트 도입</t>
+        </is>
+      </c>
+      <c r="H166" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>#135</t>
+        </is>
+      </c>
       <c r="J166" s="15" t="n">
         <v>287</v>
       </c>
       <c r="K166" s="20" t="inlineStr">
         <is>
+          <t>#134</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="15" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C167" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D167" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E167" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F167" s="15" t="n">
+        <v>241</v>
+      </c>
+      <c r="G167" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: prettier 형식 일괄 정리 및 CI 형식 검사 추가</t>
+        </is>
+      </c>
+      <c r="H167" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I167" s="16" t="n"/>
+      <c r="J167" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K167" s="20" t="inlineStr">
+        <is>
+          <t>#241</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D168" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F168" s="15" t="n">
+        <v>244</v>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: CI action을 Node 24 지원 버전으로 올리고 Dependabot으로 버전 업데이트 자동화</t>
+        </is>
+      </c>
+      <c r="H168" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I168" s="16" t="n"/>
+      <c r="J168" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K168" s="20" t="inlineStr">
+        <is>
+          <t>#244</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="15" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C169" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D169" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E169" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F169" s="15" t="n">
+        <v>288</v>
+      </c>
+      <c r="G169" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: SonarQube 코드 품질 측정 도입</t>
+        </is>
+      </c>
+      <c r="H169" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I169" s="16" t="n"/>
+      <c r="J169" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K169" s="20" t="inlineStr">
+        <is>
           <t>#288</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="9" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" s="10" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="9" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C167" s="10" t="inlineStr">
+      <c r="C170" s="10" t="inlineStr">
         <is>
           <t>Story 9-5</t>
         </is>
       </c>
-      <c r="D167" s="9" t="n">
+      <c r="D170" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E167" s="11" t="inlineStr">
+      <c r="E170" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F167" s="9" t="n">
+      <c r="F170" s="9" t="n">
         <v>289</v>
       </c>
-      <c r="G167" s="12" t="inlineStr">
+      <c r="G170" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-5: 본 연구 규모(참가자 약 80명)의 부하를 서버가 견딘다</t>
         </is>
       </c>
-      <c r="H167" s="23" t="inlineStr">
+      <c r="H170" s="23" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I167" s="10" t="n"/>
-      <c r="J167" s="9" t="n">
+      <c r="I170" s="10" t="n"/>
+      <c r="J170" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K167" s="14" t="inlineStr">
+      <c r="K170" s="14" t="inlineStr">
         <is>
           <t>#289</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K167"/>
+  <autoFilter ref="A1:K170"/>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Epic,Story,Task,Bug"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H167" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,Closed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8333,6 +8468,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId169"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -8415,15 +8553,15 @@
         </is>
       </c>
       <c r="C2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A2,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A2,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A2,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F2" s="26">
@@ -8431,11 +8569,11 @@
         <v/>
       </c>
       <c r="G2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A2,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A2,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I2" s="36">
@@ -8455,15 +8593,15 @@
         </is>
       </c>
       <c r="C3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A3,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A3,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A3,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F3" s="26">
@@ -8471,11 +8609,11 @@
         <v/>
       </c>
       <c r="G3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A3,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A3,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I3" s="36">
@@ -8495,15 +8633,15 @@
         </is>
       </c>
       <c r="C4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A4,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A4,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A4,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F4" s="26">
@@ -8511,11 +8649,11 @@
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A4,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A4,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I4" s="36">
@@ -8535,15 +8673,15 @@
         </is>
       </c>
       <c r="C5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A5,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A5,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A5,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F5" s="26">
@@ -8551,11 +8689,11 @@
         <v/>
       </c>
       <c r="G5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A5,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A5,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I5" s="36">
@@ -8575,15 +8713,15 @@
         </is>
       </c>
       <c r="C6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A6,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A6,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A6,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F6" s="26">
@@ -8591,11 +8729,11 @@
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A6,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A6,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I6" s="36">
@@ -8615,15 +8753,15 @@
         </is>
       </c>
       <c r="C7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A7,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A7,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A7,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F7" s="26">
@@ -8631,11 +8769,11 @@
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A7,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A7,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I7" s="36">
@@ -8655,15 +8793,15 @@
         </is>
       </c>
       <c r="C8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A8,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A8,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A8,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F8" s="26">
@@ -8671,11 +8809,11 @@
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A8,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A8,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I8" s="36">
@@ -8695,15 +8833,15 @@
         </is>
       </c>
       <c r="C9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A9,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A9,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A9,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F9" s="26">
@@ -8711,11 +8849,11 @@
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A9,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A9,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I9" s="36">
@@ -8735,15 +8873,15 @@
         </is>
       </c>
       <c r="C10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A10,백로그!$E$2:$E$167,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$E$2:$E$170,"Story")</f>
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A10,백로그!$E$2:$E$167,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$E$2:$E$170,"Task")</f>
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A10,백로그!$E$2:$E$167,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$E$2:$E$170,"Bug")</f>
         <v/>
       </c>
       <c r="F10" s="26">
@@ -8751,11 +8889,11 @@
         <v/>
       </c>
       <c r="G10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A10,백로그!$H$2:$H$167,"Open",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$167,$A10,백로그!$H$2:$H$167,"Closed",백로그!$E$2:$E$167,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I10" s="36">

--- a/docs/youtube-bias-feedback_backlog.xlsx
+++ b/docs/youtube-bias-feedback_backlog.xlsx
@@ -11,7 +11,7 @@
     <sheet name="미분류·확인 필요" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'백로그'!$A$1:$K$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'백로그'!$A$1:$K$185</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:K185"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -903,7 +903,7 @@
       <c r="F8" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="21" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        영상 제목 DOM에서 파싱하는 로직 구현</t>
         </is>
@@ -999,12 +999,12 @@
       </c>
       <c r="G10" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 영상 전환 시 직전 영상 제목이 다음 기록에 붙는 문제 — videoId 확인 강화 및 메타데이터 제목 우선 사용</t>
+          <t xml:space="preserve">        fix: 영상 전환 시 직전 영상 제목이 다음 기록에 붙는 문제</t>
         </is>
       </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I10" s="16" t="n"/>
@@ -1132,7 +1132,7 @@
       <c r="F13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        중복 videoId 방지 로직 구현</t>
         </is>
@@ -1177,7 +1177,7 @@
       <c r="F14" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        저장/조회/초기화 유틸 함수 모듈화</t>
         </is>
@@ -1355,7 +1355,7 @@
       <c r="F18" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        마지막 시청 시각 갱신 로직 구현</t>
         </is>
@@ -1445,7 +1445,7 @@
       <c r="F20" s="15" t="n">
         <v>16</v>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        세션 시작/종료 시간 및 세션 ID 기록 로직 구현</t>
         </is>
@@ -1531,7 +1531,7 @@
       <c r="D22" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="17" t="inlineStr">
         <is>
           <t>Bug</t>
         </is>
@@ -1564,92 +1564,96 @@
       </c>
     </row>
     <row r="23" outlineLevel="2">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="15" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Epic 2</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Story 2-1</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>321</v>
+      </c>
+      <c r="G23" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 브라우저를 닫았다 다시 열 때 세션 종료 시각·세션 경계가 틀어지고, 함께 닫힌 세션이 서버로 전송되지 않음</t>
+        </is>
+      </c>
+      <c r="H23" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>#323</t>
+        </is>
+      </c>
+      <c r="J23" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>#321</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="2">
+      <c r="A24" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Epic 2</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Story 2-2</t>
         </is>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F24" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 2-2: 영상 ID로 YouTube Data API를 통해 카테고리 정보를 조회할 수 있다</t>
         </is>
       </c>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="9" t="n">
+      <c r="H24" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>#17</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" outlineLevel="2">
-      <c r="A24" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Epic 2</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Story 2-2</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="G24" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        YouTube Data API v3 키 발급 및 환경 설정</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="n"/>
-      <c r="J24" s="15" t="n">
-        <v>17</v>
-      </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>#18</t>
         </is>
       </c>
     </row>
@@ -1676,11 +1680,11 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        videos.list API 호출 함수 구현</t>
+          <t xml:space="preserve">        YouTube Data API v3 키 발급 및 환경 설정</t>
         </is>
       </c>
       <c r="H25" s="19" t="inlineStr">
@@ -1694,7 +1698,7 @@
       </c>
       <c r="K25" s="20" t="inlineStr">
         <is>
-          <t>#19</t>
+          <t>#18</t>
         </is>
       </c>
     </row>
@@ -1721,11 +1725,11 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        categoryId → 카테고리명 매핑 테이블 작성</t>
+          <t xml:space="preserve">        videos.list API 호출 함수 구현</t>
         </is>
       </c>
       <c r="H26" s="19" t="inlineStr">
@@ -1739,7 +1743,7 @@
       </c>
       <c r="K26" s="20" t="inlineStr">
         <is>
-          <t>#20</t>
+          <t>#19</t>
         </is>
       </c>
     </row>
@@ -1766,11 +1770,11 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        API 에러 처리 및 할당량 초과 대응 로직 구현</t>
+          <t xml:space="preserve">        categoryId → 카테고리명 매핑 테이블 작성</t>
         </is>
       </c>
       <c r="H27" s="19" t="inlineStr">
@@ -1784,7 +1788,7 @@
       </c>
       <c r="K27" s="20" t="inlineStr">
         <is>
-          <t>#21</t>
+          <t>#20</t>
         </is>
       </c>
     </row>
@@ -1811,11 +1815,11 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 영상 ID로 YouTube Data API를 통해 카테고리 정보를 조회할 수 있다</t>
+          <t xml:space="preserve">        API 에러 처리 및 할당량 초과 대응 로직 구현</t>
         </is>
       </c>
       <c r="H28" s="19" t="inlineStr">
@@ -1823,107 +1827,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>#62</t>
-        </is>
-      </c>
+      <c r="I28" s="16" t="n"/>
       <c r="J28" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K28" s="20" t="inlineStr">
         <is>
+          <t>#21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="2">
+      <c r="A29" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Epic 2</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Story 2-2</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="G29" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 영상 ID로 YouTube Data API를 통해 카테고리 정보를 조회할 수 있다</t>
+        </is>
+      </c>
+      <c r="H29" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>#62</t>
+        </is>
+      </c>
+      <c r="J29" s="15" t="n">
+        <v>17</v>
+      </c>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
           <t>#61</t>
         </is>
       </c>
     </row>
-    <row r="29" outlineLevel="2">
-      <c r="A29" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
+    <row r="30" outlineLevel="2">
+      <c r="A30" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Epic 2</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>Story 2-3</t>
         </is>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="E30" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F30" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 2-3: 세션별 카테고리 분포를 Shannon Entropy로 계산할 수 있다</t>
         </is>
       </c>
-      <c r="H29" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="n"/>
-      <c r="J29" s="9" t="n">
+      <c r="H30" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="n"/>
+      <c r="J30" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="14" t="inlineStr">
+      <c r="K30" s="14" t="inlineStr">
         <is>
           <t>#22</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" outlineLevel="2">
-      <c r="A30" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>Epic 2</t>
-        </is>
-      </c>
-      <c r="C30" s="16" t="inlineStr">
-        <is>
-          <t>Story 2-3</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        카테고리별 비율 계산 함수 구현</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="K30" s="20" t="inlineStr">
-        <is>
-          <t>#23</t>
         </is>
       </c>
     </row>
@@ -1950,11 +1954,11 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Shannon Entropy 계산 함수 구현</t>
+          <t xml:space="preserve">        카테고리별 비율 계산 함수 구현</t>
         </is>
       </c>
       <c r="H31" s="19" t="inlineStr">
@@ -1968,7 +1972,7 @@
       </c>
       <c r="K31" s="20" t="inlineStr">
         <is>
-          <t>#24</t>
+          <t>#23</t>
         </is>
       </c>
     </row>
@@ -1995,11 +1999,11 @@
         </is>
       </c>
       <c r="F32" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        세션 분석 결과 데이터 구조 정의 및 storage 저장</t>
+        <v>24</v>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Shannon Entropy 계산 함수 구현</t>
         </is>
       </c>
       <c r="H32" s="19" t="inlineStr">
@@ -2013,7 +2017,7 @@
       </c>
       <c r="K32" s="20" t="inlineStr">
         <is>
-          <t>#25</t>
+          <t>#24</t>
         </is>
       </c>
     </row>
@@ -2040,11 +2044,11 @@
         </is>
       </c>
       <c r="F33" s="15" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 세션별 카테고리 분포를 Shannon Entropy로 계산할 수 있다</t>
+          <t xml:space="preserve">        세션 분석 결과 데이터 구조 정의 및 storage 저장</t>
         </is>
       </c>
       <c r="H33" s="19" t="inlineStr">
@@ -2052,107 +2056,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>#64</t>
-        </is>
-      </c>
+      <c r="I33" s="16" t="n"/>
       <c r="J33" s="15" t="n">
         <v>22</v>
       </c>
       <c r="K33" s="20" t="inlineStr">
         <is>
+          <t>#25</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="2">
+      <c r="A34" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Epic 2</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Story 2-3</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 세션별 카테고리 분포를 Shannon Entropy로 계산할 수 있다</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>#64</t>
+        </is>
+      </c>
+      <c r="J34" s="15" t="n">
+        <v>22</v>
+      </c>
+      <c r="K34" s="20" t="inlineStr">
+        <is>
           <t>#63</t>
         </is>
       </c>
     </row>
-    <row r="34" outlineLevel="2">
-      <c r="A34" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="10" t="inlineStr">
+    <row r="35" outlineLevel="2">
+      <c r="A35" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Epic 2</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>Story 2-4</t>
         </is>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D35" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E35" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F35" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 2-4: LLM API를 통해 카테고리 분포 기반 자연어 리뷰를 자동 생성할 수 있다</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="n"/>
-      <c r="J34" s="9" t="n">
+      <c r="H35" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="9" t="n">
         <v>12</v>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K35" s="14" t="inlineStr">
         <is>
           <t>#26</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" outlineLevel="2">
-      <c r="A35" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
-        <is>
-          <t>Epic 2</t>
-        </is>
-      </c>
-      <c r="C35" s="16" t="inlineStr">
-        <is>
-          <t>Story 2-4</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="n">
-        <v>27</v>
-      </c>
-      <c r="G35" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        LLM API 선택 및 키 발급</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I35" s="16" t="n"/>
-      <c r="J35" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="K35" s="20" t="inlineStr">
-        <is>
-          <t>#27</t>
         </is>
       </c>
     </row>
@@ -2179,11 +2183,11 @@
         </is>
       </c>
       <c r="F36" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        카테고리 분포를 LLM 프롬프트로 변환하는 함수 구현</t>
+        <v>27</v>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        LLM API 선택 및 키 발급</t>
         </is>
       </c>
       <c r="H36" s="19" t="inlineStr">
@@ -2197,7 +2201,7 @@
       </c>
       <c r="K36" s="20" t="inlineStr">
         <is>
-          <t>#28</t>
+          <t>#27</t>
         </is>
       </c>
     </row>
@@ -2224,11 +2228,11 @@
         </is>
       </c>
       <c r="F37" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        LLM API 호출 및 응답 파싱 함수 구현</t>
+          <t xml:space="preserve">        카테고리 분포를 LLM 프롬프트로 변환하는 함수 구현</t>
         </is>
       </c>
       <c r="H37" s="19" t="inlineStr">
@@ -2242,7 +2246,7 @@
       </c>
       <c r="K37" s="20" t="inlineStr">
         <is>
-          <t>#29</t>
+          <t>#28</t>
         </is>
       </c>
     </row>
@@ -2269,11 +2273,11 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        리뷰 생성 실패 시 폴백 처리 구현</t>
+        <v>29</v>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        LLM API 호출 및 응답 파싱 함수 구현</t>
         </is>
       </c>
       <c r="H38" s="19" t="inlineStr">
@@ -2287,7 +2291,7 @@
       </c>
       <c r="K38" s="20" t="inlineStr">
         <is>
-          <t>#30</t>
+          <t>#29</t>
         </is>
       </c>
     </row>
@@ -2314,11 +2318,11 @@
         </is>
       </c>
       <c r="F39" s="15" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: LLM API를 통해 카테고리 분포 기반 자연어 리뷰를 자동 생성할 수 있다</t>
+          <t xml:space="preserve">        리뷰 생성 실패 시 폴백 처리 구현</t>
         </is>
       </c>
       <c r="H39" s="19" t="inlineStr">
@@ -2326,17 +2330,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>#66</t>
-        </is>
-      </c>
+      <c r="I39" s="16" t="n"/>
       <c r="J39" s="15" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="20" t="inlineStr">
         <is>
-          <t>#65</t>
+          <t>#30</t>
         </is>
       </c>
     </row>
@@ -2363,11 +2363,11 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="G40" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 시청 패턴 변화 기반 연구 맞춤형 피드백 생성</t>
+          <t xml:space="preserve">        feat: LLM API를 통해 카테고리 분포 기반 자연어 리뷰를 자동 생성할 수 있다</t>
         </is>
       </c>
       <c r="H40" s="19" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
-          <t>#103</t>
+          <t>#66</t>
         </is>
       </c>
       <c r="J40" s="15" t="n">
@@ -2385,136 +2385,140 @@
       </c>
       <c r="K40" s="20" t="inlineStr">
         <is>
+          <t>#65</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" outlineLevel="1">
+      <c r="A41" s="15" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Epic 2</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Story 2-4</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F41" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="G41" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 시청 패턴 변화 기반 연구 맞춤형 피드백 생성</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>#103</t>
+        </is>
+      </c>
+      <c r="J41" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="K41" s="20" t="inlineStr">
+        <is>
           <t>#102</t>
         </is>
       </c>
     </row>
-    <row r="41" outlineLevel="1">
-      <c r="A41" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" outlineLevel="2">
+      <c r="A42" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="3" t="n">
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F41" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="G41" s="6" t="inlineStr">
+      <c r="G42" s="6" t="inlineStr">
         <is>
           <t>Epic 3: 팝업 UI &amp; 시각화</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="8" t="inlineStr">
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>#31</t>
         </is>
       </c>
     </row>
-    <row r="42" outlineLevel="2">
-      <c r="A42" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="10" t="inlineStr">
+    <row r="43" outlineLevel="2">
+      <c r="A43" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>Story 3-1</t>
         </is>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D43" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E42" s="11" t="inlineStr">
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F43" s="9" t="n">
         <v>32</v>
       </c>
-      <c r="G42" s="12" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 3-1: 팝업에서 세션의 카테고리 분포를 막대그래프로 확인할 수 있다</t>
         </is>
       </c>
-      <c r="H42" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="n"/>
-      <c r="J42" s="9" t="n">
+      <c r="H43" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="K42" s="14" t="inlineStr">
+      <c r="K43" s="14" t="inlineStr">
         <is>
           <t>#32</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" outlineLevel="2">
-      <c r="A43" s="15" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
-        <is>
-          <t>Epic 3</t>
-        </is>
-      </c>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>Story 3-1</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E43" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F43" s="15" t="n">
-        <v>33</v>
-      </c>
-      <c r="G43" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        popup.html / popup.js 기본 구조 작성</t>
-        </is>
-      </c>
-      <c r="H43" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="K43" s="20" t="inlineStr">
-        <is>
-          <t>#33</t>
         </is>
       </c>
     </row>
@@ -2541,11 +2545,11 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>34</v>
-      </c>
-      <c r="G44" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        카테고리 분포 막대그래프 렌더링 구현</t>
+        <v>33</v>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        popup.html / popup.js 기본 구조 작성</t>
         </is>
       </c>
       <c r="H44" s="19" t="inlineStr">
@@ -2559,7 +2563,7 @@
       </c>
       <c r="K44" s="20" t="inlineStr">
         <is>
-          <t>#34</t>
+          <t>#33</t>
         </is>
       </c>
     </row>
@@ -2586,11 +2590,11 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="G45" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        팝업 CSS 스타일링</t>
+        <v>34</v>
+      </c>
+      <c r="G45" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        카테고리 분포 막대그래프 렌더링 구현</t>
         </is>
       </c>
       <c r="H45" s="19" t="inlineStr">
@@ -2604,7 +2608,7 @@
       </c>
       <c r="K45" s="20" t="inlineStr">
         <is>
-          <t>#35</t>
+          <t>#34</t>
         </is>
       </c>
     </row>
@@ -2631,11 +2635,11 @@
         </is>
       </c>
       <c r="F46" s="15" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G46" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 팝업에서 세션의 카테고리 분포를 막대그래프로 확인할 수 있다</t>
+          <t xml:space="preserve">        팝업 CSS 스타일링</t>
         </is>
       </c>
       <c r="H46" s="19" t="inlineStr">
@@ -2643,107 +2647,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>#68</t>
-        </is>
-      </c>
+      <c r="I46" s="16" t="n"/>
       <c r="J46" s="15" t="n">
         <v>32</v>
       </c>
       <c r="K46" s="20" t="inlineStr">
         <is>
+          <t>#35</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="2">
+      <c r="A47" s="15" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-1</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="n">
+        <v>67</v>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 팝업에서 세션의 카테고리 분포를 막대그래프로 확인할 수 있다</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>#68</t>
+        </is>
+      </c>
+      <c r="J47" s="15" t="n">
+        <v>32</v>
+      </c>
+      <c r="K47" s="20" t="inlineStr">
+        <is>
           <t>#67</t>
         </is>
       </c>
     </row>
-    <row r="47" outlineLevel="2">
-      <c r="A47" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="10" t="inlineStr">
+    <row r="48" outlineLevel="2">
+      <c r="A48" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C47" s="10" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>Story 3-2</t>
         </is>
       </c>
-      <c r="D47" s="9" t="n">
+      <c r="D48" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E47" s="11" t="inlineStr">
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F47" s="9" t="n">
+      <c r="F48" s="9" t="n">
         <v>36</v>
       </c>
-      <c r="G47" s="12" t="inlineStr">
+      <c r="G48" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 3-2: 팝업에서 세션 종료 후 자동 생성된 자연어 리뷰를 확인할 수 있다</t>
         </is>
       </c>
-      <c r="H47" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="n"/>
-      <c r="J47" s="9" t="n">
+      <c r="H48" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="K47" s="14" t="inlineStr">
+      <c r="K48" s="14" t="inlineStr">
         <is>
           <t>#36</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="2">
-      <c r="A48" s="15" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>Epic 3</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>Story 3-2</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E48" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F48" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        리뷰 텍스트 표시 영역 구현</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I48" s="16" t="n"/>
-      <c r="J48" s="15" t="n">
-        <v>36</v>
-      </c>
-      <c r="K48" s="20" t="inlineStr">
-        <is>
-          <t>#37</t>
         </is>
       </c>
     </row>
@@ -2770,11 +2774,11 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>38</v>
-      </c>
-      <c r="G49" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        리뷰 생성 로딩 상태 UI 구현</t>
+        <v>37</v>
+      </c>
+      <c r="G49" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        리뷰 텍스트 표시 영역 구현</t>
         </is>
       </c>
       <c r="H49" s="19" t="inlineStr">
@@ -2788,7 +2792,7 @@
       </c>
       <c r="K49" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>#37</t>
         </is>
       </c>
     </row>
@@ -2815,11 +2819,11 @@
         </is>
       </c>
       <c r="F50" s="15" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 팝업에서 세션 종료 후 자동 생성된 자연어 리뷰를 확인할 수 있다</t>
+          <t xml:space="preserve">        리뷰 생성 로딩 상태 UI 구현</t>
         </is>
       </c>
       <c r="H50" s="19" t="inlineStr">
@@ -2827,107 +2831,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>#70</t>
-        </is>
-      </c>
+      <c r="I50" s="16" t="n"/>
       <c r="J50" s="15" t="n">
         <v>36</v>
       </c>
       <c r="K50" s="20" t="inlineStr">
         <is>
+          <t>#38</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" outlineLevel="2">
+      <c r="A51" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-2</t>
+        </is>
+      </c>
+      <c r="D51" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="n">
+        <v>69</v>
+      </c>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 팝업에서 세션 종료 후 자동 생성된 자연어 리뷰를 확인할 수 있다</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>#70</t>
+        </is>
+      </c>
+      <c r="J51" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="K51" s="20" t="inlineStr">
+        <is>
           <t>#69</t>
         </is>
       </c>
     </row>
-    <row r="51" outlineLevel="2">
-      <c r="A51" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="10" t="inlineStr">
+    <row r="52" outlineLevel="2">
+      <c r="A52" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C51" s="10" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>Story 3-3</t>
         </is>
       </c>
-      <c r="D51" s="9" t="n">
+      <c r="D52" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E51" s="11" t="inlineStr">
+      <c r="E52" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F51" s="9" t="n">
+      <c r="F52" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="G51" s="12" t="inlineStr">
+      <c r="G52" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 3-3: 주간 리포트를 통해 기간별 카테고리 소비 패턴 변화를 확인할 수 있다</t>
         </is>
       </c>
-      <c r="H51" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="n"/>
-      <c r="J51" s="9" t="n">
+      <c r="H52" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="n"/>
+      <c r="J52" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="K51" s="14" t="inlineStr">
+      <c r="K52" s="14" t="inlineStr">
         <is>
           <t>#39</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="2">
-      <c r="A52" s="15" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>Epic 3</t>
-        </is>
-      </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>Story 3-3</t>
-        </is>
-      </c>
-      <c r="D52" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E52" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="G52" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        최근 7일 누적 세션 데이터 집계 함수 구현</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I52" s="16" t="n"/>
-      <c r="J52" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="K52" s="20" t="inlineStr">
-        <is>
-          <t>#40</t>
         </is>
       </c>
     </row>
@@ -2954,11 +2958,11 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>41</v>
-      </c>
-      <c r="G53" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        주간 카테고리 분포 변화 시각화 구현</t>
+        <v>40</v>
+      </c>
+      <c r="G53" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        최근 7일 누적 세션 데이터 집계 함수 구현</t>
         </is>
       </c>
       <c r="H53" s="19" t="inlineStr">
@@ -2972,7 +2976,7 @@
       </c>
       <c r="K53" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>#40</t>
         </is>
       </c>
     </row>
@@ -2999,11 +3003,11 @@
         </is>
       </c>
       <c r="F54" s="15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Entropy 변화 추이 표시 구현</t>
+          <t xml:space="preserve">        주간 카테고리 분포 변화 시각화 구현</t>
         </is>
       </c>
       <c r="H54" s="19" t="inlineStr">
@@ -3017,7 +3021,7 @@
       </c>
       <c r="K54" s="20" t="inlineStr">
         <is>
-          <t>#42</t>
+          <t>#41</t>
         </is>
       </c>
     </row>
@@ -3044,11 +3048,11 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 주간 리포트를 통해 기간별 카테고리 소비 패턴 변화를 확인할 수 있다</t>
+          <t xml:space="preserve">        Entropy 변화 추이 표시 구현</t>
         </is>
       </c>
       <c r="H55" s="19" t="inlineStr">
@@ -3056,17 +3060,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>#72</t>
-        </is>
-      </c>
+      <c r="I55" s="16" t="n"/>
       <c r="J55" s="15" t="n">
         <v>39</v>
       </c>
       <c r="K55" s="20" t="inlineStr">
         <is>
-          <t>#71</t>
+          <t>#42</t>
         </is>
       </c>
     </row>
@@ -3089,123 +3089,123 @@
       </c>
       <c r="E56" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>301</v>
+        <v>71</v>
       </c>
       <c r="G56" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 끝난 구간의 기간 리뷰가 팝업 캐시 때문에 다음 날까지 보이지 않음</t>
+          <t xml:space="preserve">        feat: 주간 리포트를 통해 기간별 카테고리 소비 패턴 변화를 확인할 수 있다</t>
         </is>
       </c>
       <c r="H56" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I56" s="16" t="n"/>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>#72</t>
+        </is>
+      </c>
       <c r="J56" s="15" t="n">
         <v>39</v>
       </c>
       <c r="K56" s="20" t="inlineStr">
         <is>
+          <t>#71</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="15" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-3</t>
+        </is>
+      </c>
+      <c r="D57" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F57" s="15" t="n">
+        <v>301</v>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 끝난 구간의 기간 리뷰가 팝업 캐시 때문에 다음 날까지 보이지 않음</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I57" s="16" t="n"/>
+      <c r="J57" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="K57" s="20" t="inlineStr">
+        <is>
           <t>#301</t>
         </is>
       </c>
     </row>
-    <row r="57" outlineLevel="1">
-      <c r="A57" s="9" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="10" t="inlineStr">
+    <row r="58" outlineLevel="2">
+      <c r="A58" s="9" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>Story 3-5</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="n">
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Story 3-4</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="11" t="inlineStr">
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F57" s="9" t="n">
-        <v>270</v>
-      </c>
-      <c r="G57" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 3-5: 참가자마다 익명 ID가 발급되어 데이터가 참가자 단위로 저장된다</t>
-        </is>
-      </c>
-      <c r="H57" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="n"/>
-      <c r="J57" s="9" t="n">
+      <c r="F58" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 3-4: 참가자가 설치 시 참여코드를 입력하고 설문 알림을 받을 수 있다</t>
+        </is>
+      </c>
+      <c r="H58" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I58" s="10" t="n"/>
+      <c r="J58" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="K57" s="14" t="inlineStr">
-        <is>
-          <t>#270</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" outlineLevel="2">
-      <c r="A58" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Epic 3</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>Story 3-5</t>
-        </is>
-      </c>
-      <c r="D58" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F58" s="15" t="n">
-        <v>88</v>
-      </c>
-      <c r="G58" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 온보딩 시 anonymousId(UUID) 생성</t>
-        </is>
-      </c>
-      <c r="H58" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>#90</t>
-        </is>
-      </c>
-      <c r="J58" s="15" t="n">
-        <v>270</v>
-      </c>
-      <c r="K58" s="20" t="inlineStr">
-        <is>
-          <t>#88</t>
+      <c r="K58" s="14" t="inlineStr">
+        <is>
+          <t>#49</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Story 3-6</t>
+          <t>Story 3-5</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
@@ -3232,16 +3232,16 @@
         </is>
       </c>
       <c r="F59" s="9" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 3-6: 참가자가 개편된 팝업에서 집단별 화면과 오늘의 시청 현황을 볼 수 있다</t>
-        </is>
-      </c>
-      <c r="H59" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">    Story 3-5: 참가자마다 익명 ID가 발급되어 데이터가 참가자 단위로 저장된다</t>
+        </is>
+      </c>
+      <c r="H59" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I59" s="10" t="n"/>
@@ -3250,7 +3250,7 @@
       </c>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>#290</t>
+          <t>#270</t>
         </is>
       </c>
     </row>
@@ -3265,174 +3265,184 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
+          <t>Story 3-5</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="n">
+        <v>88</v>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 온보딩 시 anonymousId(UUID) 생성</t>
+        </is>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>#90</t>
+        </is>
+      </c>
+      <c r="J60" s="15" t="n">
+        <v>270</v>
+      </c>
+      <c r="K60" s="20" t="inlineStr">
+        <is>
+          <t>#88</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
           <t>Story 3-6</t>
         </is>
       </c>
-      <c r="D60" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="n">
+      <c r="D61" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="n">
+        <v>290</v>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 3-6: 참가자가 개편된 팝업에서 집단별 화면과 오늘의 시청 현황을 볼 수 있다</t>
+        </is>
+      </c>
+      <c r="H61" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I61" s="10" t="n"/>
+      <c r="J61" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>#290</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="2">
+      <c r="A62" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-6</t>
+        </is>
+      </c>
+      <c r="D62" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="n">
         <v>86</v>
       </c>
-      <c r="G60" s="18" t="inlineStr">
+      <c r="G62" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat: 팝업 UI 전면 개편(실험군/대조군에 따른 UI 분기)</t>
         </is>
       </c>
-      <c r="H60" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
+      <c r="H62" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>#87</t>
         </is>
       </c>
-      <c r="J60" s="15" t="n">
+      <c r="J62" s="15" t="n">
         <v>290</v>
       </c>
-      <c r="K60" s="20" t="inlineStr">
+      <c r="K62" s="20" t="inlineStr">
         <is>
           <t>#86</t>
         </is>
       </c>
     </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="15" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="16" t="inlineStr">
+    <row r="63" outlineLevel="2">
+      <c r="A63" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>Epic 3</t>
         </is>
       </c>
-      <c r="C61" s="16" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>Story 3-6</t>
         </is>
       </c>
-      <c r="D61" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="n">
+      <c r="D63" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="n">
         <v>95</v>
       </c>
-      <c r="G61" s="18" t="inlineStr">
+      <c r="G63" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat: 오늘의 시청 탭 ux 개선</t>
         </is>
       </c>
-      <c r="H61" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>#96</t>
         </is>
       </c>
-      <c r="J61" s="15" t="n">
+      <c r="J63" s="15" t="n">
         <v>290</v>
       </c>
-      <c r="K61" s="20" t="inlineStr">
+      <c r="K63" s="20" t="inlineStr">
         <is>
           <t>#95</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" outlineLevel="2">
-      <c r="A62" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>Epic 4: 백엔드 서버 - API &amp; DB</t>
-        </is>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I62" s="4" t="n"/>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="8" t="inlineStr">
-        <is>
-          <t>#43</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" outlineLevel="2">
-      <c r="A63" s="9" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>Story 4-1</t>
-        </is>
-      </c>
-      <c r="D63" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>44</v>
-      </c>
-      <c r="G63" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 4-1: 서버가 익명화된 세션 분석 결과를 수신하여 DB에 저장할 수 있다</t>
-        </is>
-      </c>
-      <c r="H63" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="n"/>
-      <c r="J63" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="K63" s="14" t="inlineStr">
-        <is>
-          <t>#44</t>
         </is>
       </c>
     </row>
@@ -3442,132 +3452,130 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
+          <t>Epic 3</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>Story 3-6</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F64" s="15" t="n">
+        <v>328</v>
+      </c>
+      <c r="G64" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 온보딩 직후 팝업 머리말에 참여 코드가 없고, 기간 탭이 항상 1구간으로 열리며, 홈 안내 문구가 단어 중간에서 줄바꿈됨</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>#331</t>
+        </is>
+      </c>
+      <c r="J64" s="15" t="n">
+        <v>290</v>
+      </c>
+      <c r="K64" s="20" t="inlineStr">
+        <is>
+          <t>#328</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="2">
+      <c r="A65" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
           <t>Epic 4</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C65" s="4" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>Epic 4: 백엔드 서버 - API &amp; DB</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>#43</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" outlineLevel="2">
+      <c r="A66" s="9" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
         <is>
           <t>Story 4-1</t>
         </is>
       </c>
-      <c r="D64" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F64" s="15" t="n">
-        <v>45</v>
-      </c>
-      <c r="G64" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        db.js 작성 - SQLite 연결 및 테이블 초기화</t>
-        </is>
-      </c>
-      <c r="H64" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I64" s="16" t="n"/>
-      <c r="J64" s="15" t="n">
+      <c r="D66" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="K64" s="20" t="inlineStr">
-        <is>
-          <t>#45</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" outlineLevel="2">
-      <c r="A65" s="15" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C65" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-1</t>
-        </is>
-      </c>
-      <c r="D65" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="n">
-        <v>46</v>
-      </c>
-      <c r="G65" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        sessions 테이블 스키마 정의</t>
-        </is>
-      </c>
-      <c r="H65" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I65" s="16" t="n"/>
-      <c r="J65" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="K65" s="20" t="inlineStr">
-        <is>
-          <t>#46</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" outlineLevel="2">
-      <c r="A66" s="15" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-1</t>
-        </is>
-      </c>
-      <c r="D66" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="n">
-        <v>47</v>
-      </c>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        POST /api/sessions 라우터 구현</t>
-        </is>
-      </c>
-      <c r="H66" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I66" s="16" t="n"/>
-      <c r="J66" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="K66" s="20" t="inlineStr">
-        <is>
-          <t>#47</t>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 4-1: 서버가 익명화된 세션 분석 결과를 수신하여 DB에 저장할 수 있다</t>
+        </is>
+      </c>
+      <c r="H66" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I66" s="10" t="n"/>
+      <c r="J66" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="K66" s="14" t="inlineStr">
+        <is>
+          <t>#44</t>
         </is>
       </c>
     </row>
@@ -3594,11 +3602,11 @@
         </is>
       </c>
       <c r="F67" s="15" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        sessions 라우터 입력값 검증 로직 구현</t>
+          <t xml:space="preserve">        db.js 작성 - SQLite 연결 및 테이블 초기화</t>
         </is>
       </c>
       <c r="H67" s="19" t="inlineStr">
@@ -3612,7 +3620,7 @@
       </c>
       <c r="K67" s="20" t="inlineStr">
         <is>
-          <t>#48</t>
+          <t>#45</t>
         </is>
       </c>
     </row>
@@ -3639,11 +3647,11 @@
         </is>
       </c>
       <c r="F68" s="15" t="n">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: POST /api/sessions - 익명화된 세션 분석 결과 수신하여 DB에 저장할 수 있다</t>
+          <t xml:space="preserve">        sessions 테이블 스키마 정의</t>
         </is>
       </c>
       <c r="H68" s="19" t="inlineStr">
@@ -3651,17 +3659,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>#74</t>
-        </is>
-      </c>
+      <c r="I68" s="16" t="n"/>
       <c r="J68" s="15" t="n">
         <v>44</v>
       </c>
       <c r="K68" s="20" t="inlineStr">
         <is>
-          <t>#73</t>
+          <t>#46</t>
         </is>
       </c>
     </row>
@@ -3688,11 +3692,11 @@
         </is>
       </c>
       <c r="F69" s="15" t="n">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="G69" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 세션 분석 완료 후 서버 전송</t>
+          <t xml:space="preserve">        POST /api/sessions 라우터 구현</t>
         </is>
       </c>
       <c r="H69" s="19" t="inlineStr">
@@ -3700,107 +3704,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>#92</t>
-        </is>
-      </c>
+      <c r="I69" s="16" t="n"/>
       <c r="J69" s="15" t="n">
         <v>44</v>
       </c>
       <c r="K69" s="20" t="inlineStr">
         <is>
-          <t>#89</t>
+          <t>#47</t>
         </is>
       </c>
     </row>
     <row r="70" outlineLevel="2">
-      <c r="A70" s="9" t="n">
+      <c r="A70" s="15" t="n">
         <v>69</v>
       </c>
-      <c r="B70" s="10" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>Epic 4</t>
         </is>
       </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Story 4-2</t>
-        </is>
-      </c>
-      <c r="D70" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="G70" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 4-2: 실험 온보딩 및 설문 알림 기능을 사용할 수 있다</t>
-        </is>
-      </c>
-      <c r="H70" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="n"/>
-      <c r="J70" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="K70" s="14" t="inlineStr">
-        <is>
-          <t>#49</t>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-1</t>
+        </is>
+      </c>
+      <c r="D70" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="n">
+        <v>48</v>
+      </c>
+      <c r="G70" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        sessions 라우터 입력값 검증 로직 구현</t>
+        </is>
+      </c>
+      <c r="H70" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I70" s="16" t="n"/>
+      <c r="J70" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="K70" s="20" t="inlineStr">
+        <is>
+          <t>#48</t>
         </is>
       </c>
     </row>
     <row r="71" outlineLevel="2">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="15" t="n">
         <v>70</v>
       </c>
-      <c r="B71" s="10" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>Epic 4</t>
         </is>
       </c>
-      <c r="C71" s="10" t="inlineStr">
-        <is>
-          <t>Story 4-2</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>271</v>
-      </c>
-      <c r="G71" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 4-2: 서버가 설문 응답을 수신하여 DB에 저장할 수 있다</t>
-        </is>
-      </c>
-      <c r="H71" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="n"/>
-      <c r="J71" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="K71" s="14" t="inlineStr">
-        <is>
-          <t>#271</t>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-1</t>
+        </is>
+      </c>
+      <c r="D71" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="G71" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: POST /api/sessions - 익명화된 세션 분석 결과 수신하여 DB에 저장할 수 있다</t>
+        </is>
+      </c>
+      <c r="H71" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>#74</t>
+        </is>
+      </c>
+      <c r="J71" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="K71" s="20" t="inlineStr">
+        <is>
+          <t>#73</t>
         </is>
       </c>
     </row>
@@ -3815,127 +3819,131 @@
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
+          <t>Story 4-1</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="n">
+        <v>89</v>
+      </c>
+      <c r="G72" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 세션 분석 완료 후 서버 전송</t>
+        </is>
+      </c>
+      <c r="H72" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>#92</t>
+        </is>
+      </c>
+      <c r="J72" s="15" t="n">
+        <v>44</v>
+      </c>
+      <c r="K72" s="20" t="inlineStr">
+        <is>
+          <t>#89</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" outlineLevel="2">
+      <c r="A73" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
           <t>Story 4-2</t>
         </is>
       </c>
-      <c r="D72" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E72" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F72" s="15" t="n">
+      <c r="D73" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 4-2: 서버가 설문 응답을 수신하여 DB에 저장할 수 있다</t>
+        </is>
+      </c>
+      <c r="H73" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="n"/>
+      <c r="J73" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="K73" s="14" t="inlineStr">
+        <is>
+          <t>#271</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" outlineLevel="2">
+      <c r="A74" s="15" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-2</t>
+        </is>
+      </c>
+      <c r="D74" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="n">
         <v>50</v>
       </c>
-      <c r="G72" s="18" t="inlineStr">
+      <c r="G74" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        surveys 테이블 스키마 정의</t>
         </is>
       </c>
-      <c r="H72" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I72" s="16" t="n"/>
-      <c r="J72" s="15" t="n">
+      <c r="H74" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I74" s="16" t="n"/>
+      <c r="J74" s="15" t="n">
         <v>271</v>
       </c>
-      <c r="K72" s="20" t="inlineStr">
+      <c r="K74" s="20" t="inlineStr">
         <is>
           <t>#50</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" outlineLevel="2">
-      <c r="A73" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C73" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-2</t>
-        </is>
-      </c>
-      <c r="D73" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E73" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="n">
-        <v>51</v>
-      </c>
-      <c r="G73" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: POST /api/surveys 라우터 구현</t>
-        </is>
-      </c>
-      <c r="H73" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I73" s="16" t="n"/>
-      <c r="J73" s="15" t="n">
-        <v>271</v>
-      </c>
-      <c r="K73" s="20" t="inlineStr">
-        <is>
-          <t>#51</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" outlineLevel="2">
-      <c r="A74" s="9" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="10" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C74" s="10" t="inlineStr">
-        <is>
-          <t>Story 4-3</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="G74" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 4-3: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
-        </is>
-      </c>
-      <c r="H74" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="n"/>
-      <c r="J74" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="K74" s="14" t="inlineStr">
-        <is>
-          <t>#78</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3958,7 @@
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Story 4-3</t>
+          <t>Story 4-2</t>
         </is>
       </c>
       <c r="D75" s="15" t="n">
@@ -3962,11 +3970,11 @@
         </is>
       </c>
       <c r="F75" s="15" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G75" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: 서버 외부 배포 및 /health 확인</t>
+          <t xml:space="preserve">        feat: POST /api/surveys 라우터 구현</t>
         </is>
       </c>
       <c r="H75" s="19" t="inlineStr">
@@ -3976,56 +3984,56 @@
       </c>
       <c r="I75" s="16" t="n"/>
       <c r="J75" s="15" t="n">
+        <v>271</v>
+      </c>
+      <c r="K75" s="20" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" outlineLevel="2">
+      <c r="A76" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Story 4-3</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="n">
         <v>78</v>
       </c>
-      <c r="K75" s="20" t="inlineStr">
-        <is>
-          <t>#52</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" outlineLevel="2">
-      <c r="A76" s="15" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>Epic 4</t>
-        </is>
-      </c>
-      <c r="C76" s="16" t="inlineStr">
-        <is>
-          <t>Story 4-3</t>
-        </is>
-      </c>
-      <c r="D76" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E76" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F76" s="15" t="n">
-        <v>53</v>
-      </c>
-      <c r="G76" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        docs: .env.example 파일 작성</t>
-        </is>
-      </c>
-      <c r="H76" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I76" s="16" t="n"/>
-      <c r="J76" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="K76" s="20" t="inlineStr">
-        <is>
-          <t>#53</t>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 4-3: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
+        </is>
+      </c>
+      <c r="H76" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I76" s="10" t="n"/>
+      <c r="J76" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="K76" s="14" t="inlineStr">
+        <is>
+          <t>#78</t>
         </is>
       </c>
     </row>
@@ -4052,11 +4060,11 @@
         </is>
       </c>
       <c r="F77" s="15" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        deploy: 서버 배포</t>
+          <t xml:space="preserve">        chore: 서버 외부 배포 및 /health 확인</t>
         </is>
       </c>
       <c r="H77" s="19" t="inlineStr">
@@ -4070,7 +4078,7 @@
       </c>
       <c r="K77" s="20" t="inlineStr">
         <is>
-          <t>#54</t>
+          <t>#52</t>
         </is>
       </c>
     </row>
@@ -4097,11 +4105,11 @@
         </is>
       </c>
       <c r="F78" s="15" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
+          <t xml:space="preserve">        docs: .env.example 파일 작성</t>
         </is>
       </c>
       <c r="H78" s="19" t="inlineStr">
@@ -4109,203 +4117,195 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>#80</t>
-        </is>
-      </c>
+      <c r="I78" s="16" t="n"/>
       <c r="J78" s="15" t="n">
         <v>78</v>
       </c>
       <c r="K78" s="20" t="inlineStr">
         <is>
+          <t>#53</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="16" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C79" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-3</t>
+        </is>
+      </c>
+      <c r="D79" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F79" s="15" t="n">
+        <v>54</v>
+      </c>
+      <c r="G79" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        deploy: 서버 배포</t>
+        </is>
+      </c>
+      <c r="H79" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I79" s="16" t="n"/>
+      <c r="J79" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="K79" s="20" t="inlineStr">
+        <is>
+          <t>#54</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" outlineLevel="2">
+      <c r="A80" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="16" t="inlineStr">
+        <is>
+          <t>Epic 4</t>
+        </is>
+      </c>
+      <c r="C80" s="16" t="inlineStr">
+        <is>
+          <t>Story 4-3</t>
+        </is>
+      </c>
+      <c r="D80" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="n">
+        <v>79</v>
+      </c>
+      <c r="G80" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 서버를 외부에 배포하여 확장 프로그램과 통신할 수 있다</t>
+        </is>
+      </c>
+      <c r="H80" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>#80</t>
+        </is>
+      </c>
+      <c r="J80" s="15" t="n">
+        <v>78</v>
+      </c>
+      <c r="K80" s="20" t="inlineStr">
+        <is>
           <t>#79</t>
         </is>
       </c>
     </row>
-    <row r="79" outlineLevel="1">
-      <c r="A79" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="3" t="n">
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F79" s="3" t="n">
+      <c r="F81" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>Epic 5: 데이터·개인정보 보강</t>
         </is>
       </c>
-      <c r="H79" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I79" s="4" t="n"/>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="8" t="inlineStr">
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="n"/>
+      <c r="J81" s="3" t="n"/>
+      <c r="K81" s="8" t="inlineStr">
         <is>
           <t>#127</t>
         </is>
       </c>
     </row>
-    <row r="80" outlineLevel="2">
-      <c r="A80" s="9" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="10" t="inlineStr">
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C80" s="10" t="inlineStr">
-        <is>
-          <t>Story 10-1</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="n">
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Story 5-1</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E80" s="11" t="inlineStr">
+      <c r="E82" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F80" s="9" t="n">
+      <c r="F82" s="9" t="n">
         <v>128</v>
       </c>
-      <c r="G80" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 10-1: 가명처리 기반 식별자 체계 및 IRB / 개인정보 처리방침 재설계</t>
-        </is>
-      </c>
-      <c r="H80" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I80" s="10" t="inlineStr">
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 5-1: 가명처리 기반 식별자 체계 및 IRB / 개인정보 처리방침 재설계</t>
+        </is>
+      </c>
+      <c r="H82" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>#129</t>
         </is>
       </c>
-      <c r="J80" s="9" t="n">
+      <c r="J82" s="9" t="n">
         <v>127</v>
       </c>
-      <c r="K80" s="14" t="inlineStr">
+      <c r="K82" s="14" t="inlineStr">
         <is>
           <t>#128</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="10" t="inlineStr">
-        <is>
-          <t>Epic 5</t>
-        </is>
-      </c>
-      <c r="C81" s="10" t="inlineStr">
-        <is>
-          <t>Story 5-2</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="n">
-        <v>130</v>
-      </c>
-      <c r="G81" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 5-2: 데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
-        </is>
-      </c>
-      <c r="H81" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I81" s="10" t="inlineStr">
-        <is>
-          <t>#131</t>
-        </is>
-      </c>
-      <c r="J81" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="K81" s="14" t="inlineStr">
-        <is>
-          <t>#130</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="A82" s="15" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="16" t="inlineStr">
-        <is>
-          <t>Epic 5</t>
-        </is>
-      </c>
-      <c r="C82" s="16" t="inlineStr">
-        <is>
-          <t>Story 5-2</t>
-        </is>
-      </c>
-      <c r="D82" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E82" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="n">
-        <v>116</v>
-      </c>
-      <c r="G82" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
-        </is>
-      </c>
-      <c r="H82" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>#121</t>
-        </is>
-      </c>
-      <c r="J82" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="K82" s="20" t="inlineStr">
-        <is>
-          <t>#116</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Story 5-3</t>
+          <t>Story 5-2</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
@@ -4332,11 +4332,11 @@
         </is>
       </c>
       <c r="F83" s="9" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-3: 세션 처리 지연시간(Latency) 로깅</t>
+          <t xml:space="preserve">    Story 5-2: 데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
         </is>
       </c>
       <c r="H83" s="13" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="I83" s="10" t="inlineStr">
         <is>
-          <t>#125</t>
+          <t>#131</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
@@ -4354,56 +4354,56 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>#117</t>
+          <t>#130</t>
         </is>
       </c>
     </row>
     <row r="84" outlineLevel="1">
-      <c r="A84" s="9" t="n">
+      <c r="A84" s="15" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="10" t="inlineStr">
+      <c r="B84" s="16" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C84" s="10" t="inlineStr">
-        <is>
-          <t>Story 5-4</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E84" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F84" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="G84" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 5-4: LLM 실패·폴백 작동 로깅</t>
-        </is>
-      </c>
-      <c r="H84" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I84" s="10" t="inlineStr">
-        <is>
-          <t>#125</t>
-        </is>
-      </c>
-      <c r="J84" s="9" t="n">
-        <v>127</v>
-      </c>
-      <c r="K84" s="14" t="inlineStr">
-        <is>
-          <t>#118</t>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>Story 5-2</t>
+        </is>
+      </c>
+      <c r="D84" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="n">
+        <v>116</v>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        데이터 저장소(SQLite) 유지·이전 검토 및 스키마 확정</t>
+        </is>
+      </c>
+      <c r="H84" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>#121</t>
+        </is>
+      </c>
+      <c r="J84" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="K84" s="20" t="inlineStr">
+        <is>
+          <t>#116</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>Story 5-5</t>
+          <t>Story 5-3</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
@@ -4430,11 +4430,11 @@
         </is>
       </c>
       <c r="F85" s="9" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-5: 팝업 상호작용(체류시간·탭 클릭) 마이크로 로그</t>
+          <t xml:space="preserve">    Story 5-3: 세션 처리 지연시간(Latency) 로깅</t>
         </is>
       </c>
       <c r="H85" s="13" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>#119</t>
+          <t>#117</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Story 5-6</t>
+          <t>Story 5-4</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
@@ -4479,11 +4479,11 @@
         </is>
       </c>
       <c r="F86" s="9" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-6: 세션 분석 완료 알림 및 피드백 열람 유도</t>
+          <t xml:space="preserve">    Story 5-4: LLM 실패·폴백 작동 로깅</t>
         </is>
       </c>
       <c r="H86" s="13" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="I86" s="10" t="inlineStr">
         <is>
-          <t>#133</t>
+          <t>#125</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>#132</t>
+          <t>#118</t>
         </is>
       </c>
     </row>
@@ -4516,7 +4516,7 @@
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Story 5-7</t>
+          <t>Story 5-5</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
@@ -4528,11 +4528,11 @@
         </is>
       </c>
       <c r="F87" s="9" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-7: 세밀 다양성 신호(토픽·채널·발견 경로)</t>
+          <t xml:space="preserve">    Story 5-5: 팝업 상호작용(체류시간·탭 클릭) 마이크로 로그</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="I87" s="10" t="inlineStr">
         <is>
-          <t>#141</t>
+          <t>#125</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>#140</t>
+          <t>#119</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Story 5-8</t>
+          <t>Story 5-6</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
@@ -4577,11 +4577,11 @@
         </is>
       </c>
       <c r="F88" s="9" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-8: 2주 베이스라인 이후 그룹(CON/EXP) 분기 전달</t>
+          <t xml:space="preserve">    Story 5-6: 세션 분석 완료 알림 및 피드백 열람 유도</t>
         </is>
       </c>
       <c r="H88" s="13" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I88" s="10" t="inlineStr">
         <is>
-          <t>#137</t>
+          <t>#133</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>#136</t>
+          <t>#132</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Story 5-9</t>
+          <t>Story 5-7</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
@@ -4626,25 +4626,29 @@
         </is>
       </c>
       <c r="F89" s="9" t="n">
-        <v>291</v>
+        <v>140</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-9: 설문 척도 설계·검증 (다문항화·파일럿)</t>
-        </is>
-      </c>
-      <c r="H89" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I89" s="10" t="n"/>
+          <t xml:space="preserve">    Story 5-7: 세밀 다양성 신호(토픽·채널·발견 경로)</t>
+        </is>
+      </c>
+      <c r="H89" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I89" s="10" t="inlineStr">
+        <is>
+          <t>#141</t>
+        </is>
+      </c>
       <c r="J89" s="9" t="n">
         <v>127</v>
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>#291</t>
+          <t>#140</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4663,7 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Story 10-11</t>
+          <t>Story 5-8</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
@@ -4671,11 +4675,11 @@
         </is>
       </c>
       <c r="F90" s="9" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 10-11: llm.js 피드백 보강 (서버 저장·문구 톤 통일·프롬프트 버전·가드레일 필터)</t>
+          <t xml:space="preserve">    Story 5-8: 2주 베이스라인 이후 그룹(CON/EXP) 분기 전달</t>
         </is>
       </c>
       <c r="H90" s="13" t="inlineStr">
@@ -4685,7 +4689,7 @@
       </c>
       <c r="I90" s="10" t="inlineStr">
         <is>
-          <t>#139</t>
+          <t>#137</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
@@ -4693,7 +4697,7 @@
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>#138</t>
+          <t>#136</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4712,7 @@
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Story 5-11</t>
+          <t>Story 5-9</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
@@ -4720,16 +4724,16 @@
         </is>
       </c>
       <c r="F91" s="9" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-11: 기간 리뷰를 다시 생성해도 참가자가 본 이전 버전이 보존된다</t>
+          <t xml:space="preserve">    Story 5-9: 설문 척도 설계·검증 (다문항화·파일럿)</t>
         </is>
       </c>
       <c r="H91" s="13" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="I91" s="10" t="n"/>
@@ -4738,52 +4742,56 @@
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>#273</t>
+          <t>#291</t>
         </is>
       </c>
     </row>
     <row r="92" outlineLevel="1">
-      <c r="A92" s="15" t="n">
+      <c r="A92" s="9" t="n">
         <v>91</v>
       </c>
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C92" s="16" t="inlineStr">
-        <is>
-          <t>Story 5-11</t>
-        </is>
-      </c>
-      <c r="D92" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E92" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F92" s="15" t="n">
-        <v>224</v>
-      </c>
-      <c r="G92" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 기간 리뷰를 다시 생성해도 참여자가 본 이전 버전이 남도록 append-only 이력 테이블 추가</t>
-        </is>
-      </c>
-      <c r="H92" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I92" s="16" t="n"/>
-      <c r="J92" s="15" t="n">
-        <v>273</v>
-      </c>
-      <c r="K92" s="20" t="inlineStr">
-        <is>
-          <t>#224</t>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>Story 5-10</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 5-10: llm.js 피드백 보강 (서버 저장·문구 톤 통일·프롬프트 버전·가드레일 필터)</t>
+        </is>
+      </c>
+      <c r="H92" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>#139</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="K92" s="14" t="inlineStr">
+        <is>
+          <t>#138</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4806,7 @@
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Story 5-12</t>
+          <t>Story 5-11</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
@@ -4810,16 +4818,16 @@
         </is>
       </c>
       <c r="F93" s="9" t="n">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 5-12: 시청 맥락(유입 경로·영상·채널 메타데이터)을 함께 수집한다</t>
-        </is>
-      </c>
-      <c r="H93" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">    Story 5-11: 기간 리뷰를 다시 생성해도 참가자가 본 이전 버전이 보존된다</t>
+        </is>
+      </c>
+      <c r="H93" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I93" s="10" t="n"/>
@@ -4828,7 +4836,7 @@
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>#292</t>
+          <t>#273</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4851,7 @@
       </c>
       <c r="C94" s="16" t="inlineStr">
         <is>
-          <t>Story 5-12</t>
+          <t>Story 5-11</t>
         </is>
       </c>
       <c r="D94" s="15" t="n">
@@ -4855,11 +4863,11 @@
         </is>
       </c>
       <c r="F94" s="15" t="n">
-        <v>178</v>
+        <v>224</v>
       </c>
       <c r="G94" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 영상 시청 이벤트에 유입 경로 라벨링 및 자동재생/클릭 구분 로직 추가</t>
+          <t xml:space="preserve">        feat: 기간 리뷰를 다시 생성해도 참여자가 본 이전 버전이 남도록 append-only 이력 테이블 추가</t>
         </is>
       </c>
       <c r="H94" s="19" t="inlineStr">
@@ -4869,140 +4877,146 @@
       </c>
       <c r="I94" s="16" t="n"/>
       <c r="J94" s="15" t="n">
+        <v>273</v>
+      </c>
+      <c r="K94" s="20" t="inlineStr">
+        <is>
+          <t>#224</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" outlineLevel="2">
+      <c r="A95" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>Story 5-12</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="n">
         <v>292</v>
       </c>
-      <c r="K94" s="20" t="inlineStr">
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 5-12: 시청 맥락(유입 경로·영상·채널 메타데이터)을 함께 수집한다</t>
+        </is>
+      </c>
+      <c r="H95" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I95" s="10" t="n"/>
+      <c r="J95" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="K95" s="14" t="inlineStr">
+        <is>
+          <t>#292</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" outlineLevel="2">
+      <c r="A96" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="inlineStr">
+        <is>
+          <t>Story 5-12</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="n">
+        <v>178</v>
+      </c>
+      <c r="G96" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 영상 시청 이벤트에 유입 경로 라벨링 및 자동재생/클릭 구분 로직 추가</t>
+        </is>
+      </c>
+      <c r="H96" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I96" s="16" t="n"/>
+      <c r="J96" s="15" t="n">
+        <v>292</v>
+      </c>
+      <c r="K96" s="20" t="inlineStr">
         <is>
           <t>#178</t>
         </is>
       </c>
     </row>
-    <row r="95" outlineLevel="2">
-      <c r="A95" s="15" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="16" t="inlineStr">
+    <row r="97" outlineLevel="1">
+      <c r="A97" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>Epic 5</t>
         </is>
       </c>
-      <c r="C95" s="16" t="inlineStr">
+      <c r="C97" s="16" t="inlineStr">
         <is>
           <t>Story 5-12</t>
         </is>
       </c>
-      <c r="D95" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E95" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F95" s="15" t="n">
+      <c r="D97" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="n">
         <v>180</v>
       </c>
-      <c r="G95" s="18" t="inlineStr">
+      <c r="G97" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat:YouTube 영상·채널 메타데이터 수집 확장</t>
         </is>
       </c>
-      <c r="H95" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I95" s="16" t="n"/>
-      <c r="J95" s="15" t="n">
+      <c r="H97" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I97" s="16" t="n"/>
+      <c r="J97" s="15" t="n">
         <v>292</v>
       </c>
-      <c r="K95" s="20" t="inlineStr">
+      <c r="K97" s="20" t="inlineStr">
         <is>
           <t>#180</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" outlineLevel="2">
-      <c r="A96" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="4" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>145</v>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>Epic 6. 본 연구 착수 전 기능 안정화</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="n"/>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="8" t="inlineStr">
-        <is>
-          <t>#145</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" outlineLevel="1">
-      <c r="A97" s="9" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="10" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C97" s="10" t="inlineStr">
-        <is>
-          <t>Story 6-1</t>
-        </is>
-      </c>
-      <c r="D97" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E97" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F97" s="9" t="n">
-        <v>274</v>
-      </c>
-      <c r="G97" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 6-1: 대조군 참가자가 연구 종료 후 6주 누적 리뷰를 열람할 수 있다</t>
-        </is>
-      </c>
-      <c r="H97" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I97" s="10" t="n"/>
-      <c r="J97" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="K97" s="14" t="inlineStr">
-        <is>
-          <t>#274</t>
         </is>
       </c>
     </row>
@@ -5012,12 +5026,12 @@
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Epic 6</t>
+          <t>Epic 5</t>
         </is>
       </c>
       <c r="C98" s="16" t="inlineStr">
         <is>
-          <t>Story 6-1</t>
+          <t>Story 5-12</t>
         </is>
       </c>
       <c r="D98" s="15" t="n">
@@ -5029,11 +5043,11 @@
         </is>
       </c>
       <c r="F98" s="15" t="n">
-        <v>146</v>
+        <v>312</v>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 대조군 period_reviews 사전 생성 활성화</t>
+          <t xml:space="preserve">        feat: 자동재생/클릭 판정 품질 점검과 유입 경로 기준 H2 민감도 분석(백그라운드·자동재생 제외, 검색 유입 제외) 스크립트 추가</t>
         </is>
       </c>
       <c r="H98" s="19" t="inlineStr">
@@ -5041,13 +5055,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I98" s="16" t="n"/>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>#314</t>
+        </is>
+      </c>
       <c r="J98" s="15" t="n">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="K98" s="20" t="inlineStr">
         <is>
-          <t>#146</t>
+          <t>#312</t>
         </is>
       </c>
     </row>
@@ -5057,177 +5075,175 @@
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
+          <t>Epic 5</t>
+        </is>
+      </c>
+      <c r="C99" s="16" t="inlineStr">
+        <is>
+          <t>Story 5-12</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="n">
+        <v>313</v>
+      </c>
+      <c r="G99" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 측정 정의 기준 H2 민감도 분석(시청시간 상한 없음, 유효 시청 상대 컷오프 10%·50%) 스크립트 추가</t>
+        </is>
+      </c>
+      <c r="H99" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>#315</t>
+        </is>
+      </c>
+      <c r="J99" s="15" t="n">
+        <v>292</v>
+      </c>
+      <c r="K99" s="20" t="inlineStr">
+        <is>
+          <t>#313</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" outlineLevel="1">
+      <c r="A100" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C99" s="16" t="inlineStr">
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Epic 6. 본 연구 착수 전 기능 안정화</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="8" t="inlineStr">
+        <is>
+          <t>#145</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" outlineLevel="2">
+      <c r="A101" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
         <is>
           <t>Story 6-1</t>
         </is>
       </c>
-      <c r="D99" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E99" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F99" s="15" t="n">
-        <v>147</v>
-      </c>
-      <c r="G99" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 대조군 6주 리뷰 열람 접근 제어 + 열람 이벤트 로깅</t>
-        </is>
-      </c>
-      <c r="H99" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I99" s="16" t="n"/>
-      <c r="J99" s="15" t="n">
+      <c r="D101" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n">
         <v>274</v>
       </c>
-      <c r="K99" s="20" t="inlineStr">
-        <is>
-          <t>#147</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" outlineLevel="1">
-      <c r="A100" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="16" t="inlineStr">
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 6-1: 대조군 참가자가 연구 종료 후 6주 누적 리뷰를 열람할 수 있다</t>
+        </is>
+      </c>
+      <c r="H101" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I101" s="10" t="n"/>
+      <c r="J101" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="K101" s="14" t="inlineStr">
+        <is>
+          <t>#274</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" outlineLevel="2">
+      <c r="A102" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C100" s="16" t="inlineStr">
+      <c r="C102" s="16" t="inlineStr">
         <is>
           <t>Story 6-1</t>
         </is>
       </c>
-      <c r="D100" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E100" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F100" s="15" t="n">
-        <v>148</v>
-      </c>
-      <c r="G100" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 종료 안내 모달 + 6주 누적 리뷰 화면</t>
-        </is>
-      </c>
-      <c r="H100" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I100" s="16" t="n"/>
-      <c r="J100" s="15" t="n">
+      <c r="D102" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="n">
+        <v>146</v>
+      </c>
+      <c r="G102" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 대조군 period_reviews 사전 생성 활성화</t>
+        </is>
+      </c>
+      <c r="H102" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I102" s="16" t="n"/>
+      <c r="J102" s="15" t="n">
         <v>274</v>
       </c>
-      <c r="K100" s="20" t="inlineStr">
-        <is>
-          <t>#148</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" outlineLevel="2">
-      <c r="A101" s="15" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-1</t>
-        </is>
-      </c>
-      <c r="D101" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E101" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F101" s="15" t="n">
-        <v>159</v>
-      </c>
-      <c r="G101" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 연구 완료 코드 기반 리뷰 열람 게이트</t>
-        </is>
-      </c>
-      <c r="H101" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I101" s="16" t="n"/>
-      <c r="J101" s="15" t="n">
-        <v>274</v>
-      </c>
-      <c r="K101" s="20" t="inlineStr">
-        <is>
-          <t>#159</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" outlineLevel="2">
-      <c r="A102" s="9" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="10" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>Story 6-2</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E102" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F102" s="9" t="n">
-        <v>275</v>
-      </c>
-      <c r="G102" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 6-2: 참가자가 재설치해도 참여코드로 상태를 복구할 수 있다</t>
-        </is>
-      </c>
-      <c r="H102" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I102" s="10" t="n"/>
-      <c r="J102" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="K102" s="14" t="inlineStr">
-        <is>
-          <t>#275</t>
+      <c r="K102" s="20" t="inlineStr">
+        <is>
+          <t>#146</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5258,7 @@
       </c>
       <c r="C103" s="16" t="inlineStr">
         <is>
-          <t>Story 6-2</t>
+          <t>Story 6-1</t>
         </is>
       </c>
       <c r="D103" s="15" t="n">
@@ -5254,11 +5270,11 @@
         </is>
       </c>
       <c r="F103" s="15" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참여코드 기반 재설치 복구</t>
+          <t xml:space="preserve">        feat: 대조군 6주 리뷰 열람 접근 제어 + 열람 이벤트 로깅</t>
         </is>
       </c>
       <c r="H103" s="19" t="inlineStr">
@@ -5268,11 +5284,11 @@
       </c>
       <c r="I103" s="16" t="n"/>
       <c r="J103" s="15" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K103" s="20" t="inlineStr">
         <is>
-          <t>#149</t>
+          <t>#147</t>
         </is>
       </c>
     </row>
@@ -5287,127 +5303,127 @@
       </c>
       <c r="C104" s="16" t="inlineStr">
         <is>
-          <t>Story 6-2</t>
+          <t>Story 6-1</t>
         </is>
       </c>
       <c r="D104" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E104" s="22" t="inlineStr">
-        <is>
-          <t>Bug</t>
+      <c r="E104" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
         </is>
       </c>
       <c r="F104" s="15" t="n">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 참여자 등록 시 시간대가 없는 installDate를 거부하고 저장 형식을 UTC ISO로 통일</t>
-        </is>
-      </c>
-      <c r="H104" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 종료 안내 모달 + 6주 누적 리뷰 화면</t>
+        </is>
+      </c>
+      <c r="H104" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I104" s="16" t="n"/>
       <c r="J104" s="15" t="n">
+        <v>274</v>
+      </c>
+      <c r="K104" s="20" t="inlineStr">
+        <is>
+          <t>#148</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" outlineLevel="1">
+      <c r="A105" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C105" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-1</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="n">
+        <v>159</v>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 연구 완료 코드 기반 리뷰 열람 게이트</t>
+        </is>
+      </c>
+      <c r="H105" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I105" s="16" t="n"/>
+      <c r="J105" s="15" t="n">
+        <v>274</v>
+      </c>
+      <c r="K105" s="20" t="inlineStr">
+        <is>
+          <t>#159</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" outlineLevel="2">
+      <c r="A106" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>Story 6-2</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="K104" s="20" t="inlineStr">
-        <is>
-          <t>#223</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" outlineLevel="1">
-      <c r="A105" s="9" t="n">
-        <v>104</v>
-      </c>
-      <c r="B105" s="10" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C105" s="10" t="inlineStr">
-        <is>
-          <t>Story 6-3</t>
-        </is>
-      </c>
-      <c r="D105" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E105" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F105" s="9" t="n">
-        <v>276</v>
-      </c>
-      <c r="G105" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 6-3: 참가자가 자정 기준 하루 누적 리뷰를 확인할 수 있다</t>
-        </is>
-      </c>
-      <c r="H105" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I105" s="10" t="n"/>
-      <c r="J105" s="9" t="n">
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 6-2: 참가자가 재설치해도 참여코드로 상태를 복구할 수 있다</t>
+        </is>
+      </c>
+      <c r="H106" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I106" s="10" t="n"/>
+      <c r="J106" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K105" s="14" t="inlineStr">
-        <is>
-          <t>#276</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" outlineLevel="2">
-      <c r="A106" s="15" t="n">
-        <v>105</v>
-      </c>
-      <c r="B106" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C106" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-3</t>
-        </is>
-      </c>
-      <c r="D106" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E106" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F106" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="G106" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 세션-종료 트리거를 오늘 누적 계산으로 통합</t>
-        </is>
-      </c>
-      <c r="H106" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I106" s="16" t="n"/>
-      <c r="J106" s="15" t="n">
-        <v>276</v>
-      </c>
-      <c r="K106" s="20" t="inlineStr">
-        <is>
-          <t>#152</t>
+      <c r="K106" s="14" t="inlineStr">
+        <is>
+          <t>#275</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5438,7 @@
       </c>
       <c r="C107" s="16" t="inlineStr">
         <is>
-          <t>Story 6-3</t>
+          <t>Story 6-2</t>
         </is>
       </c>
       <c r="D107" s="15" t="n">
@@ -5434,11 +5450,11 @@
         </is>
       </c>
       <c r="F107" s="15" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G107" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 자정 경계 처리 + "어제 돌아보기" 리빌 애니메이션</t>
+          <t xml:space="preserve">        feat: 참여코드 기반 재설치 복구</t>
         </is>
       </c>
       <c r="H107" s="19" t="inlineStr">
@@ -5448,11 +5464,11 @@
       </c>
       <c r="I107" s="16" t="n"/>
       <c r="J107" s="15" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K107" s="20" t="inlineStr">
         <is>
-          <t>#153</t>
+          <t>#149</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5483,7 @@
       </c>
       <c r="C108" s="16" t="inlineStr">
         <is>
-          <t>Story 6-3</t>
+          <t>Story 6-2</t>
         </is>
       </c>
       <c r="D108" s="15" t="n">
@@ -5475,15 +5491,15 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F108" s="15" t="n">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 리뷰 카드 헤드라인 문구 스코프별 분기</t>
+          <t xml:space="preserve">        fix: 참여자 등록 시 시간대가 없는 installDate를 거부하고 저장 형식을 UTC ISO로 통일</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
@@ -5493,11 +5509,11 @@
       </c>
       <c r="I108" s="16" t="n"/>
       <c r="J108" s="15" t="n">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K108" s="20" t="inlineStr">
         <is>
-          <t>#154</t>
+          <t>#223</t>
         </is>
       </c>
     </row>
@@ -5512,127 +5528,135 @@
       </c>
       <c r="C109" s="16" t="inlineStr">
         <is>
+          <t>Story 6-2</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>332</v>
+      </c>
+      <c r="G109" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 재설치 후 같은 날 오늘 리뷰 카드가 보이지 않음</t>
+        </is>
+      </c>
+      <c r="H109" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>#333</t>
+        </is>
+      </c>
+      <c r="J109" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="K109" s="20" t="inlineStr">
+        <is>
+          <t>#332</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" outlineLevel="1">
+      <c r="A110" s="15" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C110" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-2</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="n">
+        <v>339</v>
+      </c>
+      <c r="G110" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 재설치 후 지난 날짜와 오늘의 재생한 영상 목록에 이전 기록이 보이지 않음</t>
+        </is>
+      </c>
+      <c r="H110" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>#341</t>
+        </is>
+      </c>
+      <c r="J110" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="K110" s="20" t="inlineStr">
+        <is>
+          <t>#339</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" outlineLevel="2">
+      <c r="A111" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="10" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
           <t>Story 6-3</t>
         </is>
       </c>
-      <c r="D109" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E109" s="22" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="F109" s="15" t="n">
-        <v>261</v>
-      </c>
-      <c r="G109" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        bug: 피드백 생성 완료 직후 날짜 이동 시 "오늘" 탭이 갱신되지 않음</t>
-        </is>
-      </c>
-      <c r="H109" s="24" t="inlineStr">
+      <c r="D111" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F111" s="9" t="n">
+        <v>276</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 6-3: 참가자가 자정 기준 하루 누적 리뷰를 확인할 수 있다</t>
+        </is>
+      </c>
+      <c r="H111" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I109" s="16" t="n"/>
-      <c r="J109" s="15" t="n">
-        <v>276</v>
-      </c>
-      <c r="K109" s="20" t="inlineStr">
-        <is>
-          <t>#261</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" outlineLevel="1">
-      <c r="A110" s="9" t="n">
-        <v>109</v>
-      </c>
-      <c r="B110" s="10" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>Story 6-4</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E110" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F110" s="9" t="n">
-        <v>277</v>
-      </c>
-      <c r="G110" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 6-4: 네트워크·인증 오류가 나도 데이터 전송과 참여자 등록이 자동 복구된다</t>
-        </is>
-      </c>
-      <c r="H110" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I110" s="10" t="n"/>
-      <c r="J110" s="9" t="n">
+      <c r="I111" s="10" t="n"/>
+      <c r="J111" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K110" s="14" t="inlineStr">
-        <is>
-          <t>#277</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" outlineLevel="2">
-      <c r="A111" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C111" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-4</t>
-        </is>
-      </c>
-      <c r="D111" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E111" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F111" s="15" t="n">
-        <v>193</v>
-      </c>
-      <c r="G111" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 전송 큐 재시도에 큐 레벨 fail-fast·재진입 가드·타임아웃 도입</t>
-        </is>
-      </c>
-      <c r="H111" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I111" s="16" t="n"/>
-      <c r="J111" s="15" t="n">
-        <v>277</v>
-      </c>
-      <c r="K111" s="20" t="inlineStr">
-        <is>
-          <t>#193</t>
+      <c r="K111" s="14" t="inlineStr">
+        <is>
+          <t>#276</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5671,7 @@
       </c>
       <c r="C112" s="16" t="inlineStr">
         <is>
-          <t>Story 6-4</t>
+          <t>Story 6-3</t>
         </is>
       </c>
       <c r="D112" s="15" t="n">
@@ -5659,11 +5683,11 @@
         </is>
       </c>
       <c r="F112" s="15" t="n">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="G112" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참여자 등록 게이트를 백그라운드에서 자동 복구하고 403 무효화 경로 추가</t>
+          <t xml:space="preserve">        feat: 세션-종료 트리거를 오늘 누적 계산으로 통합</t>
         </is>
       </c>
       <c r="H112" s="19" t="inlineStr">
@@ -5673,140 +5697,146 @@
       </c>
       <c r="I112" s="16" t="n"/>
       <c r="J112" s="15" t="n">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="K112" s="20" t="inlineStr">
         <is>
-          <t>#196</t>
+          <t>#152</t>
         </is>
       </c>
     </row>
     <row r="113" outlineLevel="2">
-      <c r="A113" s="9" t="n">
+      <c r="A113" s="15" t="n">
         <v>112</v>
       </c>
-      <c r="B113" s="10" t="inlineStr">
+      <c r="B113" s="16" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C113" s="10" t="inlineStr">
-        <is>
-          <t>Story 6-5</t>
-        </is>
-      </c>
-      <c r="D113" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F113" s="9" t="n">
-        <v>278</v>
-      </c>
-      <c r="G113" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 6-5: 참가자가 오류 발생 시 팝업에서 안내를 볼 수 있다</t>
-        </is>
-      </c>
-      <c r="H113" s="23" t="inlineStr">
+      <c r="C113" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-3</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>153</v>
+      </c>
+      <c r="G113" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 자정 경계 처리 + "어제 돌아보기" 리빌 애니메이션</t>
+        </is>
+      </c>
+      <c r="H113" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I113" s="16" t="n"/>
+      <c r="J113" s="15" t="n">
+        <v>276</v>
+      </c>
+      <c r="K113" s="20" t="inlineStr">
+        <is>
+          <t>#153</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" outlineLevel="2" ht="26.25" customHeight="1">
+      <c r="A114" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C114" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-3</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="n">
+        <v>154</v>
+      </c>
+      <c r="G114" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 리뷰 카드 헤드라인 문구 스코프별 분기</t>
+        </is>
+      </c>
+      <c r="H114" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I114" s="16" t="n"/>
+      <c r="J114" s="15" t="n">
+        <v>276</v>
+      </c>
+      <c r="K114" s="20" t="inlineStr">
+        <is>
+          <t>#154</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" outlineLevel="1">
+      <c r="A115" s="15" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C115" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-3</t>
+        </is>
+      </c>
+      <c r="D115" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>261</v>
+      </c>
+      <c r="G115" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        bug: 피드백 생성 완료 직후 날짜 이동 시 "오늘" 탭이 갱신되지 않음</t>
+        </is>
+      </c>
+      <c r="H115" s="19" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I113" s="10" t="n"/>
-      <c r="J113" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="K113" s="14" t="inlineStr">
-        <is>
-          <t>#278</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" outlineLevel="2" ht="26.25" customHeight="1">
-      <c r="A114" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="4" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C114" s="4" t="n"/>
-      <c r="D114" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>202</v>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>Epic 7. 관측 체계 구축 및 운영</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I114" s="4" t="n"/>
-      <c r="J114" s="3" t="n"/>
-      <c r="K114" s="8" t="inlineStr">
-        <is>
-          <t>#202</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1">
-      <c r="A115" s="9" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="10" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C115" s="10" t="inlineStr">
-        <is>
-          <t>Story 7-1</t>
-        </is>
-      </c>
-      <c r="D115" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F115" s="9" t="n">
-        <v>172</v>
-      </c>
-      <c r="G115" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 7-1: 운영자가 서버·cron·결측 이상을 즉시 알림으로 받을 수 있다(최소 관제 체계(MVM) 구축)</t>
-        </is>
-      </c>
-      <c r="H115" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I115" s="10" t="n"/>
-      <c r="J115" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="K115" s="14" t="inlineStr">
-        <is>
-          <t>#172</t>
+      <c r="I115" s="16" t="n"/>
+      <c r="J115" s="15" t="n">
+        <v>276</v>
+      </c>
+      <c r="K115" s="20" t="inlineStr">
+        <is>
+          <t>#261</t>
         </is>
       </c>
     </row>
@@ -5816,12 +5846,12 @@
       </c>
       <c r="B116" s="16" t="inlineStr">
         <is>
-          <t>Epic 7</t>
+          <t>Epic 6</t>
         </is>
       </c>
       <c r="C116" s="16" t="inlineStr">
         <is>
-          <t>Story 7-1</t>
+          <t>Story 6-3</t>
         </is>
       </c>
       <c r="D116" s="15" t="n">
@@ -5829,15 +5859,15 @@
       </c>
       <c r="E116" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F116" s="15" t="n">
-        <v>192</v>
+        <v>318</v>
       </c>
       <c r="G116" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 접근 로그에 실제 API 경로 기록 및 error-monitor 알림을 /api/* 4xx로 한정</t>
+          <t xml:space="preserve">        fix: 베이스라인이 끝난 뒤 하루 돌아보기 탭의 지난 날짜에 Gemini 피드백이 보이지 않음</t>
         </is>
       </c>
       <c r="H116" s="19" t="inlineStr">
@@ -5845,13 +5875,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I116" s="16" t="n"/>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>#320</t>
+        </is>
+      </c>
       <c r="J116" s="15" t="n">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="K116" s="20" t="inlineStr">
         <is>
-          <t>#192</t>
+          <t>#318</t>
         </is>
       </c>
     </row>
@@ -5861,12 +5895,12 @@
       </c>
       <c r="B117" s="16" t="inlineStr">
         <is>
-          <t>Epic 7</t>
+          <t>Epic 6</t>
         </is>
       </c>
       <c r="C117" s="16" t="inlineStr">
         <is>
-          <t>Story 7-1</t>
+          <t>Story 6-3</t>
         </is>
       </c>
       <c r="D117" s="15" t="n">
@@ -5874,15 +5908,15 @@
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F117" s="15" t="n">
-        <v>204</v>
+        <v>319</v>
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog Monitor로 세션 API 지연·Agent 무응답 알림 추가</t>
+          <t xml:space="preserve">        feat: "어제 돌아보기" 슬라이드를 없애고, 확인하지 않은 오늘 리뷰가 있을 때 팝업을 열면 바로 그 리뷰가 보이게 함</t>
         </is>
       </c>
       <c r="H117" s="19" t="inlineStr">
@@ -5890,13 +5924,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I117" s="16" t="n"/>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>#322</t>
+        </is>
+      </c>
       <c r="J117" s="15" t="n">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="K117" s="20" t="inlineStr">
         <is>
-          <t>#204</t>
+          <t>#319</t>
         </is>
       </c>
     </row>
@@ -5906,12 +5944,12 @@
       </c>
       <c r="B118" s="16" t="inlineStr">
         <is>
-          <t>Epic 7</t>
+          <t>Epic 6</t>
         </is>
       </c>
       <c r="C118" s="16" t="inlineStr">
         <is>
-          <t>Story 7-1</t>
+          <t>Story 6-3</t>
         </is>
       </c>
       <c r="D118" s="15" t="n">
@@ -5919,15 +5957,15 @@
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F118" s="15" t="n">
-        <v>205</v>
+        <v>336</v>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: LLM fallback 비율·Gemini 응답 시간을 Datadog 커스텀 메트릭으로 추세 감시</t>
+          <t xml:space="preserve">        fix: 자정 직전에 본 영상의 세션이 다음 날 "오늘"로 잡힘</t>
         </is>
       </c>
       <c r="H118" s="19" t="inlineStr">
@@ -5935,103 +5973,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I118" s="16" t="n"/>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>#340</t>
+        </is>
+      </c>
       <c r="J118" s="15" t="n">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="K118" s="20" t="inlineStr">
         <is>
-          <t>#205</t>
+          <t>#336</t>
         </is>
       </c>
     </row>
     <row r="119" outlineLevel="2">
-      <c r="A119" s="15" t="n">
+      <c r="A119" s="9" t="n">
         <v>118</v>
       </c>
-      <c r="B119" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C119" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-1</t>
-        </is>
-      </c>
-      <c r="D119" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E119" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F119" s="15" t="n">
-        <v>206</v>
-      </c>
-      <c r="G119" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 참가자별 결측 감지 cron 가동과 결측 의심 시 인원수 알림</t>
-        </is>
-      </c>
-      <c r="H119" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I119" s="16" t="n"/>
-      <c r="J119" s="15" t="n">
-        <v>172</v>
-      </c>
-      <c r="K119" s="20" t="inlineStr">
-        <is>
-          <t>#206</t>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>Story 6-4</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F119" s="9" t="n">
+        <v>277</v>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 6-4: 네트워크·인증 오류가 나도 데이터 전송과 참여자 등록이 자동 복구된다</t>
+        </is>
+      </c>
+      <c r="H119" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="n"/>
+      <c r="J119" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="K119" s="14" t="inlineStr">
+        <is>
+          <t>#277</t>
         </is>
       </c>
     </row>
     <row r="120" outlineLevel="2">
-      <c r="A120" s="9" t="n">
+      <c r="A120" s="15" t="n">
         <v>119</v>
       </c>
-      <c r="B120" s="10" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C120" s="10" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E120" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F120" s="9" t="n">
-        <v>279</v>
-      </c>
-      <c r="G120" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 7-2: 운영자가 오류 원인을 로그·트레이스로 추적할 수 있다</t>
-        </is>
-      </c>
-      <c r="H120" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I120" s="10" t="n"/>
-      <c r="J120" s="9" t="n">
-        <v>202</v>
-      </c>
-      <c r="K120" s="14" t="inlineStr">
-        <is>
-          <t>#279</t>
+      <c r="B120" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-4</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>193</v>
+      </c>
+      <c r="G120" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 전송 큐 재시도에 큐 레벨 fail-fast·재진입 가드·타임아웃 도입</t>
+        </is>
+      </c>
+      <c r="H120" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I120" s="16" t="n"/>
+      <c r="J120" s="15" t="n">
+        <v>277</v>
+      </c>
+      <c r="K120" s="20" t="inlineStr">
+        <is>
+          <t>#193</t>
         </is>
       </c>
     </row>
@@ -6041,12 +6083,12 @@
       </c>
       <c r="B121" s="16" t="inlineStr">
         <is>
-          <t>Epic 7</t>
+          <t>Epic 6</t>
         </is>
       </c>
       <c r="C121" s="16" t="inlineStr">
         <is>
-          <t>Story 7-2</t>
+          <t>Story 6-4</t>
         </is>
       </c>
       <c r="D121" s="15" t="n">
@@ -6058,11 +6100,11 @@
         </is>
       </c>
       <c r="F121" s="15" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 확장 프로그램 오류를 연구 서버로 원격 수집</t>
+          <t xml:space="preserve">        feat: 참여자 등록 게이트를 백그라운드에서 자동 복구하고 403 무효화 경로 추가</t>
         </is>
       </c>
       <c r="H121" s="19" t="inlineStr">
@@ -6072,11 +6114,11 @@
       </c>
       <c r="I121" s="16" t="n"/>
       <c r="J121" s="15" t="n">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="K121" s="20" t="inlineStr">
         <is>
-          <t>#203</t>
+          <t>#196</t>
         </is>
       </c>
     </row>
@@ -6086,177 +6128,175 @@
       </c>
       <c r="B122" s="16" t="inlineStr">
         <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C122" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-4</t>
+        </is>
+      </c>
+      <c r="D122" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F122" s="15" t="n">
+        <v>334</v>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 확장 저장 한도를 풀어 많이 보는 참여자의 영상 기록이 끊기지 않게 하고, 1분 재시도 틱의 저장소 조회 로직 개선</t>
+        </is>
+      </c>
+      <c r="H122" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>#337</t>
+        </is>
+      </c>
+      <c r="J122" s="15" t="n">
+        <v>277</v>
+      </c>
+      <c r="K122" s="20" t="inlineStr">
+        <is>
+          <t>#334</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" outlineLevel="1">
+      <c r="A123" s="9" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="10" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C123" s="10" t="inlineStr">
+        <is>
+          <t>Story 6-5</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F123" s="9" t="n">
+        <v>278</v>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 6-5: 참가자가 오류 발생 시 팝업에서 안내를 볼 수 있다</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I123" s="10" t="n"/>
+      <c r="J123" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="K123" s="14" t="inlineStr">
+        <is>
+          <t>#278</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C122" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F122" s="15" t="n">
-        <v>225</v>
-      </c>
-      <c r="G122" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: Datadog에서 가명 사용자 ID(anonymousId)로 로그·요청을 조회할 수 있게 UUID 마스킹 해제</t>
-        </is>
-      </c>
-      <c r="H122" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I122" s="16" t="n"/>
-      <c r="J122" s="15" t="n">
-        <v>279</v>
-      </c>
-      <c r="K122" s="20" t="inlineStr">
-        <is>
-          <t>#225</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" outlineLevel="1">
-      <c r="A123" s="15" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="16" t="inlineStr">
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>202</v>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>Epic 7. 관측 체계 구축 및 운영</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="n"/>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>#202</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" outlineLevel="1">
+      <c r="A125" s="9" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="10" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C123" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D123" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E123" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F123" s="15" t="n">
-        <v>226</v>
-      </c>
-      <c r="G123" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 서버 예외의 스택 트레이스를 확인할 수 있게 하기</t>
-        </is>
-      </c>
-      <c r="H123" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I123" s="16" t="n"/>
-      <c r="J123" s="15" t="n">
-        <v>279</v>
-      </c>
-      <c r="K123" s="20" t="inlineStr">
-        <is>
-          <t>#226</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="15" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C124" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D124" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E124" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F124" s="15" t="n">
-        <v>227</v>
-      </c>
-      <c r="G124" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 서버 로그 줄에 trace ID를 넣어 Datadog Logs와 APM trace를 연결</t>
-        </is>
-      </c>
-      <c r="H124" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I124" s="16" t="n"/>
-      <c r="J124" s="15" t="n">
-        <v>279</v>
-      </c>
-      <c r="K124" s="20" t="inlineStr">
-        <is>
-          <t>#227</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" outlineLevel="1">
-      <c r="A125" s="15" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C125" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D125" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E125" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F125" s="15" t="n">
-        <v>228</v>
-      </c>
-      <c r="G125" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 지문·anonymousId·참여 코드로 참여자 상태를 조회하는 읽기 전용 스크립트</t>
-        </is>
-      </c>
-      <c r="H125" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I125" s="16" t="n"/>
-      <c r="J125" s="15" t="n">
-        <v>279</v>
-      </c>
-      <c r="K125" s="20" t="inlineStr">
-        <is>
-          <t>#228</t>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>Story 7-1</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F125" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 7-1: 운영자가 서버·cron·결측 이상을 즉시 알림으로 받을 수 있다(최소 관제 체계(MVM) 구축)</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I125" s="10" t="n"/>
+      <c r="J125" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="K125" s="14" t="inlineStr">
+        <is>
+          <t>#172</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6311,7 @@
       </c>
       <c r="C126" s="16" t="inlineStr">
         <is>
-          <t>Story 7-2</t>
+          <t>Story 7-1</t>
         </is>
       </c>
       <c r="D126" s="15" t="n">
@@ -6283,11 +6323,11 @@
         </is>
       </c>
       <c r="F126" s="15" t="n">
-        <v>267</v>
+        <v>192</v>
       </c>
       <c r="G126" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: Datadog Agent 설치 및 Log Management 연동</t>
+          <t xml:space="preserve">        feat: 접근 로그에 실제 API 경로 기록 및 error-monitor 알림을 /api/* 4xx로 한정</t>
         </is>
       </c>
       <c r="H126" s="19" t="inlineStr">
@@ -6297,11 +6337,11 @@
       </c>
       <c r="I126" s="16" t="n"/>
       <c r="J126" s="15" t="n">
-        <v>279</v>
+        <v>172</v>
       </c>
       <c r="K126" s="20" t="inlineStr">
         <is>
-          <t>#267</t>
+          <t>#192</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6356,7 @@
       </c>
       <c r="C127" s="16" t="inlineStr">
         <is>
-          <t>Story 7-2</t>
+          <t>Story 7-1</t>
         </is>
       </c>
       <c r="D127" s="15" t="n">
@@ -6328,11 +6368,11 @@
         </is>
       </c>
       <c r="F127" s="15" t="n">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog APM(dd-trace) 계측 도입</t>
+          <t xml:space="preserve">        feat: Datadog Monitor로 세션 API 지연·Agent 무응답 알림 추가</t>
         </is>
       </c>
       <c r="H127" s="19" t="inlineStr">
@@ -6342,11 +6382,11 @@
       </c>
       <c r="I127" s="16" t="n"/>
       <c r="J127" s="15" t="n">
-        <v>279</v>
+        <v>172</v>
       </c>
       <c r="K127" s="20" t="inlineStr">
         <is>
-          <t>#268</t>
+          <t>#204</t>
         </is>
       </c>
     </row>
@@ -6359,21 +6399,25 @@
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C128" s="16" t="n"/>
+      <c r="C128" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-1</t>
+        </is>
+      </c>
       <c r="D128" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E128" s="22" t="inlineStr">
-        <is>
-          <t>Bug</t>
+        <v>3</v>
+      </c>
+      <c r="E128" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
         </is>
       </c>
       <c r="F128" s="15" t="n">
-        <v>232</v>
+        <v>205</v>
       </c>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    fix: 본문 필드가 문자열이 아닐 때 서버가 500을 반환하는 문제</t>
+          <t xml:space="preserve">        feat: LLM fallback 비율·Gemini 응답 시간을 Datadog 커스텀 메트릭으로 추세 감시</t>
         </is>
       </c>
       <c r="H128" s="19" t="inlineStr">
@@ -6383,50 +6427,56 @@
       </c>
       <c r="I128" s="16" t="n"/>
       <c r="J128" s="15" t="n">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="K128" s="20" t="inlineStr">
         <is>
-          <t>#232</t>
+          <t>#205</t>
         </is>
       </c>
     </row>
     <row r="129" outlineLevel="1">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="15" t="n">
         <v>128</v>
       </c>
-      <c r="B129" s="4" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="n"/>
-      <c r="D129" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E129" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>207</v>
-      </c>
-      <c r="G129" s="6" t="inlineStr">
-        <is>
-          <t>Epic 8. 본 연구 착수 전 IRB 정합성 확보 및 시스템 정비</t>
-        </is>
-      </c>
-      <c r="H129" s="25" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I129" s="4" t="n"/>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="8" t="inlineStr">
-        <is>
-          <t>#207</t>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-1</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F129" s="15" t="n">
+        <v>206</v>
+      </c>
+      <c r="G129" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 참가자별 결측 감지 cron 가동과 결측 의심 시 인원수 알림</t>
+        </is>
+      </c>
+      <c r="H129" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I129" s="16" t="n"/>
+      <c r="J129" s="15" t="n">
+        <v>172</v>
+      </c>
+      <c r="K129" s="20" t="inlineStr">
+        <is>
+          <t>#206</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6486,12 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Story 8-1</t>
+          <t>Story 7-2</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
@@ -6453,25 +6503,25 @@
         </is>
       </c>
       <c r="F130" s="9" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 8-1: 연구 기간이 끝나면 수집·전송이 자동으로 멈추고 참가자에게 안내된다</t>
-        </is>
-      </c>
-      <c r="H130" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">    Story 7-2: 운영자가 오류 원인을 로그·트레이스로 추적할 수 있다</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I130" s="10" t="n"/>
       <c r="J130" s="9" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>#280</t>
+          <t>#279</t>
         </is>
       </c>
     </row>
@@ -6481,12 +6531,12 @@
       </c>
       <c r="B131" s="16" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="C131" s="16" t="inlineStr">
         <is>
-          <t>Story 8-1</t>
+          <t>Story 7-2</t>
         </is>
       </c>
       <c r="D131" s="15" t="n">
@@ -6498,11 +6548,11 @@
         </is>
       </c>
       <c r="F131" s="15" t="n">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 종료 후 수집·생성 중단 + "오늘" 탭 마지막 날짜 고정</t>
+          <t xml:space="preserve">        feat: 확장 프로그램 오류를 연구 서버로 원격 수집</t>
         </is>
       </c>
       <c r="H131" s="19" t="inlineStr">
@@ -6512,11 +6562,11 @@
       </c>
       <c r="I131" s="16" t="n"/>
       <c r="J131" s="15" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K131" s="20" t="inlineStr">
         <is>
-          <t>#160</t>
+          <t>#203</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6576,12 @@
       </c>
       <c r="B132" s="16" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="C132" s="16" t="inlineStr">
         <is>
-          <t>Story 8-1</t>
+          <t>Story 7-2</t>
         </is>
       </c>
       <c r="D132" s="15" t="n">
@@ -6543,11 +6593,11 @@
         </is>
       </c>
       <c r="F132" s="15" t="n">
-        <v>197</v>
+        <v>225</v>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 기간 종료 시 확장 프로그램 수집·전송 자동 중단 및 제거 안내</t>
+          <t xml:space="preserve">        feat: Datadog에서 가명 사용자 ID(anonymousId)로 로그·요청을 조회할 수 있게 UUID 마스킹 해제</t>
         </is>
       </c>
       <c r="H132" s="19" t="inlineStr">
@@ -6557,11 +6607,11 @@
       </c>
       <c r="I132" s="16" t="n"/>
       <c r="J132" s="15" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K132" s="20" t="inlineStr">
         <is>
-          <t>#197</t>
+          <t>#225</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6621,12 @@
       </c>
       <c r="B133" s="16" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="C133" s="16" t="inlineStr">
         <is>
-          <t>Story 8-1</t>
+          <t>Story 7-2</t>
         </is>
       </c>
       <c r="D133" s="15" t="n">
@@ -6588,11 +6638,11 @@
         </is>
       </c>
       <c r="F133" s="15" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 기간에 따라 달라지는 문구를 상수에서 생성하고 기간 상수 일치를 테스트로 고정</t>
+          <t xml:space="preserve">        feat: 서버 예외의 스택 트레이스를 확인할 수 있게 하기</t>
         </is>
       </c>
       <c r="H133" s="19" t="inlineStr">
@@ -6602,56 +6652,56 @@
       </c>
       <c r="I133" s="16" t="n"/>
       <c r="J133" s="15" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="K133" s="20" t="inlineStr">
         <is>
-          <t>#210</t>
+          <t>#226</t>
         </is>
       </c>
     </row>
     <row r="134" outlineLevel="2">
-      <c r="A134" s="9" t="n">
+      <c r="A134" s="15" t="n">
         <v>133</v>
       </c>
-      <c r="B134" s="10" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C134" s="10" t="inlineStr">
-        <is>
-          <t>Story 8-2</t>
-        </is>
-      </c>
-      <c r="D134" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E134" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F134" s="9" t="n">
-        <v>281</v>
-      </c>
-      <c r="G134" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 8-2: 참가자에게 집단(실험/대조) 정보가 노출되지 않는다</t>
-        </is>
-      </c>
-      <c r="H134" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I134" s="10" t="n"/>
-      <c r="J134" s="9" t="n">
-        <v>207</v>
-      </c>
-      <c r="K134" s="14" t="inlineStr">
-        <is>
-          <t>#281</t>
+      <c r="B134" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C134" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-2</t>
+        </is>
+      </c>
+      <c r="D134" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F134" s="15" t="n">
+        <v>227</v>
+      </c>
+      <c r="G134" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 서버 로그 줄에 trace ID를 넣어 Datadog Logs와 APM trace를 연결</t>
+        </is>
+      </c>
+      <c r="H134" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I134" s="16" t="n"/>
+      <c r="J134" s="15" t="n">
+        <v>279</v>
+      </c>
+      <c r="K134" s="20" t="inlineStr">
+        <is>
+          <t>#227</t>
         </is>
       </c>
     </row>
@@ -6661,12 +6711,12 @@
       </c>
       <c r="B135" s="16" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="C135" s="16" t="inlineStr">
         <is>
-          <t>Story 8-2</t>
+          <t>Story 7-2</t>
         </is>
       </c>
       <c r="D135" s="15" t="n">
@@ -6678,11 +6728,11 @@
         </is>
       </c>
       <c r="F135" s="15" t="n">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참여코드에서 집단 표식 제거</t>
+          <t xml:space="preserve">        feat: 지문·anonymousId·참여 코드로 참여자 상태를 조회하는 읽기 전용 스크립트</t>
         </is>
       </c>
       <c r="H135" s="19" t="inlineStr">
@@ -6692,56 +6742,56 @@
       </c>
       <c r="I135" s="16" t="n"/>
       <c r="J135" s="15" t="n">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="K135" s="20" t="inlineStr">
         <is>
-          <t>#209</t>
+          <t>#228</t>
         </is>
       </c>
     </row>
     <row r="136" outlineLevel="2">
-      <c r="A136" s="9" t="n">
+      <c r="A136" s="15" t="n">
         <v>135</v>
       </c>
-      <c r="B136" s="10" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
-      <c r="D136" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E136" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F136" s="9" t="n">
-        <v>218</v>
-      </c>
-      <c r="G136" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 8-3: 화면·피드백·분석의 시청 집계 기준을 유효 시청·시청 시간으로 통일한다</t>
-        </is>
-      </c>
-      <c r="H136" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I136" s="10" t="n"/>
-      <c r="J136" s="9" t="n">
-        <v>207</v>
-      </c>
-      <c r="K136" s="14" t="inlineStr">
-        <is>
-          <t>#218</t>
+      <c r="B136" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C136" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-2</t>
+        </is>
+      </c>
+      <c r="D136" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F136" s="15" t="n">
+        <v>267</v>
+      </c>
+      <c r="G136" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: Datadog Agent 설치 및 Log Management 연동</t>
+        </is>
+      </c>
+      <c r="H136" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I136" s="16" t="n"/>
+      <c r="J136" s="15" t="n">
+        <v>279</v>
+      </c>
+      <c r="K136" s="20" t="inlineStr">
+        <is>
+          <t>#267</t>
         </is>
       </c>
     </row>
@@ -6751,12 +6801,12 @@
       </c>
       <c r="B137" s="16" t="inlineStr">
         <is>
-          <t>Epic 8</t>
+          <t>Epic 7</t>
         </is>
       </c>
       <c r="C137" s="16" t="inlineStr">
         <is>
-          <t>Story 8-3</t>
+          <t>Story 7-2</t>
         </is>
       </c>
       <c r="D137" s="15" t="n">
@@ -6768,11 +6818,11 @@
         </is>
       </c>
       <c r="F137" s="15" t="n">
-        <v>211</v>
+        <v>268</v>
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 기간별 리뷰 첫 줄에 분야별 비중과 지난 구간 대비 변화를 사실 문장으로 추가</t>
+          <t xml:space="preserve">        feat: Datadog APM(dd-trace) 계측 도입</t>
         </is>
       </c>
       <c r="H137" s="19" t="inlineStr">
@@ -6782,11 +6832,11 @@
       </c>
       <c r="I137" s="16" t="n"/>
       <c r="J137" s="15" t="n">
-        <v>218</v>
+        <v>279</v>
       </c>
       <c r="K137" s="20" t="inlineStr">
         <is>
-          <t>#211</t>
+          <t>#268</t>
         </is>
       </c>
     </row>
@@ -6796,28 +6846,24 @@
       </c>
       <c r="B138" s="16" t="inlineStr">
         <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C138" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C138" s="16" t="n"/>
       <c r="D138" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F138" s="15" t="n">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="G138" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 팝업 화면 숫자를 서버 집계 기준으로 통일하고 기간별 탭을 분야별 시청 시간 꺾은선으로 교체</t>
+          <t xml:space="preserve">    fix: 본문 필드가 문자열이 아닐 때 서버가 500을 반환하는 문제</t>
         </is>
       </c>
       <c r="H138" s="19" t="inlineStr">
@@ -6827,101 +6873,95 @@
       </c>
       <c r="I138" s="16" t="n"/>
       <c r="J138" s="15" t="n">
-        <v>218</v>
+        <v>202</v>
       </c>
       <c r="K138" s="20" t="inlineStr">
         <is>
-          <t>#217</t>
+          <t>#232</t>
         </is>
       </c>
     </row>
     <row r="139" outlineLevel="1">
-      <c r="A139" s="15" t="n">
+      <c r="A139" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="B139" s="16" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C139" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
-      <c r="D139" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E139" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F139" s="15" t="n">
-        <v>253</v>
-      </c>
-      <c r="G139" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        docs: 시청 집계 기준·화면 지표 결정을 기록하고 사전등록 문서에 반영</t>
-        </is>
-      </c>
-      <c r="H139" s="24" t="inlineStr">
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>207</v>
+      </c>
+      <c r="G139" s="6" t="inlineStr">
+        <is>
+          <t>Epic 8. 본 연구 착수 전 IRB 정합성 확보 및 시스템 정비</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I139" s="16" t="n"/>
-      <c r="J139" s="15" t="n">
-        <v>218</v>
-      </c>
-      <c r="K139" s="20" t="inlineStr">
-        <is>
-          <t>#253</t>
+      <c r="I139" s="4" t="n"/>
+      <c r="J139" s="3" t="n"/>
+      <c r="K139" s="8" t="inlineStr">
+        <is>
+          <t>#207</t>
         </is>
       </c>
     </row>
     <row r="140" outlineLevel="2">
-      <c r="A140" s="15" t="n">
+      <c r="A140" s="9" t="n">
         <v>139</v>
       </c>
-      <c r="B140" s="16" t="inlineStr">
+      <c r="B140" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C140" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
-      <c r="D140" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E140" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F140" s="15" t="n">
-        <v>254</v>
-      </c>
-      <c r="G140" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 오늘·기간 집계를 원본 영상 데이터에서 유효 시청·시청 시간 기준으로 계산</t>
-        </is>
-      </c>
-      <c r="H140" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I140" s="16" t="n"/>
-      <c r="J140" s="15" t="n">
-        <v>218</v>
-      </c>
-      <c r="K140" s="20" t="inlineStr">
-        <is>
-          <t>#254</t>
+      <c r="C140" s="10" t="inlineStr">
+        <is>
+          <t>Story 8-1</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E140" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>280</v>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 8-1: 연구 기간이 끝나면 수집·전송이 자동으로 멈추고 참가자에게 안내된다</t>
+        </is>
+      </c>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I140" s="10" t="n"/>
+      <c r="J140" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K140" s="14" t="inlineStr">
+        <is>
+          <t>#280</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6976,7 @@
       </c>
       <c r="C141" s="16" t="inlineStr">
         <is>
-          <t>Story 8-3</t>
+          <t>Story 8-1</t>
         </is>
       </c>
       <c r="D141" s="15" t="n">
@@ -6948,11 +6988,11 @@
         </is>
       </c>
       <c r="F141" s="15" t="n">
-        <v>255</v>
+        <v>160</v>
       </c>
       <c r="G141" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 리뷰의 LLM 입력과 대체 문구를 유효 시청 기준으로 정렬</t>
+          <t xml:space="preserve">        feat: 연구 종료 후 수집·생성 중단 + "오늘" 탭 마지막 날짜 고정</t>
         </is>
       </c>
       <c r="H141" s="19" t="inlineStr">
@@ -6962,11 +7002,11 @@
       </c>
       <c r="I141" s="16" t="n"/>
       <c r="J141" s="15" t="n">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="K141" s="20" t="inlineStr">
         <is>
-          <t>#255</t>
+          <t>#160</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7021,7 @@
       </c>
       <c r="C142" s="16" t="inlineStr">
         <is>
-          <t>Story 8-3</t>
+          <t>Story 8-1</t>
         </is>
       </c>
       <c r="D142" s="15" t="n">
@@ -6993,11 +7033,11 @@
         </is>
       </c>
       <c r="F142" s="15" t="n">
-        <v>256</v>
+        <v>197</v>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘 리뷰를 유효 영상이 늘었을 때만 최소 간격을 두고 생성</t>
+          <t xml:space="preserve">        feat: 연구 기간 종료 시 확장 프로그램 수집·전송 자동 중단 및 제거 안내</t>
         </is>
       </c>
       <c r="H142" s="19" t="inlineStr">
@@ -7007,11 +7047,11 @@
       </c>
       <c r="I142" s="16" t="n"/>
       <c r="J142" s="15" t="n">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="K142" s="20" t="inlineStr">
         <is>
-          <t>#256</t>
+          <t>#197</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7066,7 @@
       </c>
       <c r="C143" s="16" t="inlineStr">
         <is>
-          <t>Story 8-3</t>
+          <t>Story 8-1</t>
         </is>
       </c>
       <c r="D143" s="15" t="n">
@@ -7038,70 +7078,70 @@
         </is>
       </c>
       <c r="F143" s="15" t="n">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 탭에서 제목을 먼저 보이고 시청 현황(개수) 표시를 정리</t>
-        </is>
-      </c>
-      <c r="H143" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 연구 기간에 따라 달라지는 문구를 상수에서 생성하고 기간 상수 일치를 테스트로 고정</t>
+        </is>
+      </c>
+      <c r="H143" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I143" s="16" t="n"/>
       <c r="J143" s="15" t="n">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="K143" s="20" t="inlineStr">
         <is>
-          <t>#262</t>
+          <t>#210</t>
         </is>
       </c>
     </row>
     <row r="144" outlineLevel="2">
-      <c r="A144" s="15" t="n">
+      <c r="A144" s="9" t="n">
         <v>143</v>
       </c>
-      <c r="B144" s="16" t="inlineStr">
+      <c r="B144" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C144" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
-      <c r="D144" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E144" s="17" t="inlineStr">
-        <is>
-          <t>Bug</t>
-        </is>
-      </c>
-      <c r="F144" s="15" t="n">
-        <v>302</v>
-      </c>
-      <c r="G144" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        fix: 탭을 닫을 때 마지막 영상의 시청 시간이 유실돼 "확인 중"으로 영구히 남음</t>
-        </is>
-      </c>
-      <c r="H144" s="19" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I144" s="16" t="n"/>
-      <c r="J144" s="15" t="n">
-        <v>218</v>
-      </c>
-      <c r="K144" s="20" t="inlineStr">
-        <is>
-          <t>#302</t>
+      <c r="C144" s="10" t="inlineStr">
+        <is>
+          <t>Story 8-2</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E144" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="n">
+        <v>281</v>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 8-2: 참가자에게 집단(실험/대조) 정보가 노출되지 않는다</t>
+        </is>
+      </c>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I144" s="10" t="n"/>
+      <c r="J144" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K144" s="14" t="inlineStr">
+        <is>
+          <t>#281</t>
         </is>
       </c>
     </row>
@@ -7116,7 +7156,7 @@
       </c>
       <c r="C145" s="16" t="inlineStr">
         <is>
-          <t>Story 8-3</t>
+          <t>Story 8-2</t>
         </is>
       </c>
       <c r="D145" s="15" t="n">
@@ -7124,29 +7164,29 @@
       </c>
       <c r="E145" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F145" s="15" t="n">
-        <v>303</v>
+        <v>209</v>
       </c>
       <c r="G145" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: Shorts 시청 시간이 측정되지 않고 0초로 기록돼 유효 시청에서 빠짐</t>
+          <t xml:space="preserve">        feat: 참여코드에서 집단 표식 제거</t>
         </is>
       </c>
       <c r="H145" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I145" s="16" t="n"/>
       <c r="J145" s="15" t="n">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="K145" s="20" t="inlineStr">
         <is>
-          <t>#303</t>
+          <t>#209</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7201,7 @@
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Story 8-4</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
@@ -7173,14 +7213,14 @@
         </is>
       </c>
       <c r="F146" s="9" t="n">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Story 8-4: IRB 변경심의를 신청하고 승인받는다</t>
-        </is>
-      </c>
-      <c r="H146" s="23" t="inlineStr">
+          <t xml:space="preserve">    Story 8-3: 화면·피드백·분석의 시청 집계 기준을 유효 시청·시청 시간으로 통일한다</t>
+        </is>
+      </c>
+      <c r="H146" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -7191,7 +7231,7 @@
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>#282</t>
+          <t>#218</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7246,7 @@
       </c>
       <c r="C147" s="16" t="inlineStr">
         <is>
-          <t>Story 8-4</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D147" s="15" t="n">
@@ -7218,109 +7258,115 @@
         </is>
       </c>
       <c r="F147" s="15" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        docs: IRB 변경심의 신청</t>
-        </is>
-      </c>
-      <c r="H147" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        feat: 기간별 리뷰 첫 줄에 분야별 비중과 지난 구간 대비 변화를 사실 문장으로 추가</t>
+        </is>
+      </c>
+      <c r="H147" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I147" s="16" t="n"/>
       <c r="J147" s="15" t="n">
-        <v>282</v>
+        <v>218</v>
       </c>
       <c r="K147" s="20" t="inlineStr">
         <is>
-          <t>#213</t>
+          <t>#211</t>
         </is>
       </c>
     </row>
     <row r="148" outlineLevel="2">
-      <c r="A148" s="3" t="n">
+      <c r="A148" s="15" t="n">
         <v>147</v>
       </c>
-      <c r="B148" s="4" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C148" s="4" t="n"/>
-      <c r="D148" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E148" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>208</v>
-      </c>
-      <c r="G148" s="6" t="inlineStr">
-        <is>
-          <t>Epic 9. 테스트 및 품질 보강</t>
-        </is>
-      </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I148" s="4" t="n"/>
-      <c r="J148" s="3" t="n"/>
-      <c r="K148" s="8" t="inlineStr">
-        <is>
-          <t>#208</t>
+      <c r="B148" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C148" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D148" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F148" s="15" t="n">
+        <v>217</v>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 팝업 화면 숫자를 서버 집계 기준으로 통일하고 기간별 탭을 분야별 시청 시간 꺾은선으로 교체</t>
+        </is>
+      </c>
+      <c r="H148" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I148" s="16" t="n"/>
+      <c r="J148" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K148" s="20" t="inlineStr">
+        <is>
+          <t>#217</t>
         </is>
       </c>
     </row>
     <row r="149" outlineLevel="2">
-      <c r="A149" s="9" t="n">
+      <c r="A149" s="15" t="n">
         <v>148</v>
       </c>
-      <c r="B149" s="10" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C149" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-1</t>
-        </is>
-      </c>
-      <c r="D149" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E149" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F149" s="9" t="n">
-        <v>283</v>
-      </c>
-      <c r="G149" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-1: 위험 기반 테스트로 연구 데이터 오염 위험을 제거한다</t>
-        </is>
-      </c>
-      <c r="H149" s="23" t="inlineStr">
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C149" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D149" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E149" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F149" s="15" t="n">
+        <v>253</v>
+      </c>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        docs: 시청 집계 기준·화면 지표 결정을 기록하고 사전등록 문서에 반영</t>
+        </is>
+      </c>
+      <c r="H149" s="19" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I149" s="10" t="n"/>
-      <c r="J149" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K149" s="14" t="inlineStr">
-        <is>
-          <t>#283</t>
+      <c r="I149" s="16" t="n"/>
+      <c r="J149" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K149" s="20" t="inlineStr">
+        <is>
+          <t>#253</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7376,12 @@
       </c>
       <c r="B150" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C150" s="16" t="inlineStr">
         <is>
-          <t>Story 9-1</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D150" s="15" t="n">
@@ -7347,11 +7393,11 @@
         </is>
       </c>
       <c r="F150" s="15" t="n">
-        <v>165</v>
+        <v>254</v>
       </c>
       <c r="G150" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 위험 기반 테스트 보강 및 커버리지 측정 도입</t>
+          <t xml:space="preserve">        feat: 오늘·기간 집계를 원본 영상 데이터에서 유효 시청·시청 시간 기준으로 계산</t>
         </is>
       </c>
       <c r="H150" s="19" t="inlineStr">
@@ -7361,11 +7407,11 @@
       </c>
       <c r="I150" s="16" t="n"/>
       <c r="J150" s="15" t="n">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="K150" s="20" t="inlineStr">
         <is>
-          <t>#165</t>
+          <t>#254</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7421,12 @@
       </c>
       <c r="B151" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C151" s="16" t="inlineStr">
         <is>
-          <t>Story 9-1</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D151" s="15" t="n">
@@ -7392,11 +7438,11 @@
         </is>
       </c>
       <c r="F151" s="15" t="n">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="G151" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 위험 기반 테스트 4개 항목 구현 및 리팩터링</t>
+          <t xml:space="preserve">        feat: 오늘·기간 리뷰의 LLM 입력과 대체 문구를 유효 시청 기준으로 정렬</t>
         </is>
       </c>
       <c r="H151" s="19" t="inlineStr">
@@ -7406,11 +7452,11 @@
       </c>
       <c r="I151" s="16" t="n"/>
       <c r="J151" s="15" t="n">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="K151" s="20" t="inlineStr">
         <is>
-          <t>#167</t>
+          <t>#255</t>
         </is>
       </c>
     </row>
@@ -7420,12 +7466,12 @@
       </c>
       <c r="B152" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C152" s="16" t="inlineStr">
         <is>
-          <t>Story 9-1</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D152" s="15" t="n">
@@ -7437,11 +7483,11 @@
         </is>
       </c>
       <c r="F152" s="15" t="n">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="G152" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 테스트 공백 보완 및 진행 기록</t>
+          <t xml:space="preserve">        feat: 오늘 리뷰를 유효 영상이 늘었을 때만 최소 간격을 두고 생성</t>
         </is>
       </c>
       <c r="H152" s="19" t="inlineStr">
@@ -7451,11 +7497,11 @@
       </c>
       <c r="I152" s="16" t="n"/>
       <c r="J152" s="15" t="n">
-        <v>283</v>
+        <v>218</v>
       </c>
       <c r="K152" s="20" t="inlineStr">
         <is>
-          <t>#169</t>
+          <t>#256</t>
         </is>
       </c>
     </row>
@@ -7465,12 +7511,12 @@
       </c>
       <c r="B153" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C153" s="16" t="inlineStr">
         <is>
-          <t>Story 9-1</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D153" s="15" t="n">
@@ -7478,78 +7524,74 @@
       </c>
       <c r="E153" s="17" t="inlineStr">
         <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F153" s="15" t="n">
+        <v>262</v>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 오늘·기간 탭에서 제목을 먼저 보이고 시청 현황(개수) 표시를 정리</t>
+        </is>
+      </c>
+      <c r="H153" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I153" s="16" t="n"/>
+      <c r="J153" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K153" s="20" t="inlineStr">
+        <is>
+          <t>#262</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" outlineLevel="2">
+      <c r="A154" s="15" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C154" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D154" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" s="17" t="inlineStr">
+        <is>
           <t>Bug</t>
         </is>
       </c>
-      <c r="F153" s="15" t="n">
-        <v>294</v>
-      </c>
-      <c r="G153" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        fix: 클라이언트가 보내는 시각도 시간대가 없으면 거부하고 UTC ISO로 정규화</t>
-        </is>
-      </c>
-      <c r="H153" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>#295</t>
-        </is>
-      </c>
-      <c r="J153" s="15" t="n">
-        <v>283</v>
-      </c>
-      <c r="K153" s="20" t="inlineStr">
-        <is>
-          <t>#294</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" outlineLevel="2">
-      <c r="A154" s="9" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" s="10" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-2</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E154" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F154" s="9" t="n">
-        <v>285</v>
-      </c>
-      <c r="G154" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-2: 핵심 API 경로가 실제 라우터 기준 통합 테스트로 보호된다</t>
-        </is>
-      </c>
-      <c r="H154" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I154" s="10" t="n"/>
-      <c r="J154" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K154" s="14" t="inlineStr">
-        <is>
-          <t>#285</t>
+      <c r="F154" s="15" t="n">
+        <v>302</v>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 탭을 닫을 때 마지막 영상의 시청 시간이 유실돼 "확인 중"으로 영구히 남음</t>
+        </is>
+      </c>
+      <c r="H154" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I154" s="16" t="n"/>
+      <c r="J154" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K154" s="20" t="inlineStr">
+        <is>
+          <t>#302</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7601,12 @@
       </c>
       <c r="B155" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C155" s="16" t="inlineStr">
         <is>
-          <t>Story 9-2</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D155" s="15" t="n">
@@ -7572,15 +7614,15 @@
       </c>
       <c r="E155" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F155" s="15" t="n">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="G155" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 종료 게이트 API 실제 라우터 배선 테스트</t>
+          <t xml:space="preserve">        fix: Shorts 시청 시간이 측정되지 않고 0초로 기록돼 유효 시청에서 빠짐</t>
         </is>
       </c>
       <c r="H155" s="19" t="inlineStr">
@@ -7590,11 +7632,11 @@
       </c>
       <c r="I155" s="16" t="n"/>
       <c r="J155" s="15" t="n">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="K155" s="20" t="inlineStr">
         <is>
-          <t>#234</t>
+          <t>#303</t>
         </is>
       </c>
     </row>
@@ -7604,12 +7646,12 @@
       </c>
       <c r="B156" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C156" s="16" t="inlineStr">
         <is>
-          <t>Story 9-2</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D156" s="15" t="n">
@@ -7617,15 +7659,15 @@
       </c>
       <c r="E156" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F156" s="15" t="n">
-        <v>235</v>
+        <v>324</v>
       </c>
       <c r="G156" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: CORS 허용 출처 규칙 회귀 테스트</t>
+          <t xml:space="preserve">        fix: 같은 탭에서 영상을 새로고침하거나 바로 다시 열면 기록이 둘로 나뉘거나 다시 연 뒤의 시청 시간이 유실됨</t>
         </is>
       </c>
       <c r="H156" s="19" t="inlineStr">
@@ -7633,13 +7675,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I156" s="16" t="n"/>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>#326</t>
+        </is>
+      </c>
       <c r="J156" s="15" t="n">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="K156" s="20" t="inlineStr">
         <is>
-          <t>#235</t>
+          <t>#324</t>
         </is>
       </c>
     </row>
@@ -7649,12 +7695,12 @@
       </c>
       <c r="B157" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C157" s="16" t="inlineStr">
         <is>
-          <t>Story 9-2</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D157" s="15" t="n">
@@ -7662,15 +7708,15 @@
       </c>
       <c r="E157" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F157" s="15" t="n">
-        <v>236</v>
+        <v>325</v>
       </c>
       <c r="G157" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: cron 스크립트(백업·모니터링) 테스트 가능 구조 및 테스트</t>
+          <t xml:space="preserve">        fix: 10분 넘는 영상을 보는 중 세션이 끝나면 오늘 리뷰에서 그 영상이 빠지고, 시청 시간이 늦게 와도 리뷰의 영상 수·비중이 그래프와 어긋난 채 남음</t>
         </is>
       </c>
       <c r="H157" s="19" t="inlineStr">
@@ -7678,13 +7724,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I157" s="16" t="n"/>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>#329</t>
+        </is>
+      </c>
       <c r="J157" s="15" t="n">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="K157" s="20" t="inlineStr">
         <is>
-          <t>#236</t>
+          <t>#325</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7744,12 @@
       </c>
       <c r="B158" s="16" t="inlineStr">
         <is>
-          <t>Epic 9</t>
+          <t>Epic 8</t>
         </is>
       </c>
       <c r="C158" s="16" t="inlineStr">
         <is>
-          <t>Story 9-2</t>
+          <t>Story 8-3</t>
         </is>
       </c>
       <c r="D158" s="15" t="n">
@@ -7707,15 +7757,15 @@
       </c>
       <c r="E158" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F158" s="15" t="n">
-        <v>240</v>
+        <v>327</v>
       </c>
       <c r="G158" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 연구 종료 게이트 통합 테스트를 실제 라우터로 전환</t>
+          <t xml:space="preserve">        feat: 오늘·기간 탭 제목을 한 줄로 줄이고, 가장 많이 본 분야가 다를 때만 보조 줄로 알리며 분야명만 굵게 표시</t>
         </is>
       </c>
       <c r="H158" s="19" t="inlineStr">
@@ -7723,103 +7773,111 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I158" s="16" t="n"/>
+      <c r="I158" s="16" t="inlineStr">
+        <is>
+          <t>#330</t>
+        </is>
+      </c>
       <c r="J158" s="15" t="n">
-        <v>285</v>
+        <v>218</v>
       </c>
       <c r="K158" s="20" t="inlineStr">
         <is>
-          <t>#240</t>
+          <t>#327</t>
         </is>
       </c>
     </row>
     <row r="159" outlineLevel="2">
-      <c r="A159" s="9" t="n">
+      <c r="A159" s="15" t="n">
         <v>158</v>
       </c>
-      <c r="B159" s="10" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C159" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="n">
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D159" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E159" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F159" s="15" t="n">
+        <v>335</v>
+      </c>
+      <c r="G159" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: "N일째"·현재 구간·베이스라인 판정이 설치 후 24시간 단위로 계산돼 KST 달력 기준 구간 경계와 최대 하루 어긋남</t>
+        </is>
+      </c>
+      <c r="H159" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>#338</t>
+        </is>
+      </c>
+      <c r="J159" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K159" s="20" t="inlineStr">
+        <is>
+          <t>#335</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" outlineLevel="1">
+      <c r="A160" s="9" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C160" s="10" t="inlineStr">
+        <is>
+          <t>Story 8-4</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E159" s="11" t="inlineStr">
+      <c r="E160" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F159" s="9" t="n">
-        <v>286</v>
-      </c>
-      <c r="G159" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-3: 커버리지를 정확히 측정하고 목표치를 유지한다</t>
-        </is>
-      </c>
-      <c r="H159" s="23" t="inlineStr">
+      <c r="F160" s="9" t="n">
+        <v>282</v>
+      </c>
+      <c r="G160" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 8-4: IRB 변경심의를 신청하고 승인받는다</t>
+        </is>
+      </c>
+      <c r="H160" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I159" s="10" t="n"/>
-      <c r="J159" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K159" s="14" t="inlineStr">
-        <is>
-          <t>#286</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" outlineLevel="1">
-      <c r="A160" s="15" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C160" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D160" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E160" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F160" s="15" t="n">
-        <v>233</v>
-      </c>
-      <c r="G160" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 커버리지 측정 보정 및 CI 정비</t>
-        </is>
-      </c>
-      <c r="H160" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I160" s="16" t="n"/>
-      <c r="J160" s="15" t="n">
-        <v>286</v>
-      </c>
-      <c r="K160" s="20" t="inlineStr">
-        <is>
-          <t>#233</t>
+      <c r="I160" s="10" t="n"/>
+      <c r="J160" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="K160" s="14" t="inlineStr">
+        <is>
+          <t>#282</t>
         </is>
       </c>
     </row>
@@ -7829,144 +7887,126 @@
       </c>
       <c r="B161" s="16" t="inlineStr">
         <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C161" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-4</t>
+        </is>
+      </c>
+      <c r="D161" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E161" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F161" s="15" t="n">
+        <v>213</v>
+      </c>
+      <c r="G161" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        docs: IRB 변경심의 신청</t>
+        </is>
+      </c>
+      <c r="H161" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I161" s="16" t="n"/>
+      <c r="J161" s="15" t="n">
+        <v>282</v>
+      </c>
+      <c r="K161" s="20" t="inlineStr">
+        <is>
+          <t>#213</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C161" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D161" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E161" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F161" s="15" t="n">
-        <v>259</v>
-      </c>
-      <c r="G161" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: content.js를 커버리지로 측정되게 하고 80% 이상으로 보강</t>
-        </is>
-      </c>
-      <c r="H161" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I161" s="16" t="inlineStr">
-        <is>
-          <t>#266</t>
-        </is>
-      </c>
-      <c r="J161" s="15" t="n">
-        <v>286</v>
-      </c>
-      <c r="K161" s="20" t="inlineStr">
-        <is>
-          <t>#259</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="15" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="16" t="inlineStr">
+      <c r="C162" s="4" t="n"/>
+      <c r="D162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>208</v>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>Epic 9. 테스트 및 품질 보강</t>
+        </is>
+      </c>
+      <c r="H162" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="8" t="inlineStr">
+        <is>
+          <t>#208</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C162" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D162" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E162" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F162" s="15" t="n">
-        <v>265</v>
-      </c>
-      <c r="G162" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 팝업 파일을 커버리지로 측정되게 전환</t>
-        </is>
-      </c>
-      <c r="H162" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I162" s="16" t="inlineStr">
-        <is>
-          <t>#284</t>
-        </is>
-      </c>
-      <c r="J162" s="15" t="n">
-        <v>286</v>
-      </c>
-      <c r="K162" s="20" t="inlineStr">
-        <is>
-          <t>#265</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="15" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C163" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D163" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E163" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F163" s="15" t="n">
-        <v>296</v>
-      </c>
-      <c r="G163" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 앱 조립을 create-app.js로 분리하고 실제 조립된 앱(미들웨어 순서·라우터 마운트)을 테스트로 검증</t>
-        </is>
-      </c>
-      <c r="H163" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>#298</t>
-        </is>
-      </c>
-      <c r="J163" s="15" t="n">
-        <v>286</v>
-      </c>
-      <c r="K163" s="20" t="inlineStr">
-        <is>
-          <t>#296</t>
+      <c r="C163" s="10" t="inlineStr">
+        <is>
+          <t>Story 9-1</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F163" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-1: 위험 기반 테스트로 연구 데이터 오염 위험을 제거한다</t>
+        </is>
+      </c>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I163" s="10" t="n"/>
+      <c r="J163" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K163" s="14" t="inlineStr">
+        <is>
+          <t>#283</t>
         </is>
       </c>
     </row>
@@ -7981,7 +8021,7 @@
       </c>
       <c r="C164" s="16" t="inlineStr">
         <is>
-          <t>Story 9-3</t>
+          <t>Story 9-1</t>
         </is>
       </c>
       <c r="D164" s="15" t="n">
@@ -7993,70 +8033,70 @@
         </is>
       </c>
       <c r="F164" s="15" t="n">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="G164" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: seed-codes.js를 scripts/로 옮겨 테스트 가능한 구조로 바꾸고, 잘못된 group이 있으면 명단 등록을 거부</t>
-        </is>
-      </c>
-      <c r="H164" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        test: 위험 기반 테스트 보강 및 커버리지 측정 도입</t>
+        </is>
+      </c>
+      <c r="H164" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I164" s="16" t="n"/>
       <c r="J164" s="15" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="K164" s="20" t="inlineStr">
         <is>
-          <t>#297</t>
+          <t>#165</t>
         </is>
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="9" t="n">
+      <c r="A165" s="15" t="n">
         <v>164</v>
       </c>
-      <c r="B165" s="10" t="inlineStr">
+      <c r="B165" s="16" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C165" s="10" t="inlineStr">
-        <is>
-          <t>Story 9-4</t>
-        </is>
-      </c>
-      <c r="D165" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="F165" s="9" t="n">
-        <v>287</v>
-      </c>
-      <c r="G165" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Story 9-4: 코드 형식·정적 분석·CI가 자동으로 관리된다</t>
-        </is>
-      </c>
-      <c r="H165" s="23" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I165" s="10" t="n"/>
-      <c r="J165" s="9" t="n">
-        <v>208</v>
-      </c>
-      <c r="K165" s="14" t="inlineStr">
-        <is>
-          <t>#287</t>
+      <c r="C165" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-1</t>
+        </is>
+      </c>
+      <c r="D165" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E165" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F165" s="15" t="n">
+        <v>167</v>
+      </c>
+      <c r="G165" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 위험 기반 테스트 4개 항목 구현 및 리팩터링</t>
+        </is>
+      </c>
+      <c r="H165" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I165" s="16" t="n"/>
+      <c r="J165" s="15" t="n">
+        <v>283</v>
+      </c>
+      <c r="K165" s="20" t="inlineStr">
+        <is>
+          <t>#167</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8111,7 @@
       </c>
       <c r="C166" s="16" t="inlineStr">
         <is>
-          <t>Story 9-4</t>
+          <t>Story 9-1</t>
         </is>
       </c>
       <c r="D166" s="15" t="n">
@@ -8083,11 +8123,11 @@
         </is>
       </c>
       <c r="F166" s="15" t="n">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="G166" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: ESLint 설정 복구 및 핵심 로직(analysis/llm) 단위 테스트 도입</t>
+          <t xml:space="preserve">        test: 테스트 공백 보완 및 진행 기록</t>
         </is>
       </c>
       <c r="H166" s="19" t="inlineStr">
@@ -8095,17 +8135,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>#135</t>
-        </is>
-      </c>
+      <c r="I166" s="16" t="n"/>
       <c r="J166" s="15" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K166" s="20" t="inlineStr">
         <is>
-          <t>#134</t>
+          <t>#169</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8156,7 @@
       </c>
       <c r="C167" s="16" t="inlineStr">
         <is>
-          <t>Story 9-4</t>
+          <t>Story 9-1</t>
         </is>
       </c>
       <c r="D167" s="15" t="n">
@@ -8128,15 +8164,15 @@
       </c>
       <c r="E167" s="17" t="inlineStr">
         <is>
-          <t>Task</t>
+          <t>Bug</t>
         </is>
       </c>
       <c r="F167" s="15" t="n">
-        <v>241</v>
+        <v>294</v>
       </c>
       <c r="G167" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: prettier 형식 일괄 정리 및 CI 형식 검사 추가</t>
+          <t xml:space="preserve">        fix: 클라이언트가 보내는 시각도 시간대가 없으면 거부하고 UTC ISO로 정규화</t>
         </is>
       </c>
       <c r="H167" s="19" t="inlineStr">
@@ -8144,58 +8180,62 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I167" s="16" t="n"/>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>#295</t>
+        </is>
+      </c>
       <c r="J167" s="15" t="n">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="K167" s="20" t="inlineStr">
         <is>
-          <t>#241</t>
+          <t>#294</t>
         </is>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="n">
+      <c r="A168" s="9" t="n">
         <v>167</v>
       </c>
-      <c r="B168" s="16" t="inlineStr">
+      <c r="B168" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C168" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-4</t>
-        </is>
-      </c>
-      <c r="D168" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E168" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F168" s="15" t="n">
-        <v>244</v>
-      </c>
-      <c r="G168" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        chore: CI action을 Node 24 지원 버전으로 올리고 Dependabot으로 버전 업데이트 자동화</t>
-        </is>
-      </c>
-      <c r="H168" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I168" s="16" t="n"/>
-      <c r="J168" s="15" t="n">
-        <v>287</v>
-      </c>
-      <c r="K168" s="20" t="inlineStr">
-        <is>
-          <t>#244</t>
+      <c r="C168" s="10" t="inlineStr">
+        <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F168" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-2: 핵심 API 경로가 실제 라우터 기준 통합 테스트로 보호된다</t>
+        </is>
+      </c>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I168" s="10" t="n"/>
+      <c r="J168" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K168" s="14" t="inlineStr">
+        <is>
+          <t>#285</t>
         </is>
       </c>
     </row>
@@ -8210,7 +8250,7 @@
       </c>
       <c r="C169" s="16" t="inlineStr">
         <is>
-          <t>Story 9-4</t>
+          <t>Story 9-2</t>
         </is>
       </c>
       <c r="D169" s="15" t="n">
@@ -8222,81 +8262,772 @@
         </is>
       </c>
       <c r="F169" s="15" t="n">
-        <v>288</v>
+        <v>234</v>
       </c>
       <c r="G169" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: SonarQube 코드 품질 측정 도입</t>
-        </is>
-      </c>
-      <c r="H169" s="24" t="inlineStr">
-        <is>
-          <t>Open</t>
+          <t xml:space="preserve">        test: 종료 게이트 API 실제 라우터 배선 테스트</t>
+        </is>
+      </c>
+      <c r="H169" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I169" s="16" t="n"/>
       <c r="J169" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K169" s="20" t="inlineStr">
+        <is>
+          <t>#234</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="15" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C170" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D170" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F170" s="15" t="n">
+        <v>235</v>
+      </c>
+      <c r="G170" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: CORS 허용 출처 규칙 회귀 테스트</t>
+        </is>
+      </c>
+      <c r="H170" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I170" s="16" t="n"/>
+      <c r="J170" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K170" s="20" t="inlineStr">
+        <is>
+          <t>#235</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="15" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C171" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D171" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E171" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F171" s="15" t="n">
+        <v>236</v>
+      </c>
+      <c r="G171" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: cron 스크립트(백업·모니터링) 테스트 가능 구조 및 테스트</t>
+        </is>
+      </c>
+      <c r="H171" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I171" s="16" t="n"/>
+      <c r="J171" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K171" s="20" t="inlineStr">
+        <is>
+          <t>#236</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="15" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C172" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D172" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E172" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F172" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="G172" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 연구 종료 게이트 통합 테스트를 실제 라우터로 전환</t>
+        </is>
+      </c>
+      <c r="H172" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I172" s="16" t="n"/>
+      <c r="J172" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K172" s="20" t="inlineStr">
+        <is>
+          <t>#240</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="9" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="10" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E173" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F173" s="9" t="n">
+        <v>286</v>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-3: 커버리지를 정확히 측정하고 목표치를 유지한다</t>
+        </is>
+      </c>
+      <c r="H173" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I173" s="10" t="n"/>
+      <c r="J173" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K173" s="14" t="inlineStr">
+        <is>
+          <t>#286</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="15" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C174" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D174" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E174" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F174" s="15" t="n">
+        <v>233</v>
+      </c>
+      <c r="G174" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 커버리지 측정 보정 및 CI 정비</t>
+        </is>
+      </c>
+      <c r="H174" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I174" s="16" t="n"/>
+      <c r="J174" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K174" s="20" t="inlineStr">
+        <is>
+          <t>#233</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="15" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C175" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D175" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E175" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F175" s="15" t="n">
+        <v>259</v>
+      </c>
+      <c r="G175" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: content.js를 커버리지로 측정되게 하고 80% 이상으로 보강</t>
+        </is>
+      </c>
+      <c r="H175" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>#266</t>
+        </is>
+      </c>
+      <c r="J175" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K175" s="20" t="inlineStr">
+        <is>
+          <t>#259</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="15" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C176" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D176" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E176" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F176" s="15" t="n">
+        <v>265</v>
+      </c>
+      <c r="G176" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 팝업 파일을 커버리지로 측정되게 전환</t>
+        </is>
+      </c>
+      <c r="H176" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>#284</t>
+        </is>
+      </c>
+      <c r="J176" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K176" s="20" t="inlineStr">
+        <is>
+          <t>#265</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="15" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C177" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D177" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E177" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F177" s="15" t="n">
+        <v>296</v>
+      </c>
+      <c r="G177" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 앱 조립을 create-app.js로 분리하고 실제 조립된 앱(미들웨어 순서·라우터 마운트)을 테스트로 검증</t>
+        </is>
+      </c>
+      <c r="H177" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>#298</t>
+        </is>
+      </c>
+      <c r="J177" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K177" s="20" t="inlineStr">
+        <is>
+          <t>#296</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="15" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C178" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D178" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E178" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F178" s="15" t="n">
+        <v>297</v>
+      </c>
+      <c r="G178" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: seed-codes.js를 scripts/로 옮겨 테스트 가능한 구조로 바꾸고, 잘못된 group이 있으면 명단 등록을 거부</t>
+        </is>
+      </c>
+      <c r="H178" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I178" s="16" t="n"/>
+      <c r="J178" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K178" s="20" t="inlineStr">
+        <is>
+          <t>#297</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="15" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C179" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D179" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E179" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F179" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="G179" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 서버 테스트를 Node 직접 실행 프로젝트로 분리해 커버리지 줄 밀림을 없애고, 줄 매핑 오류를 CI에서 감시</t>
+        </is>
+      </c>
+      <c r="H179" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I179" s="16" t="n"/>
+      <c r="J179" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K179" s="20" t="inlineStr">
+        <is>
+          <t>#316</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="9" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="10" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E180" s="11" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="F180" s="9" t="n">
         <v>287</v>
       </c>
-      <c r="K169" s="20" t="inlineStr">
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Story 9-4: 코드 형식·정적 분석·CI가 자동으로 관리된다</t>
+        </is>
+      </c>
+      <c r="H180" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I180" s="10" t="n"/>
+      <c r="J180" s="9" t="n">
+        <v>208</v>
+      </c>
+      <c r="K180" s="14" t="inlineStr">
+        <is>
+          <t>#287</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="15" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C181" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D181" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E181" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F181" s="15" t="n">
+        <v>134</v>
+      </c>
+      <c r="G181" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: ESLint 설정 복구 및 핵심 로직(analysis/llm) 단위 테스트 도입</t>
+        </is>
+      </c>
+      <c r="H181" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>#135</t>
+        </is>
+      </c>
+      <c r="J181" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K181" s="20" t="inlineStr">
+        <is>
+          <t>#134</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="15" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C182" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D182" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E182" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F182" s="15" t="n">
+        <v>241</v>
+      </c>
+      <c r="G182" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: prettier 형식 일괄 정리 및 CI 형식 검사 추가</t>
+        </is>
+      </c>
+      <c r="H182" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I182" s="16" t="n"/>
+      <c r="J182" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K182" s="20" t="inlineStr">
+        <is>
+          <t>#241</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="15" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C183" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D183" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E183" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F183" s="15" t="n">
+        <v>244</v>
+      </c>
+      <c r="G183" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: CI action을 Node 24 지원 버전으로 올리고 Dependabot으로 버전 업데이트 자동화</t>
+        </is>
+      </c>
+      <c r="H183" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I183" s="16" t="n"/>
+      <c r="J183" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K183" s="20" t="inlineStr">
+        <is>
+          <t>#244</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="15" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C184" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D184" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E184" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F184" s="15" t="n">
+        <v>288</v>
+      </c>
+      <c r="G184" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: SonarQube 코드 품질 측정 도입</t>
+        </is>
+      </c>
+      <c r="H184" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I184" s="16" t="n"/>
+      <c r="J184" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K184" s="20" t="inlineStr">
         <is>
           <t>#288</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="9" t="n">
-        <v>169</v>
-      </c>
-      <c r="B170" s="10" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="9" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C170" s="10" t="inlineStr">
+      <c r="C185" s="10" t="inlineStr">
         <is>
           <t>Story 9-5</t>
         </is>
       </c>
-      <c r="D170" s="9" t="n">
+      <c r="D185" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E170" s="11" t="inlineStr">
+      <c r="E185" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F170" s="9" t="n">
+      <c r="F185" s="9" t="n">
         <v>289</v>
       </c>
-      <c r="G170" s="12" t="inlineStr">
+      <c r="G185" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-5: 본 연구 규모(참가자 약 80명)의 부하를 서버가 견딘다</t>
         </is>
       </c>
-      <c r="H170" s="23" t="inlineStr">
+      <c r="H185" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I170" s="10" t="n"/>
-      <c r="J170" s="9" t="n">
+      <c r="I185" s="10" t="n"/>
+      <c r="J185" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K170" s="14" t="inlineStr">
+      <c r="K185" s="14" t="inlineStr">
         <is>
           <t>#289</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K170"/>
+  <autoFilter ref="A1:K185"/>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Epic,Story,Task,Bug"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H170" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,Closed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -8471,6 +9202,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K168" r:id="rId167"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K169" r:id="rId168"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId184"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -8553,15 +9299,15 @@
         </is>
       </c>
       <c r="C2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F2" s="26">
@@ -8569,11 +9315,11 @@
         <v/>
       </c>
       <c r="G2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A2,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I2" s="36">
@@ -8593,15 +9339,15 @@
         </is>
       </c>
       <c r="C3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F3" s="26">
@@ -8609,11 +9355,11 @@
         <v/>
       </c>
       <c r="G3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A3,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I3" s="36">
@@ -8633,15 +9379,15 @@
         </is>
       </c>
       <c r="C4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F4" s="26">
@@ -8649,11 +9395,11 @@
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A4,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I4" s="36">
@@ -8673,15 +9419,15 @@
         </is>
       </c>
       <c r="C5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F5" s="26">
@@ -8689,11 +9435,11 @@
         <v/>
       </c>
       <c r="G5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A5,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I5" s="36">
@@ -8713,15 +9459,15 @@
         </is>
       </c>
       <c r="C6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F6" s="26">
@@ -8729,11 +9475,11 @@
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A6,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I6" s="36">
@@ -8753,15 +9499,15 @@
         </is>
       </c>
       <c r="C7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F7" s="26">
@@ -8769,11 +9515,11 @@
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A7,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I7" s="36">
@@ -8793,15 +9539,15 @@
         </is>
       </c>
       <c r="C8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F8" s="26">
@@ -8809,11 +9555,11 @@
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A8,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I8" s="36">
@@ -8833,15 +9579,15 @@
         </is>
       </c>
       <c r="C9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F9" s="26">
@@ -8849,11 +9595,11 @@
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A9,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I9" s="36">
@@ -8873,15 +9619,15 @@
         </is>
       </c>
       <c r="C10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$E$2:$E$170,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$E$2:$E$185,"Story")</f>
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$E$2:$E$170,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$E$2:$E$185,"Task")</f>
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$E$2:$E$170,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$E$2:$E$185,"Bug")</f>
         <v/>
       </c>
       <c r="F10" s="26">
@@ -8889,11 +9635,11 @@
         <v/>
       </c>
       <c r="G10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$H$2:$H$170,"Open",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$170,$A10,백로그!$H$2:$H$170,"Closed",백로그!$E$2:$E$170,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I10" s="36">

--- a/docs/youtube-bias-feedback_backlog.xlsx
+++ b/docs/youtube-bias-feedback_backlog.xlsx
@@ -11,7 +11,7 @@
     <sheet name="미분류·확인 필요" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'백로그'!$A$1:$K$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'백로그'!$A$1:$K$186</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K185"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5383,92 +5383,92 @@
       </c>
     </row>
     <row r="106" outlineLevel="2">
-      <c r="A106" s="9" t="n">
+      <c r="A106" s="15" t="n">
         <v>105</v>
       </c>
-      <c r="B106" s="10" t="inlineStr">
+      <c r="B106" s="16" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C106" s="10" t="inlineStr">
+      <c r="C106" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-1</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>342</v>
+      </c>
+      <c r="G106" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 대조군이 종료 확인 코드를 검증한 직후, 같은 팝업에서 누적 리뷰·그래프가 비어 보임</t>
+        </is>
+      </c>
+      <c r="H106" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I106" s="16" t="n"/>
+      <c r="J106" s="15" t="n">
+        <v>274</v>
+      </c>
+      <c r="K106" s="20" t="inlineStr">
+        <is>
+          <t>#342</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" outlineLevel="2">
+      <c r="A107" s="9" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>Story 6-2</t>
         </is>
       </c>
-      <c r="D106" s="9" t="n">
+      <c r="D107" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E106" s="11" t="inlineStr">
+      <c r="E107" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F106" s="9" t="n">
+      <c r="F107" s="9" t="n">
         <v>275</v>
       </c>
-      <c r="G106" s="12" t="inlineStr">
+      <c r="G107" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-2: 참가자가 재설치해도 참여코드로 상태를 복구할 수 있다</t>
         </is>
       </c>
-      <c r="H106" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I106" s="10" t="n"/>
-      <c r="J106" s="9" t="n">
+      <c r="H107" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I107" s="10" t="n"/>
+      <c r="J107" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K106" s="14" t="inlineStr">
+      <c r="K107" s="14" t="inlineStr">
         <is>
           <t>#275</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" outlineLevel="2">
-      <c r="A107" s="15" t="n">
-        <v>106</v>
-      </c>
-      <c r="B107" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C107" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-2</t>
-        </is>
-      </c>
-      <c r="D107" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E107" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F107" s="15" t="n">
-        <v>149</v>
-      </c>
-      <c r="G107" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 참여코드 기반 재설치 복구</t>
-        </is>
-      </c>
-      <c r="H107" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I107" s="16" t="n"/>
-      <c r="J107" s="15" t="n">
-        <v>275</v>
-      </c>
-      <c r="K107" s="20" t="inlineStr">
-        <is>
-          <t>#149</t>
         </is>
       </c>
     </row>
@@ -5491,15 +5491,15 @@
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F108" s="15" t="n">
-        <v>223</v>
+        <v>149</v>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 참여자 등록 시 시간대가 없는 installDate를 거부하고 저장 형식을 UTC ISO로 통일</t>
+          <t xml:space="preserve">        feat: 참여코드 기반 재설치 복구</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="K108" s="20" t="inlineStr">
         <is>
-          <t>#223</t>
+          <t>#149</t>
         </is>
       </c>
     </row>
@@ -5540,11 +5540,11 @@
         </is>
       </c>
       <c r="F109" s="15" t="n">
-        <v>332</v>
+        <v>223</v>
       </c>
       <c r="G109" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 재설치 후 같은 날 오늘 리뷰 카드가 보이지 않음</t>
+          <t xml:space="preserve">        fix: 참여자 등록 시 시간대가 없는 installDate를 거부하고 저장 형식을 UTC ISO로 통일</t>
         </is>
       </c>
       <c r="H109" s="19" t="inlineStr">
@@ -5552,17 +5552,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>#333</t>
-        </is>
-      </c>
+      <c r="I109" s="16" t="n"/>
       <c r="J109" s="15" t="n">
         <v>275</v>
       </c>
       <c r="K109" s="20" t="inlineStr">
         <is>
-          <t>#332</t>
+          <t>#223</t>
         </is>
       </c>
     </row>
@@ -5589,21 +5585,21 @@
         </is>
       </c>
       <c r="F110" s="15" t="n">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="G110" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 재설치 후 지난 날짜와 오늘의 재생한 영상 목록에 이전 기록이 보이지 않음</t>
+          <t xml:space="preserve">        fix: 재설치 후 같은 날 오늘 리뷰 카드가 보이지 않음</t>
         </is>
       </c>
       <c r="H110" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
-          <t>#341</t>
+          <t>#333</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
@@ -5611,97 +5607,101 @@
       </c>
       <c r="K110" s="20" t="inlineStr">
         <is>
+          <t>#332</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" outlineLevel="2">
+      <c r="A111" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C111" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-2</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>339</v>
+      </c>
+      <c r="G111" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 재설치 후 지난 날짜와 오늘의 재생한 영상 목록에 이전 기록이 보이지 않음</t>
+        </is>
+      </c>
+      <c r="H111" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>#341</t>
+        </is>
+      </c>
+      <c r="J111" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="K111" s="20" t="inlineStr">
+        <is>
           <t>#339</t>
         </is>
       </c>
     </row>
-    <row r="111" outlineLevel="2">
-      <c r="A111" s="9" t="n">
-        <v>110</v>
-      </c>
-      <c r="B111" s="10" t="inlineStr">
+    <row r="112" outlineLevel="2">
+      <c r="A112" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C111" s="10" t="inlineStr">
+      <c r="C112" s="10" t="inlineStr">
         <is>
           <t>Story 6-3</t>
         </is>
       </c>
-      <c r="D111" s="9" t="n">
+      <c r="D112" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E111" s="11" t="inlineStr">
+      <c r="E112" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F111" s="9" t="n">
+      <c r="F112" s="9" t="n">
         <v>276</v>
       </c>
-      <c r="G111" s="12" t="inlineStr">
+      <c r="G112" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-3: 참가자가 자정 기준 하루 누적 리뷰를 확인할 수 있다</t>
         </is>
       </c>
-      <c r="H111" s="13" t="inlineStr">
+      <c r="H112" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I111" s="10" t="n"/>
-      <c r="J111" s="9" t="n">
+      <c r="I112" s="10" t="n"/>
+      <c r="J112" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K111" s="14" t="inlineStr">
+      <c r="K112" s="14" t="inlineStr">
         <is>
           <t>#276</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" outlineLevel="2">
-      <c r="A112" s="15" t="n">
-        <v>111</v>
-      </c>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C112" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-3</t>
-        </is>
-      </c>
-      <c r="D112" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E112" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F112" s="15" t="n">
-        <v>152</v>
-      </c>
-      <c r="G112" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 세션-종료 트리거를 오늘 누적 계산으로 통합</t>
-        </is>
-      </c>
-      <c r="H112" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I112" s="16" t="n"/>
-      <c r="J112" s="15" t="n">
-        <v>276</v>
-      </c>
-      <c r="K112" s="20" t="inlineStr">
-        <is>
-          <t>#152</t>
         </is>
       </c>
     </row>
@@ -5728,11 +5728,11 @@
         </is>
       </c>
       <c r="F113" s="15" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G113" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 자정 경계 처리 + "어제 돌아보기" 리빌 애니메이션</t>
+          <t xml:space="preserve">        feat: 세션-종료 트리거를 오늘 누적 계산으로 통합</t>
         </is>
       </c>
       <c r="H113" s="19" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="K113" s="20" t="inlineStr">
         <is>
-          <t>#153</t>
+          <t>#152</t>
         </is>
       </c>
     </row>
@@ -5773,11 +5773,11 @@
         </is>
       </c>
       <c r="F114" s="15" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G114" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 리뷰 카드 헤드라인 문구 스코프별 분기</t>
+          <t xml:space="preserve">        feat: 자정 경계 처리 + "어제 돌아보기" 리빌 애니메이션</t>
         </is>
       </c>
       <c r="H114" s="19" t="inlineStr">
@@ -5791,11 +5791,11 @@
       </c>
       <c r="K114" s="20" t="inlineStr">
         <is>
-          <t>#154</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" outlineLevel="1">
+          <t>#153</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" outlineLevel="1" ht="26.25" customHeight="1">
       <c r="A115" s="15" t="n">
         <v>114</v>
       </c>
@@ -5814,20 +5814,20 @@
       </c>
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F115" s="15" t="n">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="G115" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        bug: 피드백 생성 완료 직후 날짜 이동 시 "오늘" 탭이 갱신되지 않음</t>
+          <t xml:space="preserve">        feat: 리뷰 카드 헤드라인 문구 스코프별 분기</t>
         </is>
       </c>
       <c r="H115" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I115" s="16" t="n"/>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="K115" s="20" t="inlineStr">
         <is>
-          <t>#261</t>
+          <t>#154</t>
         </is>
       </c>
     </row>
@@ -5863,29 +5863,25 @@
         </is>
       </c>
       <c r="F116" s="15" t="n">
-        <v>318</v>
+        <v>261</v>
       </c>
       <c r="G116" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 베이스라인이 끝난 뒤 하루 돌아보기 탭의 지난 날짜에 Gemini 피드백이 보이지 않음</t>
+          <t xml:space="preserve">        bug: 피드백 생성 완료 직후 날짜 이동 시 "오늘" 탭이 갱신되지 않음</t>
         </is>
       </c>
       <c r="H116" s="19" t="inlineStr">
         <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I116" s="16" t="inlineStr">
-        <is>
-          <t>#320</t>
-        </is>
-      </c>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I116" s="16" t="n"/>
       <c r="J116" s="15" t="n">
         <v>276</v>
       </c>
       <c r="K116" s="20" t="inlineStr">
         <is>
-          <t>#318</t>
+          <t>#261</t>
         </is>
       </c>
     </row>
@@ -5912,11 +5908,11 @@
         </is>
       </c>
       <c r="F117" s="15" t="n">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: "어제 돌아보기" 슬라이드를 없애고, 확인하지 않은 오늘 리뷰가 있을 때 팝업을 열면 바로 그 리뷰가 보이게 함</t>
+          <t xml:space="preserve">        fix: 베이스라인이 끝난 뒤 하루 돌아보기 탭의 지난 날짜에 Gemini 피드백이 보이지 않음</t>
         </is>
       </c>
       <c r="H117" s="19" t="inlineStr">
@@ -5926,7 +5922,7 @@
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
-          <t>#322</t>
+          <t>#320</t>
         </is>
       </c>
       <c r="J117" s="15" t="n">
@@ -5934,7 +5930,7 @@
       </c>
       <c r="K117" s="20" t="inlineStr">
         <is>
-          <t>#319</t>
+          <t>#318</t>
         </is>
       </c>
     </row>
@@ -5961,11 +5957,11 @@
         </is>
       </c>
       <c r="F118" s="15" t="n">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 자정 직전에 본 영상의 세션이 다음 날 "오늘"로 잡힘</t>
+          <t xml:space="preserve">        feat: "어제 돌아보기" 슬라이드를 없애고, 확인하지 않은 오늘 리뷰가 있을 때 팝업을 열면 바로 그 리뷰가 보이게 함</t>
         </is>
       </c>
       <c r="H118" s="19" t="inlineStr">
@@ -5975,7 +5971,7 @@
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
-          <t>#340</t>
+          <t>#322</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
@@ -5983,97 +5979,101 @@
       </c>
       <c r="K118" s="20" t="inlineStr">
         <is>
+          <t>#319</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" outlineLevel="2">
+      <c r="A119" s="15" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C119" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-3</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>336</v>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 자정 직전에 본 영상의 세션이 다음 날 "오늘"로 잡힘</t>
+        </is>
+      </c>
+      <c r="H119" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>#340</t>
+        </is>
+      </c>
+      <c r="J119" s="15" t="n">
+        <v>276</v>
+      </c>
+      <c r="K119" s="20" t="inlineStr">
+        <is>
           <t>#336</t>
         </is>
       </c>
     </row>
-    <row r="119" outlineLevel="2">
-      <c r="A119" s="9" t="n">
-        <v>118</v>
-      </c>
-      <c r="B119" s="10" t="inlineStr">
+    <row r="120" outlineLevel="2">
+      <c r="A120" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C119" s="10" t="inlineStr">
+      <c r="C120" s="10" t="inlineStr">
         <is>
           <t>Story 6-4</t>
         </is>
       </c>
-      <c r="D119" s="9" t="n">
+      <c r="D120" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E119" s="11" t="inlineStr">
+      <c r="E120" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F119" s="9" t="n">
+      <c r="F120" s="9" t="n">
         <v>277</v>
       </c>
-      <c r="G119" s="12" t="inlineStr">
+      <c r="G120" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-4: 네트워크·인증 오류가 나도 데이터 전송과 참여자 등록이 자동 복구된다</t>
         </is>
       </c>
-      <c r="H119" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I119" s="10" t="n"/>
-      <c r="J119" s="9" t="n">
+      <c r="H120" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I120" s="10" t="n"/>
+      <c r="J120" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K119" s="14" t="inlineStr">
+      <c r="K120" s="14" t="inlineStr">
         <is>
           <t>#277</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" outlineLevel="2">
-      <c r="A120" s="15" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="16" t="inlineStr">
-        <is>
-          <t>Epic 6</t>
-        </is>
-      </c>
-      <c r="C120" s="16" t="inlineStr">
-        <is>
-          <t>Story 6-4</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E120" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F120" s="15" t="n">
-        <v>193</v>
-      </c>
-      <c r="G120" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 전송 큐 재시도에 큐 레벨 fail-fast·재진입 가드·타임아웃 도입</t>
-        </is>
-      </c>
-      <c r="H120" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I120" s="16" t="n"/>
-      <c r="J120" s="15" t="n">
-        <v>277</v>
-      </c>
-      <c r="K120" s="20" t="inlineStr">
-        <is>
-          <t>#193</t>
         </is>
       </c>
     </row>
@@ -6100,11 +6100,11 @@
         </is>
       </c>
       <c r="F121" s="15" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참여자 등록 게이트를 백그라운드에서 자동 복구하고 403 무효화 경로 추가</t>
+          <t xml:space="preserve">        feat: 전송 큐 재시도에 큐 레벨 fail-fast·재진입 가드·타임아웃 도입</t>
         </is>
       </c>
       <c r="H121" s="19" t="inlineStr">
@@ -6118,11 +6118,11 @@
       </c>
       <c r="K121" s="20" t="inlineStr">
         <is>
-          <t>#196</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" outlineLevel="2">
+          <t>#193</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="A122" s="15" t="n">
         <v>121</v>
       </c>
@@ -6141,15 +6141,15 @@
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F122" s="15" t="n">
-        <v>334</v>
+        <v>196</v>
       </c>
       <c r="G122" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 확장 저장 한도를 풀어 많이 보는 참여자의 영상 기록이 끊기지 않게 하고, 1분 재시도 틱의 저장소 조회 로직 개선</t>
+          <t xml:space="preserve">        feat: 참여자 등록 게이트를 백그라운드에서 자동 복구하고 403 무효화 경로 추가</t>
         </is>
       </c>
       <c r="H122" s="19" t="inlineStr">
@@ -6157,191 +6157,191 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>#337</t>
-        </is>
-      </c>
+      <c r="I122" s="16" t="n"/>
       <c r="J122" s="15" t="n">
         <v>277</v>
       </c>
       <c r="K122" s="20" t="inlineStr">
         <is>
+          <t>#196</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" outlineLevel="1">
+      <c r="A123" s="15" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="16" t="inlineStr">
+        <is>
+          <t>Epic 6</t>
+        </is>
+      </c>
+      <c r="C123" s="16" t="inlineStr">
+        <is>
+          <t>Story 6-4</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F123" s="15" t="n">
+        <v>334</v>
+      </c>
+      <c r="G123" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 확장 저장 한도를 풀어 많이 보는 참여자의 영상 기록이 끊기지 않게 하고, 1분 재시도 틱의 저장소 조회 로직 개선</t>
+        </is>
+      </c>
+      <c r="H123" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>#337</t>
+        </is>
+      </c>
+      <c r="J123" s="15" t="n">
+        <v>277</v>
+      </c>
+      <c r="K123" s="20" t="inlineStr">
+        <is>
           <t>#334</t>
         </is>
       </c>
     </row>
-    <row r="123" outlineLevel="1">
-      <c r="A123" s="9" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="10" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
         <is>
           <t>Epic 6</t>
         </is>
       </c>
-      <c r="C123" s="10" t="inlineStr">
+      <c r="C124" s="10" t="inlineStr">
         <is>
           <t>Story 6-5</t>
         </is>
       </c>
-      <c r="D123" s="9" t="n">
+      <c r="D124" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E123" s="11" t="inlineStr">
+      <c r="E124" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F123" s="9" t="n">
+      <c r="F124" s="9" t="n">
         <v>278</v>
       </c>
-      <c r="G123" s="12" t="inlineStr">
+      <c r="G124" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 6-5: 참가자가 오류 발생 시 팝업에서 안내를 볼 수 있다</t>
         </is>
       </c>
-      <c r="H123" s="13" t="inlineStr">
+      <c r="H124" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I123" s="10" t="n"/>
-      <c r="J123" s="9" t="n">
+      <c r="I124" s="10" t="n"/>
+      <c r="J124" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="K123" s="14" t="inlineStr">
+      <c r="K124" s="14" t="inlineStr">
         <is>
           <t>#278</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="3" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
+    <row r="125" outlineLevel="1">
+      <c r="A125" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="3" t="n">
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E124" s="5" t="inlineStr">
+      <c r="E125" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F124" s="3" t="n">
+      <c r="F125" s="3" t="n">
         <v>202</v>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G125" s="6" t="inlineStr">
         <is>
           <t>Epic 7. 관측 체계 구축 및 운영</t>
         </is>
       </c>
-      <c r="H124" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I124" s="4" t="n"/>
-      <c r="J124" s="3" t="n"/>
-      <c r="K124" s="8" t="inlineStr">
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="8" t="inlineStr">
         <is>
           <t>#202</t>
         </is>
       </c>
     </row>
-    <row r="125" outlineLevel="1">
-      <c r="A125" s="9" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="10" t="inlineStr">
+    <row r="126" outlineLevel="2">
+      <c r="A126" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C125" s="10" t="inlineStr">
+      <c r="C126" s="10" t="inlineStr">
         <is>
           <t>Story 7-1</t>
         </is>
       </c>
-      <c r="D125" s="9" t="n">
+      <c r="D126" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E125" s="11" t="inlineStr">
+      <c r="E126" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F125" s="9" t="n">
+      <c r="F126" s="9" t="n">
         <v>172</v>
       </c>
-      <c r="G125" s="12" t="inlineStr">
+      <c r="G126" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 7-1: 운영자가 서버·cron·결측 이상을 즉시 알림으로 받을 수 있다(최소 관제 체계(MVM) 구축)</t>
         </is>
       </c>
-      <c r="H125" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I125" s="10" t="n"/>
-      <c r="J125" s="9" t="n">
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I126" s="10" t="n"/>
+      <c r="J126" s="9" t="n">
         <v>202</v>
       </c>
-      <c r="K125" s="14" t="inlineStr">
+      <c r="K126" s="14" t="inlineStr">
         <is>
           <t>#172</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" outlineLevel="2">
-      <c r="A126" s="15" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C126" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-1</t>
-        </is>
-      </c>
-      <c r="D126" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E126" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F126" s="15" t="n">
-        <v>192</v>
-      </c>
-      <c r="G126" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 접근 로그에 실제 API 경로 기록 및 error-monitor 알림을 /api/* 4xx로 한정</t>
-        </is>
-      </c>
-      <c r="H126" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I126" s="16" t="n"/>
-      <c r="J126" s="15" t="n">
-        <v>172</v>
-      </c>
-      <c r="K126" s="20" t="inlineStr">
-        <is>
-          <t>#192</t>
         </is>
       </c>
     </row>
@@ -6368,11 +6368,11 @@
         </is>
       </c>
       <c r="F127" s="15" t="n">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog Monitor로 세션 API 지연·Agent 무응답 알림 추가</t>
+          <t xml:space="preserve">        feat: 접근 로그에 실제 API 경로 기록 및 error-monitor 알림을 /api/* 4xx로 한정</t>
         </is>
       </c>
       <c r="H127" s="19" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="K127" s="20" t="inlineStr">
         <is>
-          <t>#204</t>
+          <t>#192</t>
         </is>
       </c>
     </row>
@@ -6413,11 +6413,11 @@
         </is>
       </c>
       <c r="F128" s="15" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: LLM fallback 비율·Gemini 응답 시간을 Datadog 커스텀 메트릭으로 추세 감시</t>
+          <t xml:space="preserve">        feat: Datadog Monitor로 세션 API 지연·Agent 무응답 알림 추가</t>
         </is>
       </c>
       <c r="H128" s="19" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="K128" s="20" t="inlineStr">
         <is>
-          <t>#205</t>
+          <t>#204</t>
         </is>
       </c>
     </row>
@@ -6458,11 +6458,11 @@
         </is>
       </c>
       <c r="F129" s="15" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G129" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 참가자별 결측 감지 cron 가동과 결측 의심 시 인원수 알림</t>
+          <t xml:space="preserve">        feat: LLM fallback 비율·Gemini 응답 시간을 Datadog 커스텀 메트릭으로 추세 감시</t>
         </is>
       </c>
       <c r="H129" s="19" t="inlineStr">
@@ -6476,97 +6476,97 @@
       </c>
       <c r="K129" s="20" t="inlineStr">
         <is>
+          <t>#205</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" outlineLevel="2">
+      <c r="A130" s="15" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C130" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-1</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F130" s="15" t="n">
+        <v>206</v>
+      </c>
+      <c r="G130" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 참가자별 결측 감지 cron 가동과 결측 의심 시 인원수 알림</t>
+        </is>
+      </c>
+      <c r="H130" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I130" s="16" t="n"/>
+      <c r="J130" s="15" t="n">
+        <v>172</v>
+      </c>
+      <c r="K130" s="20" t="inlineStr">
+        <is>
           <t>#206</t>
         </is>
       </c>
     </row>
-    <row r="130" outlineLevel="2">
-      <c r="A130" s="9" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="10" t="inlineStr">
+    <row r="131" outlineLevel="1">
+      <c r="A131" s="9" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="10" t="inlineStr">
         <is>
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C130" s="10" t="inlineStr">
+      <c r="C131" s="10" t="inlineStr">
         <is>
           <t>Story 7-2</t>
         </is>
       </c>
-      <c r="D130" s="9" t="n">
+      <c r="D131" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E130" s="11" t="inlineStr">
+      <c r="E131" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F130" s="9" t="n">
+      <c r="F131" s="9" t="n">
         <v>279</v>
       </c>
-      <c r="G130" s="12" t="inlineStr">
+      <c r="G131" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 7-2: 운영자가 오류 원인을 로그·트레이스로 추적할 수 있다</t>
         </is>
       </c>
-      <c r="H130" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I130" s="10" t="n"/>
-      <c r="J130" s="9" t="n">
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I131" s="10" t="n"/>
+      <c r="J131" s="9" t="n">
         <v>202</v>
       </c>
-      <c r="K130" s="14" t="inlineStr">
+      <c r="K131" s="14" t="inlineStr">
         <is>
           <t>#279</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" outlineLevel="1">
-      <c r="A131" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="B131" s="16" t="inlineStr">
-        <is>
-          <t>Epic 7</t>
-        </is>
-      </c>
-      <c r="C131" s="16" t="inlineStr">
-        <is>
-          <t>Story 7-2</t>
-        </is>
-      </c>
-      <c r="D131" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E131" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F131" s="15" t="n">
-        <v>203</v>
-      </c>
-      <c r="G131" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 확장 프로그램 오류를 연구 서버로 원격 수집</t>
-        </is>
-      </c>
-      <c r="H131" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I131" s="16" t="n"/>
-      <c r="J131" s="15" t="n">
-        <v>279</v>
-      </c>
-      <c r="K131" s="20" t="inlineStr">
-        <is>
-          <t>#203</t>
         </is>
       </c>
     </row>
@@ -6593,11 +6593,11 @@
         </is>
       </c>
       <c r="F132" s="15" t="n">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog에서 가명 사용자 ID(anonymousId)로 로그·요청을 조회할 수 있게 UUID 마스킹 해제</t>
+          <t xml:space="preserve">        feat: 확장 프로그램 오류를 연구 서버로 원격 수집</t>
         </is>
       </c>
       <c r="H132" s="19" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="K132" s="20" t="inlineStr">
         <is>
-          <t>#225</t>
+          <t>#203</t>
         </is>
       </c>
     </row>
@@ -6638,11 +6638,11 @@
         </is>
       </c>
       <c r="F133" s="15" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 서버 예외의 스택 트레이스를 확인할 수 있게 하기</t>
+          <t xml:space="preserve">        feat: Datadog에서 가명 사용자 ID(anonymousId)로 로그·요청을 조회할 수 있게 UUID 마스킹 해제</t>
         </is>
       </c>
       <c r="H133" s="19" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="K133" s="20" t="inlineStr">
         <is>
-          <t>#226</t>
+          <t>#225</t>
         </is>
       </c>
     </row>
@@ -6683,11 +6683,11 @@
         </is>
       </c>
       <c r="F134" s="15" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G134" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 서버 로그 줄에 trace ID를 넣어 Datadog Logs와 APM trace를 연결</t>
+          <t xml:space="preserve">        feat: 서버 예외의 스택 트레이스를 확인할 수 있게 하기</t>
         </is>
       </c>
       <c r="H134" s="19" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="K134" s="20" t="inlineStr">
         <is>
-          <t>#227</t>
+          <t>#226</t>
         </is>
       </c>
     </row>
@@ -6728,11 +6728,11 @@
         </is>
       </c>
       <c r="F135" s="15" t="n">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 지문·anonymousId·참여 코드로 참여자 상태를 조회하는 읽기 전용 스크립트</t>
+          <t xml:space="preserve">        feat: 서버 로그 줄에 trace ID를 넣어 Datadog Logs와 APM trace를 연결</t>
         </is>
       </c>
       <c r="H135" s="19" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="K135" s="20" t="inlineStr">
         <is>
-          <t>#228</t>
+          <t>#227</t>
         </is>
       </c>
     </row>
@@ -6773,11 +6773,11 @@
         </is>
       </c>
       <c r="F136" s="15" t="n">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="G136" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: Datadog Agent 설치 및 Log Management 연동</t>
+          <t xml:space="preserve">        feat: 지문·anonymousId·참여 코드로 참여자 상태를 조회하는 읽기 전용 스크립트</t>
         </is>
       </c>
       <c r="H136" s="19" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="K136" s="20" t="inlineStr">
         <is>
-          <t>#267</t>
+          <t>#228</t>
         </is>
       </c>
     </row>
@@ -6818,11 +6818,11 @@
         </is>
       </c>
       <c r="F137" s="15" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: Datadog APM(dd-trace) 계측 도입</t>
+          <t xml:space="preserve">        chore: Datadog Agent 설치 및 Log Management 연동</t>
         </is>
       </c>
       <c r="H137" s="19" t="inlineStr">
@@ -6836,11 +6836,11 @@
       </c>
       <c r="K137" s="20" t="inlineStr">
         <is>
-          <t>#268</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" outlineLevel="2">
+          <t>#267</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" outlineLevel="2" ht="25.5" customHeight="1">
       <c r="A138" s="15" t="n">
         <v>137</v>
       </c>
@@ -6849,21 +6849,25 @@
           <t>Epic 7</t>
         </is>
       </c>
-      <c r="C138" s="16" t="n"/>
+      <c r="C138" s="16" t="inlineStr">
+        <is>
+          <t>Story 7-2</t>
+        </is>
+      </c>
       <c r="D138" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F138" s="15" t="n">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="G138" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    fix: 본문 필드가 문자열이 아닐 때 서버가 500을 반환하는 문제</t>
+          <t xml:space="preserve">        feat: Datadog APM(dd-trace) 계측 도입</t>
         </is>
       </c>
       <c r="H138" s="19" t="inlineStr">
@@ -6873,140 +6877,136 @@
       </c>
       <c r="I138" s="16" t="n"/>
       <c r="J138" s="15" t="n">
+        <v>279</v>
+      </c>
+      <c r="K138" s="20" t="inlineStr">
+        <is>
+          <t>#268</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" outlineLevel="1">
+      <c r="A139" s="15" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>Epic 7</t>
+        </is>
+      </c>
+      <c r="C139" s="16" t="n"/>
+      <c r="D139" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E139" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F139" s="15" t="n">
+        <v>232</v>
+      </c>
+      <c r="G139" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    fix: 본문 필드가 문자열이 아닐 때 서버가 500을 반환하는 문제</t>
+        </is>
+      </c>
+      <c r="H139" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I139" s="16" t="n"/>
+      <c r="J139" s="15" t="n">
         <v>202</v>
       </c>
-      <c r="K138" s="20" t="inlineStr">
+      <c r="K139" s="20" t="inlineStr">
         <is>
           <t>#232</t>
         </is>
       </c>
     </row>
-    <row r="139" outlineLevel="1">
-      <c r="A139" s="3" t="n">
-        <v>138</v>
-      </c>
-      <c r="B139" s="4" t="inlineStr">
+    <row r="140" outlineLevel="2">
+      <c r="A140" s="3" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C139" s="4" t="n"/>
-      <c r="D139" s="3" t="n">
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E139" s="5" t="inlineStr">
+      <c r="E140" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F139" s="3" t="n">
+      <c r="F140" s="3" t="n">
         <v>207</v>
       </c>
-      <c r="G139" s="6" t="inlineStr">
+      <c r="G140" s="6" t="inlineStr">
         <is>
           <t>Epic 8. 본 연구 착수 전 IRB 정합성 확보 및 시스템 정비</t>
         </is>
       </c>
-      <c r="H139" s="7" t="inlineStr">
+      <c r="H140" s="7" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I139" s="4" t="n"/>
-      <c r="J139" s="3" t="n"/>
-      <c r="K139" s="8" t="inlineStr">
+      <c r="I140" s="4" t="n"/>
+      <c r="J140" s="3" t="n"/>
+      <c r="K140" s="8" t="inlineStr">
         <is>
           <t>#207</t>
         </is>
       </c>
     </row>
-    <row r="140" outlineLevel="2">
-      <c r="A140" s="9" t="n">
-        <v>139</v>
-      </c>
-      <c r="B140" s="10" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C140" s="10" t="inlineStr">
+      <c r="C141" s="10" t="inlineStr">
         <is>
           <t>Story 8-1</t>
         </is>
       </c>
-      <c r="D140" s="9" t="n">
+      <c r="D141" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E140" s="11" t="inlineStr">
+      <c r="E141" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F140" s="9" t="n">
+      <c r="F141" s="9" t="n">
         <v>280</v>
       </c>
-      <c r="G140" s="12" t="inlineStr">
+      <c r="G141" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-1: 연구 기간이 끝나면 수집·전송이 자동으로 멈추고 참가자에게 안내된다</t>
         </is>
       </c>
-      <c r="H140" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I140" s="10" t="n"/>
-      <c r="J140" s="9" t="n">
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I141" s="10" t="n"/>
+      <c r="J141" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K140" s="14" t="inlineStr">
+      <c r="K141" s="14" t="inlineStr">
         <is>
           <t>#280</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" s="16" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C141" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-1</t>
-        </is>
-      </c>
-      <c r="D141" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E141" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F141" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="G141" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 연구 종료 후 수집·생성 중단 + "오늘" 탭 마지막 날짜 고정</t>
-        </is>
-      </c>
-      <c r="H141" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I141" s="16" t="n"/>
-      <c r="J141" s="15" t="n">
-        <v>280</v>
-      </c>
-      <c r="K141" s="20" t="inlineStr">
-        <is>
-          <t>#160</t>
         </is>
       </c>
     </row>
@@ -7033,11 +7033,11 @@
         </is>
       </c>
       <c r="F142" s="15" t="n">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 기간 종료 시 확장 프로그램 수집·전송 자동 중단 및 제거 안내</t>
+          <t xml:space="preserve">        feat: 연구 종료 후 수집·생성 중단 + "오늘" 탭 마지막 날짜 고정</t>
         </is>
       </c>
       <c r="H142" s="19" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="K142" s="20" t="inlineStr">
         <is>
-          <t>#197</t>
+          <t>#160</t>
         </is>
       </c>
     </row>
@@ -7078,11 +7078,11 @@
         </is>
       </c>
       <c r="F143" s="15" t="n">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 연구 기간에 따라 달라지는 문구를 상수에서 생성하고 기간 상수 일치를 테스트로 고정</t>
+          <t xml:space="preserve">        feat: 연구 기간 종료 시 확장 프로그램 수집·전송 자동 중단 및 제거 안내</t>
         </is>
       </c>
       <c r="H143" s="19" t="inlineStr">
@@ -7096,187 +7096,187 @@
       </c>
       <c r="K143" s="20" t="inlineStr">
         <is>
+          <t>#197</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" outlineLevel="2">
+      <c r="A144" s="15" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C144" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-1</t>
+        </is>
+      </c>
+      <c r="D144" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F144" s="15" t="n">
+        <v>210</v>
+      </c>
+      <c r="G144" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        feat: 연구 기간에 따라 달라지는 문구를 상수에서 생성하고 기간 상수 일치를 테스트로 고정</t>
+        </is>
+      </c>
+      <c r="H144" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I144" s="16" t="n"/>
+      <c r="J144" s="15" t="n">
+        <v>280</v>
+      </c>
+      <c r="K144" s="20" t="inlineStr">
+        <is>
           <t>#210</t>
         </is>
       </c>
     </row>
-    <row r="144" outlineLevel="2">
-      <c r="A144" s="9" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="10" t="inlineStr">
+    <row r="145" outlineLevel="2">
+      <c r="A145" s="9" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C144" s="10" t="inlineStr">
+      <c r="C145" s="10" t="inlineStr">
         <is>
           <t>Story 8-2</t>
         </is>
       </c>
-      <c r="D144" s="9" t="n">
+      <c r="D145" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E144" s="11" t="inlineStr">
+      <c r="E145" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F144" s="9" t="n">
+      <c r="F145" s="9" t="n">
         <v>281</v>
       </c>
-      <c r="G144" s="12" t="inlineStr">
+      <c r="G145" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-2: 참가자에게 집단(실험/대조) 정보가 노출되지 않는다</t>
         </is>
       </c>
-      <c r="H144" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I144" s="10" t="n"/>
-      <c r="J144" s="9" t="n">
+      <c r="H145" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I145" s="10" t="n"/>
+      <c r="J145" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K144" s="14" t="inlineStr">
+      <c r="K145" s="14" t="inlineStr">
         <is>
           <t>#281</t>
         </is>
       </c>
     </row>
-    <row r="145" outlineLevel="2">
-      <c r="A145" s="15" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="16" t="inlineStr">
+    <row r="146" outlineLevel="1">
+      <c r="A146" s="15" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="16" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C145" s="16" t="inlineStr">
+      <c r="C146" s="16" t="inlineStr">
         <is>
           <t>Story 8-2</t>
         </is>
       </c>
-      <c r="D145" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E145" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F145" s="15" t="n">
+      <c r="D146" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E146" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F146" s="15" t="n">
         <v>209</v>
       </c>
-      <c r="G145" s="18" t="inlineStr">
+      <c r="G146" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        feat: 참여코드에서 집단 표식 제거</t>
         </is>
       </c>
-      <c r="H145" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I145" s="16" t="n"/>
-      <c r="J145" s="15" t="n">
+      <c r="H146" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I146" s="16" t="n"/>
+      <c r="J146" s="15" t="n">
         <v>281</v>
       </c>
-      <c r="K145" s="20" t="inlineStr">
+      <c r="K146" s="20" t="inlineStr">
         <is>
           <t>#209</t>
         </is>
       </c>
     </row>
-    <row r="146" outlineLevel="1">
-      <c r="A146" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="10" t="inlineStr">
+    <row r="147" outlineLevel="2">
+      <c r="A147" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>Story 8-3</t>
         </is>
       </c>
-      <c r="D146" s="9" t="n">
+      <c r="D147" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E146" s="11" t="inlineStr">
+      <c r="E147" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F146" s="9" t="n">
+      <c r="F147" s="9" t="n">
         <v>218</v>
       </c>
-      <c r="G146" s="12" t="inlineStr">
+      <c r="G147" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-3: 화면·피드백·분석의 시청 집계 기준을 유효 시청·시청 시간으로 통일한다</t>
         </is>
       </c>
-      <c r="H146" s="13" t="inlineStr">
+      <c r="H147" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I146" s="10" t="n"/>
-      <c r="J146" s="9" t="n">
+      <c r="I147" s="10" t="n"/>
+      <c r="J147" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K146" s="14" t="inlineStr">
+      <c r="K147" s="14" t="inlineStr">
         <is>
           <t>#218</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" outlineLevel="2">
-      <c r="A147" s="15" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="16" t="inlineStr">
-        <is>
-          <t>Epic 8</t>
-        </is>
-      </c>
-      <c r="C147" s="16" t="inlineStr">
-        <is>
-          <t>Story 8-3</t>
-        </is>
-      </c>
-      <c r="D147" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E147" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F147" s="15" t="n">
-        <v>211</v>
-      </c>
-      <c r="G147" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        feat: 기간별 리뷰 첫 줄에 분야별 비중과 지난 구간 대비 변화를 사실 문장으로 추가</t>
-        </is>
-      </c>
-      <c r="H147" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I147" s="16" t="n"/>
-      <c r="J147" s="15" t="n">
-        <v>218</v>
-      </c>
-      <c r="K147" s="20" t="inlineStr">
-        <is>
-          <t>#211</t>
         </is>
       </c>
     </row>
@@ -7303,11 +7303,11 @@
         </is>
       </c>
       <c r="F148" s="15" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G148" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 팝업 화면 숫자를 서버 집계 기준으로 통일하고 기간별 탭을 분야별 시청 시간 꺾은선으로 교체</t>
+          <t xml:space="preserve">        feat: 기간별 리뷰 첫 줄에 분야별 비중과 지난 구간 대비 변화를 사실 문장으로 추가</t>
         </is>
       </c>
       <c r="H148" s="19" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="K148" s="20" t="inlineStr">
         <is>
-          <t>#217</t>
+          <t>#211</t>
         </is>
       </c>
     </row>
@@ -7348,16 +7348,16 @@
         </is>
       </c>
       <c r="F149" s="15" t="n">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="G149" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        docs: 시청 집계 기준·화면 지표 결정을 기록하고 사전등록 문서에 반영</t>
+          <t xml:space="preserve">        feat: 팝업 화면 숫자를 서버 집계 기준으로 통일하고 기간별 탭을 분야별 시청 시간 꺾은선으로 교체</t>
         </is>
       </c>
       <c r="H149" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I149" s="16" t="n"/>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="K149" s="20" t="inlineStr">
         <is>
-          <t>#253</t>
+          <t>#217</t>
         </is>
       </c>
     </row>
@@ -7393,16 +7393,16 @@
         </is>
       </c>
       <c r="F150" s="15" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G150" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 집계를 원본 영상 데이터에서 유효 시청·시청 시간 기준으로 계산</t>
+          <t xml:space="preserve">        docs: 시청 집계 기준·화면 지표 결정을 기록하고 사전등록 문서에 반영</t>
         </is>
       </c>
       <c r="H150" s="19" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="I150" s="16" t="n"/>
@@ -7411,7 +7411,7 @@
       </c>
       <c r="K150" s="20" t="inlineStr">
         <is>
-          <t>#254</t>
+          <t>#253</t>
         </is>
       </c>
     </row>
@@ -7438,11 +7438,11 @@
         </is>
       </c>
       <c r="F151" s="15" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G151" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 리뷰의 LLM 입력과 대체 문구를 유효 시청 기준으로 정렬</t>
+          <t xml:space="preserve">        feat: 오늘·기간 집계를 원본 영상 데이터에서 유효 시청·시청 시간 기준으로 계산</t>
         </is>
       </c>
       <c r="H151" s="19" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="K151" s="20" t="inlineStr">
         <is>
-          <t>#255</t>
+          <t>#254</t>
         </is>
       </c>
     </row>
@@ -7483,11 +7483,11 @@
         </is>
       </c>
       <c r="F152" s="15" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G152" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘 리뷰를 유효 영상이 늘었을 때만 최소 간격을 두고 생성</t>
+          <t xml:space="preserve">        feat: 오늘·기간 리뷰의 LLM 입력과 대체 문구를 유효 시청 기준으로 정렬</t>
         </is>
       </c>
       <c r="H152" s="19" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="K152" s="20" t="inlineStr">
         <is>
-          <t>#256</t>
+          <t>#255</t>
         </is>
       </c>
     </row>
@@ -7528,11 +7528,11 @@
         </is>
       </c>
       <c r="F153" s="15" t="n">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="G153" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 탭에서 제목을 먼저 보이고 시청 현황(개수) 표시를 정리</t>
+          <t xml:space="preserve">        feat: 오늘 리뷰를 유효 영상이 늘었을 때만 최소 간격을 두고 생성</t>
         </is>
       </c>
       <c r="H153" s="19" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="K153" s="20" t="inlineStr">
         <is>
-          <t>#262</t>
+          <t>#256</t>
         </is>
       </c>
     </row>
@@ -7569,15 +7569,15 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F154" s="15" t="n">
-        <v>302</v>
+        <v>262</v>
       </c>
       <c r="G154" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 탭을 닫을 때 마지막 영상의 시청 시간이 유실돼 "확인 중"으로 영구히 남음</t>
+          <t xml:space="preserve">        feat: 오늘·기간 탭에서 제목을 먼저 보이고 시청 현황(개수) 표시를 정리</t>
         </is>
       </c>
       <c r="H154" s="19" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="K154" s="20" t="inlineStr">
         <is>
-          <t>#302</t>
+          <t>#262</t>
         </is>
       </c>
     </row>
@@ -7618,11 +7618,11 @@
         </is>
       </c>
       <c r="F155" s="15" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G155" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: Shorts 시청 시간이 측정되지 않고 0초로 기록돼 유효 시청에서 빠짐</t>
+          <t xml:space="preserve">        fix: 탭을 닫을 때 마지막 영상의 시청 시간이 유실돼 "확인 중"으로 영구히 남음</t>
         </is>
       </c>
       <c r="H155" s="19" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="K155" s="20" t="inlineStr">
         <is>
-          <t>#303</t>
+          <t>#302</t>
         </is>
       </c>
     </row>
@@ -7663,11 +7663,11 @@
         </is>
       </c>
       <c r="F156" s="15" t="n">
-        <v>324</v>
+        <v>303</v>
       </c>
       <c r="G156" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 같은 탭에서 영상을 새로고침하거나 바로 다시 열면 기록이 둘로 나뉘거나 다시 연 뒤의 시청 시간이 유실됨</t>
+          <t xml:space="preserve">        fix: Shorts 시청 시간이 측정되지 않고 0초로 기록돼 유효 시청에서 빠짐</t>
         </is>
       </c>
       <c r="H156" s="19" t="inlineStr">
@@ -7675,17 +7675,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I156" s="16" t="inlineStr">
-        <is>
-          <t>#326</t>
-        </is>
-      </c>
+      <c r="I156" s="16" t="n"/>
       <c r="J156" s="15" t="n">
         <v>218</v>
       </c>
       <c r="K156" s="20" t="inlineStr">
         <is>
-          <t>#324</t>
+          <t>#303</t>
         </is>
       </c>
     </row>
@@ -7712,11 +7708,11 @@
         </is>
       </c>
       <c r="F157" s="15" t="n">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G157" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 10분 넘는 영상을 보는 중 세션이 끝나면 오늘 리뷰에서 그 영상이 빠지고, 시청 시간이 늦게 와도 리뷰의 영상 수·비중이 그래프와 어긋난 채 남음</t>
+          <t xml:space="preserve">        fix: 같은 탭에서 영상을 새로고침하거나 바로 다시 열면 기록이 둘로 나뉘거나 다시 연 뒤의 시청 시간이 유실됨</t>
         </is>
       </c>
       <c r="H157" s="19" t="inlineStr">
@@ -7726,7 +7722,7 @@
       </c>
       <c r="I157" s="16" t="inlineStr">
         <is>
-          <t>#329</t>
+          <t>#326</t>
         </is>
       </c>
       <c r="J157" s="15" t="n">
@@ -7734,7 +7730,7 @@
       </c>
       <c r="K157" s="20" t="inlineStr">
         <is>
-          <t>#325</t>
+          <t>#324</t>
         </is>
       </c>
     </row>
@@ -7761,11 +7757,11 @@
         </is>
       </c>
       <c r="F158" s="15" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G158" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        feat: 오늘·기간 탭 제목을 한 줄로 줄이고, 가장 많이 본 분야가 다를 때만 보조 줄로 알리며 분야명만 굵게 표시</t>
+          <t xml:space="preserve">        fix: 10분 넘는 영상을 보는 중 세션이 끝나면 오늘 리뷰에서 그 영상이 빠지고, 시청 시간이 늦게 와도 리뷰의 영상 수·비중이 그래프와 어긋난 채 남음</t>
         </is>
       </c>
       <c r="H158" s="19" t="inlineStr">
@@ -7775,7 +7771,7 @@
       </c>
       <c r="I158" s="16" t="inlineStr">
         <is>
-          <t>#330</t>
+          <t>#329</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
@@ -7783,7 +7779,7 @@
       </c>
       <c r="K158" s="20" t="inlineStr">
         <is>
-          <t>#327</t>
+          <t>#325</t>
         </is>
       </c>
     </row>
@@ -7810,11 +7806,11 @@
         </is>
       </c>
       <c r="F159" s="15" t="n">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="G159" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: "N일째"·현재 구간·베이스라인 판정이 설치 후 24시간 단위로 계산돼 KST 달력 기준 구간 경계와 최대 하루 어긋남</t>
+          <t xml:space="preserve">        feat: 오늘·기간 탭 제목을 한 줄로 줄이고, 가장 많이 본 분야가 다를 때만 보조 줄로 알리며 분야명만 굵게 표시</t>
         </is>
       </c>
       <c r="H159" s="19" t="inlineStr">
@@ -7824,7 +7820,7 @@
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
-          <t>#338</t>
+          <t>#330</t>
         </is>
       </c>
       <c r="J159" s="15" t="n">
@@ -7832,226 +7828,230 @@
       </c>
       <c r="K159" s="20" t="inlineStr">
         <is>
+          <t>#327</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" outlineLevel="1">
+      <c r="A160" s="15" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="16" t="inlineStr">
+        <is>
+          <t>Epic 8</t>
+        </is>
+      </c>
+      <c r="C160" s="16" t="inlineStr">
+        <is>
+          <t>Story 8-3</t>
+        </is>
+      </c>
+      <c r="D160" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E160" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F160" s="15" t="n">
+        <v>335</v>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: "N일째"·현재 구간·베이스라인 판정이 설치 후 24시간 단위로 계산돼 KST 달력 기준 구간 경계와 최대 하루 어긋남</t>
+        </is>
+      </c>
+      <c r="H160" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I160" s="16" t="inlineStr">
+        <is>
+          <t>#338</t>
+        </is>
+      </c>
+      <c r="J160" s="15" t="n">
+        <v>218</v>
+      </c>
+      <c r="K160" s="20" t="inlineStr">
+        <is>
           <t>#335</t>
         </is>
       </c>
     </row>
-    <row r="160" outlineLevel="1">
-      <c r="A160" s="9" t="n">
-        <v>159</v>
-      </c>
-      <c r="B160" s="10" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="10" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C160" s="10" t="inlineStr">
+      <c r="C161" s="10" t="inlineStr">
         <is>
           <t>Story 8-4</t>
         </is>
       </c>
-      <c r="D160" s="9" t="n">
+      <c r="D161" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E160" s="11" t="inlineStr">
+      <c r="E161" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F160" s="9" t="n">
+      <c r="F161" s="9" t="n">
         <v>282</v>
       </c>
-      <c r="G160" s="12" t="inlineStr">
+      <c r="G161" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 8-4: IRB 변경심의를 신청하고 승인받는다</t>
         </is>
       </c>
-      <c r="H160" s="13" t="inlineStr">
+      <c r="H161" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I160" s="10" t="n"/>
-      <c r="J160" s="9" t="n">
+      <c r="I161" s="10" t="n"/>
+      <c r="J161" s="9" t="n">
         <v>207</v>
       </c>
-      <c r="K160" s="14" t="inlineStr">
+      <c r="K161" s="14" t="inlineStr">
         <is>
           <t>#282</t>
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="15" t="n">
-        <v>160</v>
-      </c>
-      <c r="B161" s="16" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="15" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="16" t="inlineStr">
         <is>
           <t>Epic 8</t>
         </is>
       </c>
-      <c r="C161" s="16" t="inlineStr">
+      <c r="C162" s="16" t="inlineStr">
         <is>
           <t>Story 8-4</t>
         </is>
       </c>
-      <c r="D161" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E161" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F161" s="15" t="n">
+      <c r="D162" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F162" s="15" t="n">
         <v>213</v>
       </c>
-      <c r="G161" s="18" t="inlineStr">
+      <c r="G162" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">        docs: IRB 변경심의 신청</t>
         </is>
       </c>
-      <c r="H161" s="19" t="inlineStr">
+      <c r="H162" s="19" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I161" s="16" t="n"/>
-      <c r="J161" s="15" t="n">
+      <c r="I162" s="16" t="n"/>
+      <c r="J162" s="15" t="n">
         <v>282</v>
       </c>
-      <c r="K161" s="20" t="inlineStr">
+      <c r="K162" s="20" t="inlineStr">
         <is>
           <t>#213</t>
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>161</v>
-      </c>
-      <c r="B162" s="4" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="3" t="n">
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E162" s="5" t="inlineStr">
+      <c r="E163" s="5" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="F162" s="3" t="n">
+      <c r="F163" s="3" t="n">
         <v>208</v>
       </c>
-      <c r="G162" s="6" t="inlineStr">
+      <c r="G163" s="6" t="inlineStr">
         <is>
           <t>Epic 9. 테스트 및 품질 보강</t>
         </is>
       </c>
-      <c r="H162" s="7" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="n"/>
-      <c r="J162" s="3" t="n"/>
-      <c r="K162" s="8" t="inlineStr">
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="n"/>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="8" t="inlineStr">
         <is>
           <t>#208</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="9" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" s="10" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="9" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C163" s="10" t="inlineStr">
+      <c r="C164" s="10" t="inlineStr">
         <is>
           <t>Story 9-1</t>
         </is>
       </c>
-      <c r="D163" s="9" t="n">
+      <c r="D164" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E163" s="11" t="inlineStr">
+      <c r="E164" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F163" s="9" t="n">
+      <c r="F164" s="9" t="n">
         <v>283</v>
       </c>
-      <c r="G163" s="12" t="inlineStr">
+      <c r="G164" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-1: 위험 기반 테스트로 연구 데이터 오염 위험을 제거한다</t>
         </is>
       </c>
-      <c r="H163" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I163" s="10" t="n"/>
-      <c r="J163" s="9" t="n">
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I164" s="10" t="n"/>
+      <c r="J164" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K163" s="14" t="inlineStr">
+      <c r="K164" s="14" t="inlineStr">
         <is>
           <t>#283</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="15" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C164" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-1</t>
-        </is>
-      </c>
-      <c r="D164" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E164" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F164" s="15" t="n">
-        <v>165</v>
-      </c>
-      <c r="G164" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 위험 기반 테스트 보강 및 커버리지 측정 도입</t>
-        </is>
-      </c>
-      <c r="H164" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I164" s="16" t="n"/>
-      <c r="J164" s="15" t="n">
-        <v>283</v>
-      </c>
-      <c r="K164" s="20" t="inlineStr">
-        <is>
-          <t>#165</t>
         </is>
       </c>
     </row>
@@ -8078,11 +8078,11 @@
         </is>
       </c>
       <c r="F165" s="15" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G165" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 위험 기반 테스트 4개 항목 구현 및 리팩터링</t>
+          <t xml:space="preserve">        test: 위험 기반 테스트 보강 및 커버리지 측정 도입</t>
         </is>
       </c>
       <c r="H165" s="19" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="K165" s="20" t="inlineStr">
         <is>
-          <t>#167</t>
+          <t>#165</t>
         </is>
       </c>
     </row>
@@ -8123,11 +8123,11 @@
         </is>
       </c>
       <c r="F166" s="15" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G166" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 테스트 공백 보완 및 진행 기록</t>
+          <t xml:space="preserve">        test: 위험 기반 테스트 4개 항목 구현 및 리팩터링</t>
         </is>
       </c>
       <c r="H166" s="19" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="K166" s="20" t="inlineStr">
         <is>
-          <t>#169</t>
+          <t>#167</t>
         </is>
       </c>
     </row>
@@ -8164,15 +8164,15 @@
       </c>
       <c r="E167" s="17" t="inlineStr">
         <is>
-          <t>Bug</t>
+          <t>Task</t>
         </is>
       </c>
       <c r="F167" s="15" t="n">
-        <v>294</v>
+        <v>169</v>
       </c>
       <c r="G167" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        fix: 클라이언트가 보내는 시각도 시간대가 없으면 거부하고 UTC ISO로 정규화</t>
+          <t xml:space="preserve">        test: 테스트 공백 보완 및 진행 기록</t>
         </is>
       </c>
       <c r="H167" s="19" t="inlineStr">
@@ -8180,107 +8180,107 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I167" s="16" t="inlineStr">
-        <is>
-          <t>#295</t>
-        </is>
-      </c>
+      <c r="I167" s="16" t="n"/>
       <c r="J167" s="15" t="n">
         <v>283</v>
       </c>
       <c r="K167" s="20" t="inlineStr">
         <is>
+          <t>#169</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="15" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C168" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-1</t>
+        </is>
+      </c>
+      <c r="D168" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E168" s="17" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="F168" s="15" t="n">
+        <v>294</v>
+      </c>
+      <c r="G168" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        fix: 클라이언트가 보내는 시각도 시간대가 없으면 거부하고 UTC ISO로 정규화</t>
+        </is>
+      </c>
+      <c r="H168" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>#295</t>
+        </is>
+      </c>
+      <c r="J168" s="15" t="n">
+        <v>283</v>
+      </c>
+      <c r="K168" s="20" t="inlineStr">
+        <is>
           <t>#294</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="9" t="n">
-        <v>167</v>
-      </c>
-      <c r="B168" s="10" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="9" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C168" s="10" t="inlineStr">
+      <c r="C169" s="10" t="inlineStr">
         <is>
           <t>Story 9-2</t>
         </is>
       </c>
-      <c r="D168" s="9" t="n">
+      <c r="D169" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E168" s="11" t="inlineStr">
+      <c r="E169" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F168" s="9" t="n">
+      <c r="F169" s="9" t="n">
         <v>285</v>
       </c>
-      <c r="G168" s="12" t="inlineStr">
+      <c r="G169" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-2: 핵심 API 경로가 실제 라우터 기준 통합 테스트로 보호된다</t>
         </is>
       </c>
-      <c r="H168" s="13" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I168" s="10" t="n"/>
-      <c r="J168" s="9" t="n">
+      <c r="H169" s="13" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I169" s="10" t="n"/>
+      <c r="J169" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K168" s="14" t="inlineStr">
+      <c r="K169" s="14" t="inlineStr">
         <is>
           <t>#285</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="15" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C169" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-2</t>
-        </is>
-      </c>
-      <c r="D169" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E169" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F169" s="15" t="n">
-        <v>234</v>
-      </c>
-      <c r="G169" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 종료 게이트 API 실제 라우터 배선 테스트</t>
-        </is>
-      </c>
-      <c r="H169" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I169" s="16" t="n"/>
-      <c r="J169" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="K169" s="20" t="inlineStr">
-        <is>
-          <t>#234</t>
         </is>
       </c>
     </row>
@@ -8307,11 +8307,11 @@
         </is>
       </c>
       <c r="F170" s="15" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G170" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: CORS 허용 출처 규칙 회귀 테스트</t>
+          <t xml:space="preserve">        test: 종료 게이트 API 실제 라우터 배선 테스트</t>
         </is>
       </c>
       <c r="H170" s="19" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="K170" s="20" t="inlineStr">
         <is>
-          <t>#235</t>
+          <t>#234</t>
         </is>
       </c>
     </row>
@@ -8352,11 +8352,11 @@
         </is>
       </c>
       <c r="F171" s="15" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G171" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: cron 스크립트(백업·모니터링) 테스트 가능 구조 및 테스트</t>
+          <t xml:space="preserve">        test: CORS 허용 출처 규칙 회귀 테스트</t>
         </is>
       </c>
       <c r="H171" s="19" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="K171" s="20" t="inlineStr">
         <is>
-          <t>#236</t>
+          <t>#235</t>
         </is>
       </c>
     </row>
@@ -8397,11 +8397,11 @@
         </is>
       </c>
       <c r="F172" s="15" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G172" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 연구 종료 게이트 통합 테스트를 실제 라우터로 전환</t>
+          <t xml:space="preserve">        test: cron 스크립트(백업·모니터링) 테스트 가능 구조 및 테스트</t>
         </is>
       </c>
       <c r="H172" s="19" t="inlineStr">
@@ -8415,97 +8415,97 @@
       </c>
       <c r="K172" s="20" t="inlineStr">
         <is>
+          <t>#236</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="15" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C173" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-2</t>
+        </is>
+      </c>
+      <c r="D173" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E173" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F173" s="15" t="n">
+        <v>240</v>
+      </c>
+      <c r="G173" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 연구 종료 게이트 통합 테스트를 실제 라우터로 전환</t>
+        </is>
+      </c>
+      <c r="H173" s="19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I173" s="16" t="n"/>
+      <c r="J173" s="15" t="n">
+        <v>285</v>
+      </c>
+      <c r="K173" s="20" t="inlineStr">
+        <is>
           <t>#240</t>
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="9" t="n">
-        <v>172</v>
-      </c>
-      <c r="B173" s="10" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="9" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C173" s="10" t="inlineStr">
+      <c r="C174" s="10" t="inlineStr">
         <is>
           <t>Story 9-3</t>
         </is>
       </c>
-      <c r="D173" s="9" t="n">
+      <c r="D174" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E173" s="11" t="inlineStr">
+      <c r="E174" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F173" s="9" t="n">
+      <c r="F174" s="9" t="n">
         <v>286</v>
       </c>
-      <c r="G173" s="12" t="inlineStr">
+      <c r="G174" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-3: 커버리지를 정확히 측정하고 목표치를 유지한다</t>
         </is>
       </c>
-      <c r="H173" s="13" t="inlineStr">
+      <c r="H174" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I173" s="10" t="n"/>
-      <c r="J173" s="9" t="n">
+      <c r="I174" s="10" t="n"/>
+      <c r="J174" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K173" s="14" t="inlineStr">
+      <c r="K174" s="14" t="inlineStr">
         <is>
           <t>#286</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="15" t="n">
-        <v>173</v>
-      </c>
-      <c r="B174" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C174" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-3</t>
-        </is>
-      </c>
-      <c r="D174" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E174" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F174" s="15" t="n">
-        <v>233</v>
-      </c>
-      <c r="G174" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: 커버리지 측정 보정 및 CI 정비</t>
-        </is>
-      </c>
-      <c r="H174" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I174" s="16" t="n"/>
-      <c r="J174" s="15" t="n">
-        <v>286</v>
-      </c>
-      <c r="K174" s="20" t="inlineStr">
-        <is>
-          <t>#233</t>
         </is>
       </c>
     </row>
@@ -8532,11 +8532,11 @@
         </is>
       </c>
       <c r="F175" s="15" t="n">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="G175" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: content.js를 커버리지로 측정되게 하고 80% 이상으로 보강</t>
+          <t xml:space="preserve">        test: 커버리지 측정 보정 및 CI 정비</t>
         </is>
       </c>
       <c r="H175" s="19" t="inlineStr">
@@ -8544,17 +8544,13 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I175" s="16" t="inlineStr">
-        <is>
-          <t>#266</t>
-        </is>
-      </c>
+      <c r="I175" s="16" t="n"/>
       <c r="J175" s="15" t="n">
         <v>286</v>
       </c>
       <c r="K175" s="20" t="inlineStr">
         <is>
-          <t>#259</t>
+          <t>#233</t>
         </is>
       </c>
     </row>
@@ -8581,11 +8577,11 @@
         </is>
       </c>
       <c r="F176" s="15" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="G176" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 팝업 파일을 커버리지로 측정되게 전환</t>
+          <t xml:space="preserve">        test: content.js를 커버리지로 측정되게 하고 80% 이상으로 보강</t>
         </is>
       </c>
       <c r="H176" s="19" t="inlineStr">
@@ -8595,7 +8591,7 @@
       </c>
       <c r="I176" s="16" t="inlineStr">
         <is>
-          <t>#284</t>
+          <t>#266</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
@@ -8603,7 +8599,7 @@
       </c>
       <c r="K176" s="20" t="inlineStr">
         <is>
-          <t>#265</t>
+          <t>#259</t>
         </is>
       </c>
     </row>
@@ -8630,11 +8626,11 @@
         </is>
       </c>
       <c r="F177" s="15" t="n">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="G177" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 앱 조립을 create-app.js로 분리하고 실제 조립된 앱(미들웨어 순서·라우터 마운트)을 테스트로 검증</t>
+          <t xml:space="preserve">        test: 팝업 파일을 커버리지로 측정되게 전환</t>
         </is>
       </c>
       <c r="H177" s="19" t="inlineStr">
@@ -8644,7 +8640,7 @@
       </c>
       <c r="I177" s="16" t="inlineStr">
         <is>
-          <t>#298</t>
+          <t>#284</t>
         </is>
       </c>
       <c r="J177" s="15" t="n">
@@ -8652,7 +8648,7 @@
       </c>
       <c r="K177" s="20" t="inlineStr">
         <is>
-          <t>#296</t>
+          <t>#265</t>
         </is>
       </c>
     </row>
@@ -8679,11 +8675,11 @@
         </is>
       </c>
       <c r="F178" s="15" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G178" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: seed-codes.js를 scripts/로 옮겨 테스트 가능한 구조로 바꾸고, 잘못된 group이 있으면 명단 등록을 거부</t>
+          <t xml:space="preserve">        test: 앱 조립을 create-app.js로 분리하고 실제 조립된 앱(미들웨어 순서·라우터 마운트)을 테스트로 검증</t>
         </is>
       </c>
       <c r="H178" s="19" t="inlineStr">
@@ -8691,13 +8687,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I178" s="16" t="n"/>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>#298</t>
+        </is>
+      </c>
       <c r="J178" s="15" t="n">
         <v>286</v>
       </c>
       <c r="K178" s="20" t="inlineStr">
         <is>
-          <t>#297</t>
+          <t>#296</t>
         </is>
       </c>
     </row>
@@ -8724,16 +8724,16 @@
         </is>
       </c>
       <c r="F179" s="15" t="n">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="G179" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        test: 서버 테스트를 Node 직접 실행 프로젝트로 분리해 커버리지 줄 밀림을 없애고, 줄 매핑 오류를 CI에서 감시</t>
+          <t xml:space="preserve">        test: seed-codes.js를 scripts/로 옮겨 테스트 가능한 구조로 바꾸고, 잘못된 group이 있으면 명단 등록을 거부</t>
         </is>
       </c>
       <c r="H179" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I179" s="16" t="n"/>
@@ -8742,101 +8742,97 @@
       </c>
       <c r="K179" s="20" t="inlineStr">
         <is>
+          <t>#297</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="15" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-3</t>
+        </is>
+      </c>
+      <c r="D180" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E180" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F180" s="15" t="n">
+        <v>316</v>
+      </c>
+      <c r="G180" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        test: 서버 테스트를 Node 직접 실행 프로젝트로 분리해 커버리지 줄 밀림을 없애고, 줄 매핑 오류를 CI에서 감시</t>
+        </is>
+      </c>
+      <c r="H180" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I180" s="16" t="n"/>
+      <c r="J180" s="15" t="n">
+        <v>286</v>
+      </c>
+      <c r="K180" s="20" t="inlineStr">
+        <is>
           <t>#316</t>
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="9" t="n">
-        <v>179</v>
-      </c>
-      <c r="B180" s="10" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C180" s="10" t="inlineStr">
+      <c r="C181" s="10" t="inlineStr">
         <is>
           <t>Story 9-4</t>
         </is>
       </c>
-      <c r="D180" s="9" t="n">
+      <c r="D181" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E180" s="11" t="inlineStr">
+      <c r="E181" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F180" s="9" t="n">
+      <c r="F181" s="9" t="n">
         <v>287</v>
       </c>
-      <c r="G180" s="12" t="inlineStr">
+      <c r="G181" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-4: 코드 형식·정적 분석·CI가 자동으로 관리된다</t>
         </is>
       </c>
-      <c r="H180" s="13" t="inlineStr">
+      <c r="H181" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I180" s="10" t="n"/>
-      <c r="J180" s="9" t="n">
+      <c r="I181" s="10" t="n"/>
+      <c r="J181" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K180" s="14" t="inlineStr">
+      <c r="K181" s="14" t="inlineStr">
         <is>
           <t>#287</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="15" t="n">
-        <v>180</v>
-      </c>
-      <c r="B181" s="16" t="inlineStr">
-        <is>
-          <t>Epic 9</t>
-        </is>
-      </c>
-      <c r="C181" s="16" t="inlineStr">
-        <is>
-          <t>Story 9-4</t>
-        </is>
-      </c>
-      <c r="D181" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="E181" s="17" t="inlineStr">
-        <is>
-          <t>Task</t>
-        </is>
-      </c>
-      <c r="F181" s="15" t="n">
-        <v>134</v>
-      </c>
-      <c r="G181" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        test: ESLint 설정 복구 및 핵심 로직(analysis/llm) 단위 테스트 도입</t>
-        </is>
-      </c>
-      <c r="H181" s="19" t="inlineStr">
-        <is>
-          <t>Closed</t>
-        </is>
-      </c>
-      <c r="I181" s="16" t="inlineStr">
-        <is>
-          <t>#135</t>
-        </is>
-      </c>
-      <c r="J181" s="15" t="n">
-        <v>287</v>
-      </c>
-      <c r="K181" s="20" t="inlineStr">
-        <is>
-          <t>#134</t>
         </is>
       </c>
     </row>
@@ -8863,11 +8859,11 @@
         </is>
       </c>
       <c r="F182" s="15" t="n">
-        <v>241</v>
+        <v>134</v>
       </c>
       <c r="G182" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: prettier 형식 일괄 정리 및 CI 형식 검사 추가</t>
+          <t xml:space="preserve">        test: ESLint 설정 복구 및 핵심 로직(analysis/llm) 단위 테스트 도입</t>
         </is>
       </c>
       <c r="H182" s="19" t="inlineStr">
@@ -8875,13 +8871,17 @@
           <t>Closed</t>
         </is>
       </c>
-      <c r="I182" s="16" t="n"/>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>#135</t>
+        </is>
+      </c>
       <c r="J182" s="15" t="n">
         <v>287</v>
       </c>
       <c r="K182" s="20" t="inlineStr">
         <is>
-          <t>#241</t>
+          <t>#134</t>
         </is>
       </c>
     </row>
@@ -8908,11 +8908,11 @@
         </is>
       </c>
       <c r="F183" s="15" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="G183" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: CI action을 Node 24 지원 버전으로 올리고 Dependabot으로 버전 업데이트 자동화</t>
+          <t xml:space="preserve">        chore: prettier 형식 일괄 정리 및 CI 형식 검사 추가</t>
         </is>
       </c>
       <c r="H183" s="19" t="inlineStr">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="K183" s="20" t="inlineStr">
         <is>
-          <t>#244</t>
+          <t>#241</t>
         </is>
       </c>
     </row>
@@ -8953,16 +8953,16 @@
         </is>
       </c>
       <c r="F184" s="15" t="n">
-        <v>288</v>
+        <v>244</v>
       </c>
       <c r="G184" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">        chore: SonarQube 코드 품질 측정 도입</t>
+          <t xml:space="preserve">        chore: CI action을 Node 24 지원 버전으로 올리고 Dependabot으로 버전 업데이트 자동화</t>
         </is>
       </c>
       <c r="H184" s="19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="I184" s="16" t="n"/>
@@ -8971,63 +8971,108 @@
       </c>
       <c r="K184" s="20" t="inlineStr">
         <is>
+          <t>#244</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="15" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="16" t="inlineStr">
+        <is>
+          <t>Epic 9</t>
+        </is>
+      </c>
+      <c r="C185" s="16" t="inlineStr">
+        <is>
+          <t>Story 9-4</t>
+        </is>
+      </c>
+      <c r="D185" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E185" s="17" t="inlineStr">
+        <is>
+          <t>Task</t>
+        </is>
+      </c>
+      <c r="F185" s="15" t="n">
+        <v>288</v>
+      </c>
+      <c r="G185" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        chore: SonarQube 코드 품질 측정 도입</t>
+        </is>
+      </c>
+      <c r="H185" s="19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I185" s="16" t="n"/>
+      <c r="J185" s="15" t="n">
+        <v>287</v>
+      </c>
+      <c r="K185" s="20" t="inlineStr">
+        <is>
           <t>#288</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="9" t="n">
-        <v>184</v>
-      </c>
-      <c r="B185" s="10" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
         <is>
           <t>Epic 9</t>
         </is>
       </c>
-      <c r="C185" s="10" t="inlineStr">
+      <c r="C186" s="10" t="inlineStr">
         <is>
           <t>Story 9-5</t>
         </is>
       </c>
-      <c r="D185" s="9" t="n">
+      <c r="D186" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="E185" s="11" t="inlineStr">
+      <c r="E186" s="11" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="F185" s="9" t="n">
+      <c r="F186" s="9" t="n">
         <v>289</v>
       </c>
-      <c r="G185" s="12" t="inlineStr">
+      <c r="G186" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">    Story 9-5: 본 연구 규모(참가자 약 80명)의 부하를 서버가 견딘다</t>
         </is>
       </c>
-      <c r="H185" s="13" t="inlineStr">
+      <c r="H186" s="13" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="I185" s="10" t="n"/>
-      <c r="J185" s="9" t="n">
+      <c r="I186" s="10" t="n"/>
+      <c r="J186" s="9" t="n">
         <v>208</v>
       </c>
-      <c r="K185" s="14" t="inlineStr">
+      <c r="K186" s="14" t="inlineStr">
         <is>
           <t>#289</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K185"/>
+  <autoFilter ref="A1:K186"/>
   <dataValidations count="2">
-    <dataValidation sqref="E2:E185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="E2:E186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Epic,Story,Task,Bug"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H185" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H2:H186" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Open,Closed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9217,6 +9262,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K183" r:id="rId182"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K186" r:id="rId185"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -9299,15 +9345,15 @@
         </is>
       </c>
       <c r="C2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A2,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A2,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A2,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F2" s="26">
@@ -9315,11 +9361,11 @@
         <v/>
       </c>
       <c r="G2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A2,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H2" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A2,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A2,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I2" s="36">
@@ -9339,15 +9385,15 @@
         </is>
       </c>
       <c r="C3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A3,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A3,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A3,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F3" s="26">
@@ -9355,11 +9401,11 @@
         <v/>
       </c>
       <c r="G3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A3,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H3" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A3,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A3,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I3" s="36">
@@ -9379,15 +9425,15 @@
         </is>
       </c>
       <c r="C4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A4,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A4,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A4,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F4" s="26">
@@ -9395,11 +9441,11 @@
         <v/>
       </c>
       <c r="G4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A4,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H4" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A4,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A4,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I4" s="36">
@@ -9419,15 +9465,15 @@
         </is>
       </c>
       <c r="C5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A5,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A5,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A5,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F5" s="26">
@@ -9435,11 +9481,11 @@
         <v/>
       </c>
       <c r="G5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A5,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H5" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A5,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A5,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I5" s="36">
@@ -9459,15 +9505,15 @@
         </is>
       </c>
       <c r="C6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A6,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A6,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A6,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F6" s="26">
@@ -9475,11 +9521,11 @@
         <v/>
       </c>
       <c r="G6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A6,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A6,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A6,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I6" s="36">
@@ -9499,15 +9545,15 @@
         </is>
       </c>
       <c r="C7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A7,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A7,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A7,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F7" s="26">
@@ -9515,11 +9561,11 @@
         <v/>
       </c>
       <c r="G7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A7,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A7,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A7,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I7" s="36">
@@ -9539,15 +9585,15 @@
         </is>
       </c>
       <c r="C8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A8,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A8,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A8,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F8" s="26">
@@ -9555,11 +9601,11 @@
         <v/>
       </c>
       <c r="G8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A8,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A8,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A8,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I8" s="36">
@@ -9579,15 +9625,15 @@
         </is>
       </c>
       <c r="C9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A9,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A9,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A9,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F9" s="26">
@@ -9595,11 +9641,11 @@
         <v/>
       </c>
       <c r="G9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A9,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H9" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A9,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A9,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I9" s="36">
@@ -9619,15 +9665,15 @@
         </is>
       </c>
       <c r="C10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$E$2:$E$185,"Story")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A10,백로그!$E$2:$E$186,"Story")</f>
         <v/>
       </c>
       <c r="D10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$E$2:$E$185,"Task")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A10,백로그!$E$2:$E$186,"Task")</f>
         <v/>
       </c>
       <c r="E10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$E$2:$E$185,"Bug")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A10,백로그!$E$2:$E$186,"Bug")</f>
         <v/>
       </c>
       <c r="F10" s="26">
@@ -9635,11 +9681,11 @@
         <v/>
       </c>
       <c r="G10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$H$2:$H$185,"Open",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A10,백로그!$H$2:$H$186,"Open",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="H10" s="26">
-        <f>COUNTIFS(백로그!$B$2:$B$185,$A10,백로그!$H$2:$H$185,"Closed",백로그!$E$2:$E$185,"&lt;&gt;Epic")</f>
+        <f>COUNTIFS(백로그!$B$2:$B$186,$A10,백로그!$H$2:$H$186,"Closed",백로그!$E$2:$E$186,"&lt;&gt;Epic")</f>
         <v/>
       </c>
       <c r="I10" s="36">
